--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85FCD18F-322D-4EAB-ADF6-41B63AD2607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3866D5A-9158-45F7-A8BC-2BB9792B684C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
     <t>ele</t>
   </si>
   <si>
-    <t>e_spv_001</t>
+    <t>e_spv_IDN_001</t>
   </si>
   <si>
     <t>solar resource in cluster 1</t>
@@ -661,439 +661,439 @@
     <t>no</t>
   </si>
   <si>
-    <t>e_spv_002</t>
+    <t>e_spv_IDN_002</t>
   </si>
   <si>
     <t>solar resource in cluster 2</t>
   </si>
   <si>
-    <t>e_spv_003</t>
+    <t>e_spv_IDN_003</t>
   </si>
   <si>
     <t>solar resource in cluster 3</t>
   </si>
   <si>
-    <t>e_spv_004</t>
+    <t>e_spv_IDN_004</t>
   </si>
   <si>
     <t>solar resource in cluster 4</t>
   </si>
   <si>
-    <t>e_spv_005</t>
+    <t>e_spv_IDN_005</t>
   </si>
   <si>
     <t>solar resource in cluster 5</t>
   </si>
   <si>
-    <t>e_spv_006</t>
+    <t>e_spv_IDN_006</t>
   </si>
   <si>
     <t>solar resource in cluster 6</t>
   </si>
   <si>
-    <t>e_spv_007</t>
+    <t>e_spv_IDN_007</t>
   </si>
   <si>
     <t>solar resource in cluster 7</t>
   </si>
   <si>
-    <t>e_spv_008</t>
+    <t>e_spv_IDN_008</t>
   </si>
   <si>
     <t>solar resource in cluster 8</t>
   </si>
   <si>
-    <t>e_spv_009</t>
+    <t>e_spv_IDN_009</t>
   </si>
   <si>
     <t>solar resource in cluster 9</t>
   </si>
   <si>
-    <t>e_spv_010</t>
+    <t>e_spv_IDN_010</t>
   </si>
   <si>
     <t>solar resource in cluster 10</t>
   </si>
   <si>
-    <t>e_spv_011</t>
+    <t>e_spv_IDN_011</t>
   </si>
   <si>
     <t>solar resource in cluster 11</t>
   </si>
   <si>
-    <t>e_spv_012</t>
+    <t>e_spv_IDN_012</t>
   </si>
   <si>
     <t>solar resource in cluster 12</t>
   </si>
   <si>
-    <t>e_spv_013</t>
+    <t>e_spv_IDN_013</t>
   </si>
   <si>
     <t>solar resource in cluster 13</t>
   </si>
   <si>
-    <t>e_spv_014</t>
+    <t>e_spv_IDN_014</t>
   </si>
   <si>
     <t>solar resource in cluster 14</t>
   </si>
   <si>
-    <t>e_spv_015</t>
+    <t>e_spv_IDN_015</t>
   </si>
   <si>
     <t>solar resource in cluster 15</t>
   </si>
   <si>
-    <t>e_spv_016</t>
+    <t>e_spv_IDN_016</t>
   </si>
   <si>
     <t>solar resource in cluster 16</t>
   </si>
   <si>
-    <t>e_spv_017</t>
+    <t>e_spv_IDN_017</t>
   </si>
   <si>
     <t>solar resource in cluster 17</t>
   </si>
   <si>
-    <t>e_spv_018</t>
+    <t>e_spv_IDN_018</t>
   </si>
   <si>
     <t>solar resource in cluster 18</t>
   </si>
   <si>
-    <t>e_spv_019</t>
+    <t>e_spv_IDN_019</t>
   </si>
   <si>
     <t>solar resource in cluster 19</t>
   </si>
   <si>
-    <t>e_spv_020</t>
+    <t>e_spv_IDN_020</t>
   </si>
   <si>
     <t>solar resource in cluster 20</t>
   </si>
   <si>
-    <t>e_spv_021</t>
+    <t>e_spv_IDN_021</t>
   </si>
   <si>
     <t>solar resource in cluster 21</t>
   </si>
   <si>
-    <t>e_spv_022</t>
+    <t>e_spv_IDN_022</t>
   </si>
   <si>
     <t>solar resource in cluster 22</t>
   </si>
   <si>
-    <t>e_spv_023</t>
+    <t>e_spv_IDN_023</t>
   </si>
   <si>
     <t>solar resource in cluster 23</t>
   </si>
   <si>
-    <t>e_spv_024</t>
+    <t>e_spv_IDN_024</t>
   </si>
   <si>
     <t>solar resource in cluster 24</t>
   </si>
   <si>
-    <t>e_spv_025</t>
+    <t>e_spv_IDN_025</t>
   </si>
   <si>
     <t>solar resource in cluster 25</t>
   </si>
   <si>
-    <t>e_spv_026</t>
+    <t>e_spv_IDN_026</t>
   </si>
   <si>
     <t>solar resource in cluster 26</t>
   </si>
   <si>
-    <t>e_spv_027</t>
+    <t>e_spv_IDN_027</t>
   </si>
   <si>
     <t>solar resource in cluster 27</t>
   </si>
   <si>
-    <t>e_spv_028</t>
+    <t>e_spv_IDN_028</t>
   </si>
   <si>
     <t>solar resource in cluster 28</t>
   </si>
   <si>
-    <t>e_spv_029</t>
+    <t>e_spv_IDN_029</t>
   </si>
   <si>
     <t>solar resource in cluster 29</t>
   </si>
   <si>
-    <t>e_spv_030</t>
+    <t>e_spv_IDN_030</t>
   </si>
   <si>
     <t>solar resource in cluster 30</t>
   </si>
   <si>
-    <t>e_spv_031</t>
+    <t>e_spv_IDN_031</t>
   </si>
   <si>
     <t>solar resource in cluster 31</t>
   </si>
   <si>
-    <t>e_spv_032</t>
+    <t>e_spv_IDN_032</t>
   </si>
   <si>
     <t>solar resource in cluster 32</t>
   </si>
   <si>
-    <t>e_spv_033</t>
+    <t>e_spv_IDN_033</t>
   </si>
   <si>
     <t>solar resource in cluster 33</t>
   </si>
   <si>
-    <t>e_spv_034</t>
+    <t>e_spv_IDN_034</t>
   </si>
   <si>
     <t>solar resource in cluster 34</t>
   </si>
   <si>
-    <t>e_spv_035</t>
+    <t>e_spv_IDN_035</t>
   </si>
   <si>
     <t>solar resource in cluster 35</t>
   </si>
   <si>
-    <t>e_spv_036</t>
+    <t>e_spv_IDN_036</t>
   </si>
   <si>
     <t>solar resource in cluster 36</t>
   </si>
   <si>
-    <t>e_spv_037</t>
+    <t>e_spv_IDN_037</t>
   </si>
   <si>
     <t>solar resource in cluster 37</t>
   </si>
   <si>
-    <t>e_spv_038</t>
+    <t>e_spv_IDN_038</t>
   </si>
   <si>
     <t>solar resource in cluster 38</t>
   </si>
   <si>
-    <t>e_spv_039</t>
+    <t>e_spv_IDN_039</t>
   </si>
   <si>
     <t>solar resource in cluster 39</t>
   </si>
   <si>
-    <t>e_spv_040</t>
+    <t>e_spv_IDN_040</t>
   </si>
   <si>
     <t>solar resource in cluster 40</t>
   </si>
   <si>
-    <t>e_spv_041</t>
+    <t>e_spv_IDN_041</t>
   </si>
   <si>
     <t>solar resource in cluster 41</t>
   </si>
   <si>
-    <t>e_spv_042</t>
+    <t>e_spv_IDN_042</t>
   </si>
   <si>
     <t>solar resource in cluster 42</t>
   </si>
   <si>
-    <t>e_spv_043</t>
+    <t>e_spv_IDN_043</t>
   </si>
   <si>
     <t>solar resource in cluster 43</t>
   </si>
   <si>
-    <t>e_spv_044</t>
+    <t>e_spv_IDN_044</t>
   </si>
   <si>
     <t>solar resource in cluster 44</t>
   </si>
   <si>
-    <t>e_spv_045</t>
+    <t>e_spv_IDN_045</t>
   </si>
   <si>
     <t>solar resource in cluster 45</t>
   </si>
   <si>
-    <t>e_spv_046</t>
+    <t>e_spv_IDN_046</t>
   </si>
   <si>
     <t>solar resource in cluster 46</t>
   </si>
   <si>
-    <t>e_spv_047</t>
+    <t>e_spv_IDN_047</t>
   </si>
   <si>
     <t>solar resource in cluster 47</t>
   </si>
   <si>
-    <t>e_spv_048</t>
+    <t>e_spv_IDN_048</t>
   </si>
   <si>
     <t>solar resource in cluster 48</t>
   </si>
   <si>
-    <t>e_spv_049</t>
+    <t>e_spv_IDN_049</t>
   </si>
   <si>
     <t>solar resource in cluster 49</t>
   </si>
   <si>
-    <t>e_spv_050</t>
+    <t>e_spv_IDN_050</t>
   </si>
   <si>
     <t>solar resource in cluster 50</t>
   </si>
   <si>
-    <t>e_spv_051</t>
+    <t>e_spv_IDN_051</t>
   </si>
   <si>
     <t>solar resource in cluster 51</t>
   </si>
   <si>
-    <t>e_spv_052</t>
+    <t>e_spv_IDN_052</t>
   </si>
   <si>
     <t>solar resource in cluster 52</t>
   </si>
   <si>
-    <t>e_spv_053</t>
+    <t>e_spv_IDN_053</t>
   </si>
   <si>
     <t>solar resource in cluster 53</t>
   </si>
   <si>
-    <t>e_spv_054</t>
+    <t>e_spv_IDN_054</t>
   </si>
   <si>
     <t>solar resource in cluster 54</t>
   </si>
   <si>
-    <t>e_spv_055</t>
+    <t>e_spv_IDN_055</t>
   </si>
   <si>
     <t>solar resource in cluster 55</t>
   </si>
   <si>
-    <t>e_spv_056</t>
+    <t>e_spv_IDN_056</t>
   </si>
   <si>
     <t>solar resource in cluster 56</t>
   </si>
   <si>
-    <t>e_spv_057</t>
+    <t>e_spv_IDN_057</t>
   </si>
   <si>
     <t>solar resource in cluster 57</t>
   </si>
   <si>
-    <t>e_spv_058</t>
+    <t>e_spv_IDN_058</t>
   </si>
   <si>
     <t>solar resource in cluster 58</t>
   </si>
   <si>
-    <t>e_spv_059</t>
+    <t>e_spv_IDN_059</t>
   </si>
   <si>
     <t>solar resource in cluster 59</t>
   </si>
   <si>
-    <t>e_spv_060</t>
+    <t>e_spv_IDN_060</t>
   </si>
   <si>
     <t>solar resource in cluster 60</t>
   </si>
   <si>
-    <t>e_spv_061</t>
+    <t>e_spv_IDN_061</t>
   </si>
   <si>
     <t>solar resource in cluster 61</t>
   </si>
   <si>
-    <t>e_spv_062</t>
+    <t>e_spv_IDN_062</t>
   </si>
   <si>
     <t>solar resource in cluster 62</t>
   </si>
   <si>
-    <t>e_spv_063</t>
+    <t>e_spv_IDN_063</t>
   </si>
   <si>
     <t>solar resource in cluster 63</t>
   </si>
   <si>
-    <t>e_spv_064</t>
+    <t>e_spv_IDN_064</t>
   </si>
   <si>
     <t>solar resource in cluster 64</t>
   </si>
   <si>
-    <t>e_spv_065</t>
+    <t>e_spv_IDN_065</t>
   </si>
   <si>
     <t>solar resource in cluster 65</t>
   </si>
   <si>
-    <t>e_spv_066</t>
+    <t>e_spv_IDN_066</t>
   </si>
   <si>
     <t>solar resource in cluster 66</t>
   </si>
   <si>
-    <t>e_spv_067</t>
+    <t>e_spv_IDN_067</t>
   </si>
   <si>
     <t>solar resource in cluster 67</t>
   </si>
   <si>
-    <t>e_spv_068</t>
+    <t>e_spv_IDN_068</t>
   </si>
   <si>
     <t>solar resource in cluster 68</t>
   </si>
   <si>
-    <t>e_spv_069</t>
+    <t>e_spv_IDN_069</t>
   </si>
   <si>
     <t>solar resource in cluster 69</t>
   </si>
   <si>
-    <t>e_spv_070</t>
+    <t>e_spv_IDN_070</t>
   </si>
   <si>
     <t>solar resource in cluster 70</t>
   </si>
   <si>
-    <t>e_spv_071</t>
+    <t>e_spv_IDN_071</t>
   </si>
   <si>
     <t>solar resource in cluster 71</t>
   </si>
   <si>
-    <t>e_spv_072</t>
+    <t>e_spv_IDN_072</t>
   </si>
   <si>
     <t>solar resource in cluster 72</t>
   </si>
   <si>
-    <t>e_spv_073</t>
+    <t>e_spv_IDN_073</t>
   </si>
   <si>
     <t>solar resource in cluster 73</t>
   </si>
   <si>
-    <t>e_spv_074</t>
+    <t>e_spv_IDN_074</t>
   </si>
   <si>
     <t>solar resource in cluster 74</t>
@@ -1111,226 +1111,226 @@
     <t>af~fx</t>
   </si>
   <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>elc_spv_004</t>
-  </si>
-  <si>
-    <t>elc_spv_005</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
-    <t>elc_spv_011</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_013</t>
-  </si>
-  <si>
-    <t>elc_spv_014</t>
-  </si>
-  <si>
-    <t>elc_spv_015</t>
-  </si>
-  <si>
-    <t>elc_spv_016</t>
-  </si>
-  <si>
-    <t>elc_spv_017</t>
-  </si>
-  <si>
-    <t>elc_spv_018</t>
-  </si>
-  <si>
-    <t>elc_spv_019</t>
-  </si>
-  <si>
-    <t>elc_spv_020</t>
-  </si>
-  <si>
-    <t>elc_spv_021</t>
-  </si>
-  <si>
-    <t>elc_spv_022</t>
-  </si>
-  <si>
-    <t>elc_spv_023</t>
-  </si>
-  <si>
-    <t>elc_spv_024</t>
-  </si>
-  <si>
-    <t>elc_spv_025</t>
-  </si>
-  <si>
-    <t>elc_spv_026</t>
-  </si>
-  <si>
-    <t>elc_spv_027</t>
-  </si>
-  <si>
-    <t>elc_spv_028</t>
-  </si>
-  <si>
-    <t>elc_spv_029</t>
-  </si>
-  <si>
-    <t>elc_spv_030</t>
-  </si>
-  <si>
-    <t>elc_spv_031</t>
-  </si>
-  <si>
-    <t>elc_spv_032</t>
-  </si>
-  <si>
-    <t>elc_spv_033</t>
-  </si>
-  <si>
-    <t>elc_spv_034</t>
-  </si>
-  <si>
-    <t>elc_spv_035</t>
-  </si>
-  <si>
-    <t>elc_spv_036</t>
-  </si>
-  <si>
-    <t>elc_spv_037</t>
-  </si>
-  <si>
-    <t>elc_spv_038</t>
-  </si>
-  <si>
-    <t>elc_spv_039</t>
-  </si>
-  <si>
-    <t>elc_spv_040</t>
-  </si>
-  <si>
-    <t>elc_spv_041</t>
-  </si>
-  <si>
-    <t>elc_spv_042</t>
-  </si>
-  <si>
-    <t>elc_spv_043</t>
-  </si>
-  <si>
-    <t>elc_spv_044</t>
-  </si>
-  <si>
-    <t>elc_spv_045</t>
-  </si>
-  <si>
-    <t>elc_spv_046</t>
-  </si>
-  <si>
-    <t>elc_spv_047</t>
-  </si>
-  <si>
-    <t>elc_spv_048</t>
-  </si>
-  <si>
-    <t>elc_spv_049</t>
-  </si>
-  <si>
-    <t>elc_spv_050</t>
-  </si>
-  <si>
-    <t>elc_spv_051</t>
-  </si>
-  <si>
-    <t>elc_spv_052</t>
-  </si>
-  <si>
-    <t>elc_spv_053</t>
-  </si>
-  <si>
-    <t>elc_spv_054</t>
-  </si>
-  <si>
-    <t>elc_spv_055</t>
-  </si>
-  <si>
-    <t>elc_spv_056</t>
-  </si>
-  <si>
-    <t>elc_spv_057</t>
-  </si>
-  <si>
-    <t>elc_spv_058</t>
-  </si>
-  <si>
-    <t>elc_spv_059</t>
-  </si>
-  <si>
-    <t>elc_spv_060</t>
-  </si>
-  <si>
-    <t>elc_spv_061</t>
-  </si>
-  <si>
-    <t>elc_spv_062</t>
-  </si>
-  <si>
-    <t>elc_spv_063</t>
-  </si>
-  <si>
-    <t>elc_spv_064</t>
-  </si>
-  <si>
-    <t>elc_spv_065</t>
-  </si>
-  <si>
-    <t>elc_spv_066</t>
-  </si>
-  <si>
-    <t>elc_spv_067</t>
-  </si>
-  <si>
-    <t>elc_spv_068</t>
-  </si>
-  <si>
-    <t>elc_spv_069</t>
-  </si>
-  <si>
-    <t>elc_spv_070</t>
-  </si>
-  <si>
-    <t>elc_spv_071</t>
-  </si>
-  <si>
-    <t>elc_spv_072</t>
-  </si>
-  <si>
-    <t>elc_spv_073</t>
-  </si>
-  <si>
-    <t>elc_spv_074</t>
+    <t>elc_spv_IDN_001</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_002</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_003</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_004</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_005</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_006</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_007</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_008</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_009</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_010</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_011</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_012</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_013</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_014</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_015</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_016</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_017</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_018</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_019</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_020</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_021</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_022</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_023</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_024</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_025</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_026</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_027</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_028</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_029</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_030</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_031</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_032</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_033</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_034</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_035</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_036</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_037</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_038</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_039</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_040</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_041</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_042</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_043</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_044</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_045</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_046</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_047</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_048</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_049</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_050</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_051</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_052</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_053</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_054</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_055</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_056</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_057</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_058</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_059</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_060</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_061</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_062</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_063</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_064</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_065</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_066</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_067</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_068</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_069</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_070</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_071</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_072</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_073</t>
+  </si>
+  <si>
+    <t>elc_spv_IDN_074</t>
   </si>
   <si>
     <t>primarycg</t>
@@ -1339,451 +1339,451 @@
     <t>pre</t>
   </si>
   <si>
-    <t>distr_solelc_spv_065</t>
+    <t>distr_solelc_spv_IDN_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_065</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 65</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
+    <t>distr_solelc_spv_IDN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_064</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 64</t>
   </si>
   <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
+    <t>distr_solelc_spv_IDN_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_051</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 51</t>
   </si>
   <si>
-    <t>distr_solelc_spv_070</t>
+    <t>distr_solelc_spv_IDN_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_070</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 70</t>
   </si>
   <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
+    <t>distr_solelc_spv_IDN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_007</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
+    <t>distr_solelc_spv_IDN_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_047</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
+    <t>distr_solelc_spv_IDN_037</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 37</t>
@@ -1795,1303 +1795,1303 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_w1316876158-275,e_w161965853-500,e_w169444592-500,e_ID10-500,e_w161960924-500,e_w604684007-500,e_w264550744-500,e_w966209515-500,e_ID15-500,e_w960747936-500,e_w960747902-500,e_w314452486-500,e_ID23-500,e_w1013653012-500,e_w629512849-500,e_ID29-500</t>
-  </si>
-  <si>
-    <t>e_ID33-500,e_w264550744-500,e_w769617021-500,e_w314452486-500,e_ID29-500,e_w267626657-500,e_ID31-500,e_w166633831-500,e_w689263666-500</t>
-  </si>
-  <si>
-    <t>e_ID37-500,e_w1308433899-500,e_ID36-500,e_w265318414-500,e_w398909640-500,e_w340978681-500,e_ID35-500,e_ID38-500</t>
-  </si>
-  <si>
-    <t>e_w615581242-275,e_ID2-275</t>
-  </si>
-  <si>
-    <t>e_w615581270-275,e_w615581232-275</t>
-  </si>
-  <si>
-    <t>e_w721685825-275,e_w754073846-275,e_w340205049-275,e_w310695690-275,e_w754096394-275,e_w337039411-275</t>
-  </si>
-  <si>
-    <t>e_w931931133-275,e_w1316876158-275,e_w1316786278-275,e_w931931121-275</t>
-  </si>
-  <si>
-    <t>e_w943539373-275,e_w1186182648-500,e_w736595653-500,e_w943539373-500</t>
-  </si>
-  <si>
-    <t>e_ID28-500,e_w562061281-275,e_ID27-500,e_ID2-275</t>
-  </si>
-  <si>
-    <t>e_ID2-275,e_w615581270-275,e_w615581242-275</t>
-  </si>
-  <si>
-    <t>e_w615581242-275</t>
-  </si>
-  <si>
-    <t>e_w759130125-230</t>
-  </si>
-  <si>
-    <t>e_ID1-275,e_w721674155-275,e_w340205049-275,e_w310958602-275</t>
-  </si>
-  <si>
-    <t>e_ID2-275</t>
-  </si>
-  <si>
-    <t>e_w615581270-275,e_w615581242-275</t>
-  </si>
-  <si>
-    <t>e_w615581242-275,e_w614955993-230,e_w1193553154-275,e_w544403431-230</t>
-  </si>
-  <si>
-    <t>e_w614955993-230,e_w544403431-230,e_w759130125-230</t>
-  </si>
-  <si>
-    <t>e_w939542521-275,e_ID4-275,e_ID3-275,e_ID7-275,e_w1186182648-500,e_w736595653-500,e_w930719092-275</t>
-  </si>
-  <si>
-    <t>e_ID28-500,e_w166633831-500,e_ID27-500,e_w398909640-500</t>
-  </si>
-  <si>
-    <t>e_ID27-500,e_ID34-500,e_w615581270-275</t>
-  </si>
-  <si>
-    <t>e_w544403426-230</t>
-  </si>
-  <si>
-    <t>e_w841499143-275,e_w1312287191-275,e_w528189342-275</t>
-  </si>
-  <si>
-    <t>e_w736595653-275,e_w736595653-500</t>
-  </si>
-  <si>
-    <t>e_ID38-500,e_w615581270-275</t>
-  </si>
-  <si>
-    <t>e_w562061281-275,e_ID2-275</t>
-  </si>
-  <si>
-    <t>e_w544403431-230,e_w759130125-230</t>
-  </si>
-  <si>
-    <t>e_w928220391-275,e_ID1-275,e_w721685825-275,e_w754073846-275</t>
-  </si>
-  <si>
-    <t>e_w736595653-500,e_w562061281-275,e_ID2-275</t>
-  </si>
-  <si>
-    <t>e_w615581270-275</t>
-  </si>
-  <si>
-    <t>e_w615581232-275,e_w544403426-230</t>
-  </si>
-  <si>
-    <t>e_w544403426-230,e_w759130125-230</t>
-  </si>
-  <si>
-    <t>e_w544403431-230,e_w614955993-230</t>
-  </si>
-  <si>
-    <t>e_w930719092-275,e_w841499143-275,e_w1186182648-500,e_w943539373-275,e_w753733608-275,e_w946191122-275,e_w610198177-275,e_w943539373-500</t>
-  </si>
-  <si>
-    <t>e_ID34-500,e_ID38-500,e_w615581270-275</t>
-  </si>
-  <si>
-    <t>e_ID2-275,e_w615581270-275</t>
-  </si>
-  <si>
-    <t>e_w1193553154-275,e_w615581242-275,e_w615581232-275</t>
-  </si>
-  <si>
-    <t>e_w614955993-230,e_w544403431-230</t>
-  </si>
-  <si>
-    <t>e_ID34-500,e_ID38-500</t>
-  </si>
-  <si>
-    <t>e_w615581270-275,e_w615581242-275,e_w1193553154-275</t>
-  </si>
-  <si>
-    <t>e_w615581232-275,e_w544403426-230,e_w614955993-230</t>
-  </si>
-  <si>
-    <t>e_w544403426-230,e_w614955993-230,e_w544403431-230,e_w759130125-230</t>
-  </si>
-  <si>
-    <t>e_w469888049-275,e_w721674155-275,e_ID6-275,e_ID5-275,e_ID3-275,e_w939542521-275,e_w928928133-275</t>
-  </si>
-  <si>
-    <t>e_w721674155-275,e_w469888049-275,e_ID6-275</t>
-  </si>
-  <si>
-    <t>e_w615581242-275,e_w1193553154-275,e_w615581232-275</t>
-  </si>
-  <si>
-    <t>e_w614955993-230,e_w544403431-230,e_w544403426-230</t>
-  </si>
-  <si>
-    <t>e_w544403426-230,e_ID9-230,e_w759130125-230</t>
-  </si>
-  <si>
-    <t>e_w615581232-275</t>
-  </si>
-  <si>
-    <t>e_w340205049-275,e_w754073846-275,e_w310958602-275,e_w754096394-275,e_w721674155-275</t>
-  </si>
-  <si>
-    <t>e_ID6-275,e_w939542521-275,e_w841499143-275,e_w1312287191-275</t>
-  </si>
-  <si>
-    <t>e_w469888049-275,e_w721674155-275,e_w754178666-275,e_ID3-275,e_w310695690-275,e_w736595653-275</t>
-  </si>
-  <si>
-    <t>e_w841499143-275,e_w528189342-275,e_w931931133-275,e_w527900241-275,e_w946191122-275</t>
-  </si>
-  <si>
-    <t>e_w610198177-275,e_w753733608-275,e_w931931121-275,e_ID13-500,e_w1013653012-500,e_w562061281-275</t>
-  </si>
-  <si>
-    <t>e_w759130125-230,e_ID9-230</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
+    <t>e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN,e_w398909640-500_IDN,e_w340978681-500_IDN,e_ID35-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID34-500_IDN,e_ID38-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w610198177-275_IDN,e_w753733608-275_IDN,e_w931931121-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1193553154-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_ID9-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w1316876158-275_IDN,e_w161965853-500_IDN,e_w169444592-500_IDN,e_ID10-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_w966209515-500_IDN,e_ID15-500_IDN,e_w960747936-500_IDN,e_w960747902-500_IDN,e_w314452486-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_w629512849-500_IDN,e_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_w614955993-230_IDN,e_w1193553154-275_IDN,e_w544403431-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN,e_w615581270-275_IDN,e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w721685825-275_IDN,e_w754073846-275_IDN,e_w340205049-275_IDN,e_w310695690-275_IDN,e_w754096394-275_IDN,e_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID6-275_IDN,e_w939542521-275_IDN,e_w841499143-275_IDN,e_w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_w754178666-275_IDN,e_ID3-275_IDN,e_w310695690-275_IDN,e_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN,e_w1316786278-275_IDN,e_w931931121-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w943539373-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w721674155-275_IDN,e_w469888049-275_IDN,e_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w930719092-275_IDN,e_w841499143-275_IDN,e_w1186182648-500_IDN,e_w943539373-275_IDN,e_w753733608-275_IDN,e_w946191122-275_IDN,e_w610198177-275_IDN,e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_w166633831-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN,e_w528189342-275_IDN,e_w931931133-275_IDN,e_w527900241-275_IDN,e_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w340205049-275_IDN,e_w754073846-275_IDN,e_w310958602-275_IDN,e_w754096394-275_IDN,e_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-500_IDN,e_w562061281-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN,e_w544403426-230_IDN,e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-275_IDN,e_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_ID6-275_IDN,e_ID5-275_IDN,e_ID3-275_IDN,e_w939542521-275_IDN,e_w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID33-500_IDN,e_w264550744-500_IDN,e_w769617021-500_IDN,e_w314452486-500_IDN,e_ID29-500_IDN,e_w267626657-500_IDN,e_ID31-500_IDN,e_w166633831-500_IDN,e_w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID34-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_w1193553154-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID1-275_IDN,e_w721674155-275_IDN,e_w340205049-275_IDN,e_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN,e_w1312287191-275_IDN,e_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN,e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_ID27-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w939542521-275_IDN,e_ID4-275_IDN,e_ID3-275_IDN,e_ID7-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN,e_ID1-275_IDN,e_w721685825-275_IDN,e_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_w562061281-275_IDN,e_ID27-500_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403431-230_IDN,e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w759130125-230_IDN,e_ID9-230_IDN</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_029</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
+    <t>distr_wonelc_won_IDN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
+    <t>distr_wonelc_won_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_033</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
+    <t>distr_wonelc_won_IDN_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_027</t>
+    <t>distr_wonelc_won_IDN_027</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wonelc_won_021</t>
+    <t>distr_wonelc_won_IDN_021</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_ID28-500,e_ID34-500,e_ID38-500,e_w615581270-275</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w544403426-230,e_w614955993-230</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_ID38-500,e_ID34-500,e_w615581270-275</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w943539373-275,e_w943539373-500,e_w753733608-275,e_w610198177-275</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w562061281-275</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w544403431-230</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_w161965853-500,e_w169444592-500,e_w161960924-500,e_w604684007-500,e_w264550744-500,e_ID33-500,e_ID38-500</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_w340978681-500,e_ID38-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w736595653-500,e_w943539373-275,e_w1186182648-500,e_w943539373-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_w1316876158-275,e_w161965853-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w931931133-275,e_w528189342-275,e_w1316876158-275</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_w314452486-500,e_w629512849-500,e_ID37-500,e_w1308433899-500,e_ID36-500,e_w265318414-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w960747902-500,e_ID23-500,e_w1013653012-500,e_ID29-500,e_ID28-500,e_ID27-500,e_w398909640-500,e_ID34-500,e_ID38-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_ID28-500,e_ID27-500,e_ID34-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w615581270-275,e_w615581242-275,e_w615581232-275,e_w1193553154-275</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w841499143-275,e_w528189342-275</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w931931121-275,e_w610198177-275,e_ID13-500,e_w1013653012-500,e_w562061281-275</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
+    <t>elc_won_IDN_028</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_020</t>
+  </si>
+  <si>
+    <t>e_w544403431-230_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_005</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_001</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_002</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_012</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_009</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_016</t>
+  </si>
+  <si>
+    <t>e_w931931121-275_IDN,e_w610198177-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_036</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_ID33-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_011</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_025</t>
+  </si>
+  <si>
+    <t>e_w960747902-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_ID29-500_IDN,e_ID28-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_019</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN,e_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_007</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_030</t>
+  </si>
+  <si>
+    <t>e_w340978681-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_004</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_010</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_014</t>
+  </si>
+  <si>
+    <t>e_w943539373-275_IDN,e_w943539373-500_IDN,e_w753733608-275_IDN,e_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_035</t>
+  </si>
+  <si>
+    <t>e_w1316876158-275_IDN,e_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_003</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_015</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_029</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_017</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_018</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_034</t>
+  </si>
+  <si>
+    <t>e_w314452486-500_IDN,e_w629512849-500_IDN,e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_023</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN,e_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_024</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN,e_w528189342-275_IDN,e_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_032</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_ID27-500_IDN,e_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_031</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_026</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_022</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_013</t>
+  </si>
+  <si>
+    <t>e_w736595653-500_IDN,e_w943539373-275_IDN,e_w1186182648-500_IDN,e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_008</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_033</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_006</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_027</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_021</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_020</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
+    <t>distr_wofelc_wof_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_ID38-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w314452486-500,e_w629512849-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_033</t>
-  </si>
-  <si>
-    <t>e_w528189342-275,e_w931931133-275</t>
-  </si>
-  <si>
-    <t>elc_wof_034</t>
-  </si>
-  <si>
-    <t>e_w931931133-275,e_w1316876158-275</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_ID37-500,e_ID36-500,e_w265318414-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_w928220391-275</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_035</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_032</t>
-  </si>
-  <si>
-    <t>e_w161965853-500,e_w169444592-500,e_w264550744-500,e_w161960924-500,e_ID33-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_w928220391-275,e_w721685825-275</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_ID27-500,e_ID34-500</t>
-  </si>
-  <si>
-    <t>e_won_001</t>
+    <t>elc_wof_IDN_028</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_009</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_030</t>
+  </si>
+  <si>
+    <t>e_ID37-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_011</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_018</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_013</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_032</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w264550744-500_IDN,e_w161960924-500_IDN,e_ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_031</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_025</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_026</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_027</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN,e_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_035</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_034</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_023</t>
+  </si>
+  <si>
+    <t>e_ID27-500_IDN,e_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_033</t>
+  </si>
+  <si>
+    <t>e_w528189342-275_IDN,e_w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_016</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_029</t>
+  </si>
+  <si>
+    <t>e_w314452486-500_IDN,e_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_017</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_010</t>
+  </si>
+  <si>
+    <t>e_won_IDN_001</t>
   </si>
   <si>
     <t>wind resource in cluster 1</t>
   </si>
   <si>
-    <t>e_won_002</t>
+    <t>e_won_IDN_002</t>
   </si>
   <si>
     <t>wind resource in cluster 2</t>
   </si>
   <si>
-    <t>e_won_003</t>
+    <t>e_won_IDN_003</t>
   </si>
   <si>
     <t>wind resource in cluster 3</t>
   </si>
   <si>
-    <t>e_won_004</t>
+    <t>e_won_IDN_004</t>
   </si>
   <si>
     <t>wind resource in cluster 4</t>
   </si>
   <si>
-    <t>e_won_005</t>
+    <t>e_won_IDN_005</t>
   </si>
   <si>
     <t>wind resource in cluster 5</t>
   </si>
   <si>
-    <t>e_won_006</t>
+    <t>e_won_IDN_006</t>
   </si>
   <si>
     <t>wind resource in cluster 6</t>
   </si>
   <si>
-    <t>e_won_007</t>
+    <t>e_won_IDN_007</t>
   </si>
   <si>
     <t>wind resource in cluster 7</t>
   </si>
   <si>
-    <t>e_won_008</t>
+    <t>e_won_IDN_008</t>
   </si>
   <si>
     <t>wind resource in cluster 8</t>
   </si>
   <si>
-    <t>e_won_009</t>
+    <t>e_won_IDN_009</t>
   </si>
   <si>
     <t>wind resource in cluster 9</t>
   </si>
   <si>
-    <t>e_won_010</t>
+    <t>e_won_IDN_010</t>
   </si>
   <si>
     <t>wind resource in cluster 10</t>
   </si>
   <si>
-    <t>e_won_011</t>
+    <t>e_won_IDN_011</t>
   </si>
   <si>
     <t>wind resource in cluster 11</t>
   </si>
   <si>
-    <t>e_won_012</t>
+    <t>e_won_IDN_012</t>
   </si>
   <si>
     <t>wind resource in cluster 12</t>
   </si>
   <si>
-    <t>e_won_013</t>
+    <t>e_won_IDN_013</t>
   </si>
   <si>
     <t>wind resource in cluster 13</t>
   </si>
   <si>
-    <t>e_won_014</t>
+    <t>e_won_IDN_014</t>
   </si>
   <si>
     <t>wind resource in cluster 14</t>
   </si>
   <si>
-    <t>e_won_015</t>
+    <t>e_won_IDN_015</t>
   </si>
   <si>
     <t>wind resource in cluster 15</t>
   </si>
   <si>
-    <t>e_won_016</t>
+    <t>e_won_IDN_016</t>
   </si>
   <si>
     <t>wind resource in cluster 16</t>
   </si>
   <si>
-    <t>e_won_017</t>
+    <t>e_won_IDN_017</t>
   </si>
   <si>
     <t>wind resource in cluster 17</t>
   </si>
   <si>
-    <t>e_won_018</t>
+    <t>e_won_IDN_018</t>
   </si>
   <si>
     <t>wind resource in cluster 18</t>
   </si>
   <si>
-    <t>e_won_019</t>
+    <t>e_won_IDN_019</t>
   </si>
   <si>
     <t>wind resource in cluster 19</t>
   </si>
   <si>
-    <t>e_won_020</t>
+    <t>e_won_IDN_020</t>
   </si>
   <si>
     <t>wind resource in cluster 20</t>
   </si>
   <si>
-    <t>e_won_021</t>
+    <t>e_won_IDN_021</t>
   </si>
   <si>
     <t>wind resource in cluster 21</t>
   </si>
   <si>
-    <t>e_won_022</t>
+    <t>e_won_IDN_022</t>
   </si>
   <si>
     <t>wind resource in cluster 22</t>
   </si>
   <si>
-    <t>e_won_023</t>
+    <t>e_won_IDN_023</t>
   </si>
   <si>
     <t>wind resource in cluster 23</t>
   </si>
   <si>
-    <t>e_won_024</t>
+    <t>e_won_IDN_024</t>
   </si>
   <si>
     <t>wind resource in cluster 24</t>
   </si>
   <si>
-    <t>e_won_025</t>
+    <t>e_won_IDN_025</t>
   </si>
   <si>
     <t>wind resource in cluster 25</t>
   </si>
   <si>
-    <t>e_won_026</t>
+    <t>e_won_IDN_026</t>
   </si>
   <si>
     <t>wind resource in cluster 26</t>
   </si>
   <si>
-    <t>e_won_027</t>
+    <t>e_won_IDN_027</t>
   </si>
   <si>
     <t>wind resource in cluster 27</t>
   </si>
   <si>
-    <t>e_won_028</t>
+    <t>e_won_IDN_028</t>
   </si>
   <si>
     <t>wind resource in cluster 28</t>
   </si>
   <si>
-    <t>e_won_029</t>
+    <t>e_won_IDN_029</t>
   </si>
   <si>
     <t>wind resource in cluster 29</t>
   </si>
   <si>
-    <t>e_won_030</t>
+    <t>e_won_IDN_030</t>
   </si>
   <si>
     <t>wind resource in cluster 30</t>
   </si>
   <si>
-    <t>e_won_031</t>
+    <t>e_won_IDN_031</t>
   </si>
   <si>
     <t>wind resource in cluster 31</t>
   </si>
   <si>
-    <t>e_won_032</t>
+    <t>e_won_IDN_032</t>
   </si>
   <si>
     <t>wind resource in cluster 32</t>
   </si>
   <si>
-    <t>e_won_033</t>
+    <t>e_won_IDN_033</t>
   </si>
   <si>
     <t>wind resource in cluster 33</t>
   </si>
   <si>
-    <t>e_won_034</t>
+    <t>e_won_IDN_034</t>
   </si>
   <si>
     <t>wind resource in cluster 34</t>
   </si>
   <si>
-    <t>e_won_035</t>
+    <t>e_won_IDN_035</t>
   </si>
   <si>
     <t>wind resource in cluster 35</t>
   </si>
   <si>
-    <t>e_won_036</t>
+    <t>e_won_IDN_036</t>
   </si>
   <si>
     <t>wind resource in cluster 36</t>
   </si>
   <si>
-    <t>e_wof_001</t>
+    <t>e_wof_IDN_001</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 1</t>
   </si>
   <si>
-    <t>e_wof_002</t>
+    <t>e_wof_IDN_002</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 2</t>
   </si>
   <si>
-    <t>e_wof_003</t>
+    <t>e_wof_IDN_003</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 3</t>
   </si>
   <si>
-    <t>e_wof_004</t>
+    <t>e_wof_IDN_004</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 4</t>
   </si>
   <si>
-    <t>e_wof_005</t>
+    <t>e_wof_IDN_005</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 5</t>
   </si>
   <si>
-    <t>e_wof_006</t>
+    <t>e_wof_IDN_006</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 6</t>
   </si>
   <si>
-    <t>e_wof_007</t>
+    <t>e_wof_IDN_007</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 7</t>
   </si>
   <si>
-    <t>e_wof_008</t>
+    <t>e_wof_IDN_008</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 8</t>
   </si>
   <si>
-    <t>e_wof_009</t>
+    <t>e_wof_IDN_009</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 9</t>
   </si>
   <si>
-    <t>e_wof_010</t>
+    <t>e_wof_IDN_010</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 10</t>
   </si>
   <si>
-    <t>e_wof_011</t>
+    <t>e_wof_IDN_011</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 11</t>
   </si>
   <si>
-    <t>e_wof_012</t>
+    <t>e_wof_IDN_012</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 12</t>
   </si>
   <si>
-    <t>e_wof_013</t>
+    <t>e_wof_IDN_013</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 13</t>
   </si>
   <si>
-    <t>e_wof_014</t>
+    <t>e_wof_IDN_014</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 14</t>
   </si>
   <si>
-    <t>e_wof_015</t>
+    <t>e_wof_IDN_015</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 15</t>
   </si>
   <si>
-    <t>e_wof_016</t>
+    <t>e_wof_IDN_016</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 16</t>
   </si>
   <si>
-    <t>e_wof_017</t>
+    <t>e_wof_IDN_017</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 17</t>
   </si>
   <si>
-    <t>e_wof_018</t>
+    <t>e_wof_IDN_018</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 18</t>
   </si>
   <si>
-    <t>e_wof_019</t>
+    <t>e_wof_IDN_019</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 19</t>
   </si>
   <si>
-    <t>e_wof_020</t>
+    <t>e_wof_IDN_020</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 20</t>
   </si>
   <si>
-    <t>e_wof_021</t>
+    <t>e_wof_IDN_021</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 21</t>
   </si>
   <si>
-    <t>e_wof_022</t>
+    <t>e_wof_IDN_022</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 22</t>
   </si>
   <si>
-    <t>e_wof_023</t>
+    <t>e_wof_IDN_023</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 23</t>
   </si>
   <si>
-    <t>e_wof_024</t>
+    <t>e_wof_IDN_024</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 24</t>
   </si>
   <si>
-    <t>e_wof_025</t>
+    <t>e_wof_IDN_025</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 25</t>
   </si>
   <si>
-    <t>e_wof_026</t>
+    <t>e_wof_IDN_026</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 26</t>
   </si>
   <si>
-    <t>e_wof_027</t>
+    <t>e_wof_IDN_027</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 27</t>
   </si>
   <si>
-    <t>e_wof_028</t>
+    <t>e_wof_IDN_028</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 28</t>
   </si>
   <si>
-    <t>e_wof_029</t>
+    <t>e_wof_IDN_029</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 29</t>
   </si>
   <si>
-    <t>e_wof_030</t>
+    <t>e_wof_IDN_030</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 30</t>
   </si>
   <si>
-    <t>e_wof_031</t>
+    <t>e_wof_IDN_031</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 31</t>
   </si>
   <si>
-    <t>e_wof_032</t>
+    <t>e_wof_IDN_032</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 32</t>
   </si>
   <si>
-    <t>e_wof_033</t>
+    <t>e_wof_IDN_033</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 33</t>
   </si>
   <si>
-    <t>e_wof_034</t>
+    <t>e_wof_IDN_034</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 34</t>
   </si>
   <si>
-    <t>e_wof_035</t>
+    <t>e_wof_IDN_035</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 35</t>
@@ -3166,28 +3166,28 @@
     <t>yes</t>
   </si>
   <si>
-    <t>stepdown_w736595653_500to275</t>
-  </si>
-  <si>
-    <t>e_w736595653-500</t>
-  </si>
-  <si>
-    <t>e_w736595653-275</t>
-  </si>
-  <si>
-    <t>stepup_w736595653_275to500</t>
-  </si>
-  <si>
-    <t>stepdown_w943539373_500to275</t>
-  </si>
-  <si>
-    <t>e_w943539373-500</t>
-  </si>
-  <si>
-    <t>e_w943539373-275</t>
-  </si>
-  <si>
-    <t>stepup_w943539373_275to500</t>
+    <t>stepdown_w736595653_IDN_500to275</t>
+  </si>
+  <si>
+    <t>e_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>stepup_w736595653_IDN_275to500</t>
+  </si>
+  <si>
+    <t>stepdown_w943539373_IDN_500to275</t>
+  </si>
+  <si>
+    <t>e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w943539373-275_IDN</t>
+  </si>
+  <si>
+    <t>stepup_w943539373_IDN_275to500</t>
   </si>
   <si>
     <t>activityunit</t>
@@ -3196,19 +3196,19 @@
     <t>capacityunit</t>
   </si>
   <si>
-    <t>Transformer: e_w736595653-500 → e_w736595653-275</t>
-  </si>
-  <si>
-    <t>Transformer: e_w736595653-275 → e_w736595653-500</t>
-  </si>
-  <si>
-    <t>Transformer: e_w943539373-500 → e_w943539373-275</t>
-  </si>
-  <si>
-    <t>Transformer: e_w943539373-275 → e_w943539373-500</t>
-  </si>
-  <si>
-    <t>e_ID1-275,e_ID10-500,e_ID11-500,e_ID12-500,e_ID13-500,e_ID14-500,e_ID15-500,e_ID16-500,e_ID17-500,e_ID19-500,e_ID20-500,e_ID23-500,e_ID27-500,e_ID28-500,e_ID29-500,e_ID30-500,e_ID31-500,e_ID34-500,e_ID35-500,e_ID37-500,e_ID38-500,e_w1013653012-500,e_w159940153-500,e_w161965853-500,e_w337039411-275,e_w340978681-500,e_w544403426-230,e_w615581232-275,e_w615581270-275,e_w629512849-500,e_w662591948-500,e_w689263666-500,e_w721685825-275,e_w754073846-275,e_w928220391-275</t>
+    <t>Transformer: e_w736595653-500_IDN → e_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w736595653-275_IDN → e_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w943539373-500_IDN → e_w943539373-275_IDN</t>
+  </si>
+  <si>
+    <t>Transformer: e_w943539373-275_IDN → e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID1-275_IDN,e_ID10-500_IDN,e_ID11-500_IDN,e_ID12-500_IDN,e_ID13-500_IDN,e_ID14-500_IDN,e_ID15-500_IDN,e_ID16-500_IDN,e_ID17-500_IDN,e_ID19-500_IDN,e_ID20-500_IDN,e_ID23-500_IDN,e_ID27-500_IDN,e_ID28-500_IDN,e_ID29-500_IDN,e_ID30-500_IDN,e_ID31-500_IDN,e_ID34-500_IDN,e_ID35-500_IDN,e_ID37-500_IDN,e_ID38-500_IDN,e_w1013653012-500_IDN,e_w159940153-500_IDN,e_w161965853-500_IDN,e_w337039411-275_IDN,e_w340978681-500_IDN,e_w544403426-230_IDN,e_w615581232-275_IDN,e_w615581270-275_IDN,e_w629512849-500_IDN,e_w662591948-500_IDN,e_w689263666-500_IDN,e_w721685825-275_IDN,e_w754073846-275_IDN,e_w928220391-275_IDN</t>
   </si>
 </sst>
 </file>
@@ -4162,6 +4162,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -5102,7 +5105,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_ID1-275,e_ID10-500,e_ID11-500,e_ID12-500,e_ID13-500,e_ID14-500,e_ID15-500,e_ID16-500,e_ID17-500,e_ID19-500,e_ID20-500,e_ID23-500,e_ID27-500,e_ID28-500,e_ID29-500,e_ID30-500,e_ID31-500,e_ID34-500,e_ID35-500,e_ID37-500,e_ID38-500,e_w1013653012-500,e_w159940153-500,e_w161965853-500,e_w337039411-275,e_w340978681-500,e_w544403426-230,e_w615581232-275,e_w615581270-275,e_w629512849-500,e_w662591948-500,e_w689263666-500,e_w721685825-275,e_w754073846-275,e_w928220391-275</v>
+        <v>e_ID1-275_IDN,e_ID10-500_IDN,e_ID11-500_IDN,e_ID12-500_IDN,e_ID13-500_IDN,e_ID14-500_IDN,e_ID15-500_IDN,e_ID16-500_IDN,e_ID17-500_IDN,e_ID19-500_IDN,e_ID20-500_IDN,e_ID23-500_IDN,e_ID27-500_IDN,e_ID28-500_IDN,e_ID29-500_IDN,e_ID30-500_IDN,e_ID31-500_IDN,e_ID34-500_IDN,e_ID35-500_IDN,e_ID37-500_IDN,e_ID38-500_IDN,e_w1013653012-500_IDN,e_w159940153-500_IDN,e_w161965853-500_IDN,e_w337039411-275_IDN,e_w340978681-500_IDN,e_w544403426-230_IDN,e_w615581232-275_IDN,e_w615581270-275_IDN,e_w629512849-500_IDN,e_w662591948-500_IDN,e_w689263666-500_IDN,e_w721685825-275_IDN,e_w754073846-275_IDN,e_w928220391-275_IDN</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5124,7 +5127,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_ID1-275,e_ID10-500,e_ID11-500,e_ID12-500,e_ID13-500,e_ID14-500,e_ID15-500,e_ID16-500,e_ID17-500,e_ID19-500,e_ID20-500,e_ID23-500,e_ID27-500,e_ID28-500,e_ID29-500,e_ID30-500,e_ID31-500,e_ID34-500,e_ID35-500,e_ID37-500,e_ID38-500,e_w1013653012-500,e_w159940153-500,e_w161965853-500,e_w337039411-275,e_w340978681-500,e_w544403426-230,e_w615581232-275,e_w615581270-275,e_w629512849-500,e_w662591948-500,e_w689263666-500,e_w721685825-275,e_w754073846-275,e_w928220391-275</v>
+        <v>e_ID1-275_IDN,e_ID10-500_IDN,e_ID11-500_IDN,e_ID12-500_IDN,e_ID13-500_IDN,e_ID14-500_IDN,e_ID15-500_IDN,e_ID16-500_IDN,e_ID17-500_IDN,e_ID19-500_IDN,e_ID20-500_IDN,e_ID23-500_IDN,e_ID27-500_IDN,e_ID28-500_IDN,e_ID29-500_IDN,e_ID30-500_IDN,e_ID31-500_IDN,e_ID34-500_IDN,e_ID35-500_IDN,e_ID37-500_IDN,e_ID38-500_IDN,e_w1013653012-500_IDN,e_w159940153-500_IDN,e_w161965853-500_IDN,e_w337039411-275_IDN,e_w340978681-500_IDN,e_w544403426-230_IDN,e_w615581232-275_IDN,e_w615581270-275_IDN,e_w629512849-500_IDN,e_w662591948-500_IDN,e_w689263666-500_IDN,e_w721685825-275_IDN,e_w754073846-275_IDN,e_w928220391-275_IDN</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -7940,7 +7943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDF9921-2107-45C6-85B6-6F9D13161A6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAABC3E-5BE9-4145-AA65-2070262E2622}">
   <dimension ref="B9:BD84"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8178,16 +8181,16 @@
         <v>403</v>
       </c>
       <c r="Y11" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Z11" t="s">
         <v>555</v>
       </c>
       <c r="AA11">
-        <v>0.99770753964756576</v>
+        <v>0.99720517126173747</v>
       </c>
       <c r="AB11">
-        <v>42.028439794628142</v>
+        <v>51.238526868146437</v>
       </c>
       <c r="AD11" t="s">
         <v>402</v>
@@ -8217,13 +8220,13 @@
         <v>680</v>
       </c>
       <c r="AN11" t="s">
-        <v>681</v>
+        <v>578</v>
       </c>
       <c r="AO11">
-        <v>0.98895557240687315</v>
+        <v>0.96732413990250377</v>
       </c>
       <c r="AP11">
-        <v>202.48117254065832</v>
+        <v>599.05743512076492</v>
       </c>
       <c r="AR11" t="s">
         <v>402</v>
@@ -8253,13 +8256,13 @@
         <v>803</v>
       </c>
       <c r="BB11" t="s">
-        <v>579</v>
+        <v>804</v>
       </c>
       <c r="BC11">
-        <v>0.96620229207214314</v>
+        <v>0.98373391026642343</v>
       </c>
       <c r="BD11">
-        <v>619.62464534404216</v>
+        <v>298.21164511556987</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8324,16 +8327,16 @@
         <v>407</v>
       </c>
       <c r="Y12" t="s">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="Z12" t="s">
         <v>556</v>
       </c>
       <c r="AA12">
-        <v>0.99808394057461192</v>
+        <v>0.98421229582412162</v>
       </c>
       <c r="AB12">
-        <v>35.127756132114413</v>
+        <v>289.44124322443668</v>
       </c>
       <c r="AD12" t="s">
         <v>402</v>
@@ -8360,16 +8363,16 @@
         <v>610</v>
       </c>
       <c r="AM12" t="s">
+        <v>681</v>
+      </c>
+      <c r="AN12" t="s">
         <v>682</v>
       </c>
-      <c r="AN12" t="s">
-        <v>559</v>
-      </c>
       <c r="AO12">
-        <v>0.97755933784246885</v>
+        <v>0.97419216130718622</v>
       </c>
       <c r="AP12">
-        <v>411.4121395547387</v>
+        <v>473.14370936825355</v>
       </c>
       <c r="AR12" t="s">
         <v>402</v>
@@ -8396,10 +8399,10 @@
         <v>735</v>
       </c>
       <c r="BA12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="BB12" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="BC12">
         <v>0.98908976773019719</v>
@@ -8470,16 +8473,16 @@
         <v>409</v>
       </c>
       <c r="Y13" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="Z13" t="s">
         <v>557</v>
       </c>
       <c r="AA13">
-        <v>0.99720517126173747</v>
+        <v>0.97067956893851193</v>
       </c>
       <c r="AB13">
-        <v>51.238526868146437</v>
+        <v>537.54123612728188</v>
       </c>
       <c r="AD13" t="s">
         <v>402</v>
@@ -8509,13 +8512,13 @@
         <v>683</v>
       </c>
       <c r="AN13" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AO13">
-        <v>0.94698201881115829</v>
+        <v>0.9784298046188693</v>
       </c>
       <c r="AP13">
-        <v>971.99632179543119</v>
+        <v>395.45358198739586</v>
       </c>
       <c r="AR13" t="s">
         <v>402</v>
@@ -8542,7 +8545,7 @@
         <v>737</v>
       </c>
       <c r="BA13" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="BB13" t="s">
         <v>578</v>
@@ -8616,16 +8619,16 @@
         <v>411</v>
       </c>
       <c r="Y14" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Z14" t="s">
         <v>558</v>
       </c>
       <c r="AA14">
-        <v>0.95854557991594525</v>
+        <v>0.98091465074522166</v>
       </c>
       <c r="AB14">
-        <v>759.99770154100372</v>
+        <v>349.89806967093693</v>
       </c>
       <c r="AD14" t="s">
         <v>402</v>
@@ -8655,13 +8658,13 @@
         <v>684</v>
       </c>
       <c r="AN14" t="s">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="AO14">
-        <v>0.9784298046188693</v>
+        <v>0.9519359532349716</v>
       </c>
       <c r="AP14">
-        <v>395.45358198739586</v>
+        <v>881.17419069218636</v>
       </c>
       <c r="AR14" t="s">
         <v>402</v>
@@ -8688,16 +8691,16 @@
         <v>739</v>
       </c>
       <c r="BA14" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="BB14" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="BC14">
-        <v>0.96625736872930745</v>
+        <v>0.97829546850421678</v>
       </c>
       <c r="BD14">
-        <v>618.61490662936239</v>
+        <v>397.91641075602604</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8762,16 +8765,16 @@
         <v>413</v>
       </c>
       <c r="Y15" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="Z15" t="s">
         <v>559</v>
       </c>
       <c r="AA15">
-        <v>0.94713503807708188</v>
+        <v>0.97678876819750537</v>
       </c>
       <c r="AB15">
-        <v>969.19096858683281</v>
+        <v>425.5392497124015</v>
       </c>
       <c r="AD15" t="s">
         <v>402</v>
@@ -8801,13 +8804,13 @@
         <v>685</v>
       </c>
       <c r="AN15" t="s">
-        <v>601</v>
+        <v>686</v>
       </c>
       <c r="AO15">
-        <v>0.95419187641353731</v>
+        <v>0.96896908104036528</v>
       </c>
       <c r="AP15">
-        <v>839.81559908514964</v>
+        <v>568.90018092663558</v>
       </c>
       <c r="AR15" t="s">
         <v>402</v>
@@ -8834,16 +8837,16 @@
         <v>741</v>
       </c>
       <c r="BA15" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BB15" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="BC15">
-        <v>0.94041102627936679</v>
+        <v>0.94478739551790969</v>
       </c>
       <c r="BD15">
-        <v>1092.4645182116094</v>
+        <v>1012.2310821716558</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8908,16 +8911,16 @@
         <v>415</v>
       </c>
       <c r="Y16" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="Z16" t="s">
         <v>560</v>
       </c>
       <c r="AA16">
-        <v>0.99660643716165165</v>
+        <v>0.98696950091677516</v>
       </c>
       <c r="AB16">
-        <v>62.215318703052311</v>
+        <v>238.89248319245524</v>
       </c>
       <c r="AD16" t="s">
         <v>402</v>
@@ -8944,16 +8947,16 @@
         <v>618</v>
       </c>
       <c r="AM16" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN16" t="s">
-        <v>687</v>
+        <v>586</v>
       </c>
       <c r="AO16">
-        <v>0.96896908104036528</v>
+        <v>0.97444089635831932</v>
       </c>
       <c r="AP16">
-        <v>568.90018092663558</v>
+        <v>468.58356676414513</v>
       </c>
       <c r="AR16" t="s">
         <v>402</v>
@@ -8980,16 +8983,16 @@
         <v>743</v>
       </c>
       <c r="BA16" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="BB16" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="BC16">
-        <v>0.96587851707660599</v>
+        <v>0.94491770107559214</v>
       </c>
       <c r="BD16">
-        <v>625.56052026222312</v>
+        <v>1009.8421469474777</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9054,16 +9057,16 @@
         <v>417</v>
       </c>
       <c r="Y17" t="s">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="Z17" t="s">
         <v>561</v>
       </c>
       <c r="AA17">
-        <v>0.99624827768323054</v>
+        <v>0.98568311514415174</v>
       </c>
       <c r="AB17">
-        <v>68.781575807440518</v>
+        <v>262.47622235721866</v>
       </c>
       <c r="AD17" t="s">
         <v>402</v>
@@ -9093,13 +9096,13 @@
         <v>688</v>
       </c>
       <c r="AN17" t="s">
-        <v>689</v>
+        <v>570</v>
       </c>
       <c r="AO17">
-        <v>0.97915231383494816</v>
+        <v>0.97186368651165222</v>
       </c>
       <c r="AP17">
-        <v>382.20757969261723</v>
+        <v>515.83241395304219</v>
       </c>
       <c r="AR17" t="s">
         <v>402</v>
@@ -9126,16 +9129,16 @@
         <v>745</v>
       </c>
       <c r="BA17" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="BB17" t="s">
-        <v>810</v>
+        <v>570</v>
       </c>
       <c r="BC17">
-        <v>0.98373391026642343</v>
+        <v>0.96951273706693553</v>
       </c>
       <c r="BD17">
-        <v>298.21164511556987</v>
+        <v>558.93315377284773</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9200,16 +9203,16 @@
         <v>419</v>
       </c>
       <c r="Y18" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="Z18" t="s">
         <v>562</v>
       </c>
       <c r="AA18">
-        <v>0.98654011406382824</v>
+        <v>0.99640865233383846</v>
       </c>
       <c r="AB18">
-        <v>246.76457549648219</v>
+        <v>65.841373879627454</v>
       </c>
       <c r="AD18" t="s">
         <v>402</v>
@@ -9236,16 +9239,16 @@
         <v>622</v>
       </c>
       <c r="AM18" t="s">
+        <v>689</v>
+      </c>
+      <c r="AN18" t="s">
         <v>690</v>
       </c>
-      <c r="AN18" t="s">
-        <v>691</v>
-      </c>
       <c r="AO18">
-        <v>0.98921594161489768</v>
+        <v>0.98243109777744309</v>
       </c>
       <c r="AP18">
-        <v>197.70773706020898</v>
+        <v>322.09654074687614</v>
       </c>
       <c r="AR18" t="s">
         <v>402</v>
@@ -9275,13 +9278,13 @@
         <v>811</v>
       </c>
       <c r="BB18" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="BC18">
-        <v>0.97600654740978099</v>
+        <v>0.97175571177973974</v>
       </c>
       <c r="BD18">
-        <v>439.8799641540142</v>
+        <v>517.81195070477202</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9346,16 +9349,16 @@
         <v>421</v>
       </c>
       <c r="Y19" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="Z19" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AA19">
-        <v>0.97592802238295073</v>
+        <v>0.95152672202699851</v>
       </c>
       <c r="AB19">
-        <v>441.3195896459041</v>
+        <v>888.67676283836079</v>
       </c>
       <c r="AD19" t="s">
         <v>402</v>
@@ -9382,16 +9385,16 @@
         <v>624</v>
       </c>
       <c r="AM19" t="s">
+        <v>691</v>
+      </c>
+      <c r="AN19" t="s">
         <v>692</v>
       </c>
-      <c r="AN19" t="s">
-        <v>582</v>
-      </c>
       <c r="AO19">
-        <v>0.97444089635831932</v>
+        <v>0.9936518770554722</v>
       </c>
       <c r="AP19">
-        <v>468.58356676414513</v>
+        <v>116.38225398301061</v>
       </c>
       <c r="AR19" t="s">
         <v>402</v>
@@ -9421,13 +9424,13 @@
         <v>812</v>
       </c>
       <c r="BB19" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="BC19">
-        <v>0.96834660314974419</v>
+        <v>0.97045263692858041</v>
       </c>
       <c r="BD19">
-        <v>580.31227558802345</v>
+        <v>541.7016563093581</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9492,16 +9495,16 @@
         <v>423</v>
       </c>
       <c r="Y20" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="Z20" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AA20">
-        <v>0.96781787899545535</v>
+        <v>0.99439318395533605</v>
       </c>
       <c r="AB20">
-        <v>590.00555174998567</v>
+        <v>102.7916274855054</v>
       </c>
       <c r="AD20" t="s">
         <v>402</v>
@@ -9531,13 +9534,13 @@
         <v>693</v>
       </c>
       <c r="AN20" t="s">
-        <v>575</v>
+        <v>694</v>
       </c>
       <c r="AO20">
-        <v>0.97739363651485267</v>
+        <v>0.9880111771283725</v>
       </c>
       <c r="AP20">
-        <v>414.44999722770137</v>
+        <v>219.79508597983738</v>
       </c>
       <c r="AR20" t="s">
         <v>402</v>
@@ -9567,13 +9570,13 @@
         <v>813</v>
       </c>
       <c r="BB20" t="s">
-        <v>814</v>
+        <v>578</v>
       </c>
       <c r="BC20">
-        <v>0.99556358538362921</v>
+        <v>0.97600654740978099</v>
       </c>
       <c r="BD20">
-        <v>81.334267966797512</v>
+        <v>439.8799641540142</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9638,16 +9641,16 @@
         <v>425</v>
       </c>
       <c r="Y21" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Z21" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AA21">
-        <v>0.98451878015346617</v>
+        <v>0.99770573728283862</v>
       </c>
       <c r="AB21">
-        <v>283.82236385312052</v>
+        <v>42.061483147959365</v>
       </c>
       <c r="AD21" t="s">
         <v>402</v>
@@ -9674,16 +9677,16 @@
         <v>628</v>
       </c>
       <c r="AM21" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AN21" t="s">
-        <v>584</v>
+        <v>696</v>
       </c>
       <c r="AO21">
-        <v>0.95111092756566806</v>
+        <v>0.99700964975406792</v>
       </c>
       <c r="AP21">
-        <v>896.29966129608511</v>
+        <v>54.823087842088889</v>
       </c>
       <c r="AR21" t="s">
         <v>402</v>
@@ -9710,16 +9713,16 @@
         <v>753</v>
       </c>
       <c r="BA21" t="s">
+        <v>814</v>
+      </c>
+      <c r="BB21" t="s">
         <v>815</v>
       </c>
-      <c r="BB21" t="s">
-        <v>601</v>
-      </c>
       <c r="BC21">
-        <v>0.95614590843046721</v>
+        <v>0.99036076428701636</v>
       </c>
       <c r="BD21">
-        <v>803.99167877476805</v>
+        <v>176.71932140470005</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9784,16 +9787,16 @@
         <v>427</v>
       </c>
       <c r="Y22" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="Z22" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="AA22">
-        <v>0.98223116847554315</v>
+        <v>0.99118992399256634</v>
       </c>
       <c r="AB22">
-        <v>325.76191128170939</v>
+        <v>161.51806013628308</v>
       </c>
       <c r="AD22" t="s">
         <v>402</v>
@@ -9820,16 +9823,16 @@
         <v>630</v>
       </c>
       <c r="AM22" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AN22" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AO22">
-        <v>0.9880111771283725</v>
+        <v>0.98325145592799346</v>
       </c>
       <c r="AP22">
-        <v>219.79508597983738</v>
+        <v>307.05664132012055</v>
       </c>
       <c r="AR22" t="s">
         <v>402</v>
@@ -9859,13 +9862,13 @@
         <v>816</v>
       </c>
       <c r="BB22" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="BC22">
-        <v>0.97045263692858041</v>
+        <v>0.98102590217137298</v>
       </c>
       <c r="BD22">
-        <v>541.7016563093581</v>
+        <v>347.85846019149614</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9930,16 +9933,16 @@
         <v>429</v>
       </c>
       <c r="Y23" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="Z23" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AA23">
-        <v>0.9912986266790621</v>
+        <v>0.9582992451809369</v>
       </c>
       <c r="AB23">
-        <v>159.52517755052818</v>
+        <v>764.51383834949013</v>
       </c>
       <c r="AD23" t="s">
         <v>402</v>
@@ -9966,16 +9969,16 @@
         <v>632</v>
       </c>
       <c r="AM23" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AN23" t="s">
-        <v>698</v>
+        <v>600</v>
       </c>
       <c r="AO23">
-        <v>0.97419216130718622</v>
+        <v>0.95111092756566806</v>
       </c>
       <c r="AP23">
-        <v>473.14370936825355</v>
+        <v>896.29966129608511</v>
       </c>
       <c r="AR23" t="s">
         <v>402</v>
@@ -10005,13 +10008,13 @@
         <v>817</v>
       </c>
       <c r="BB23" t="s">
-        <v>592</v>
+        <v>568</v>
       </c>
       <c r="BC23">
-        <v>0.98584164436602861</v>
+        <v>0.96625736872930745</v>
       </c>
       <c r="BD23">
-        <v>259.56985328947479</v>
+        <v>618.61490662936239</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10076,16 +10079,16 @@
         <v>431</v>
       </c>
       <c r="Y24" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="Z24" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AA24">
-        <v>0.99118992399256634</v>
+        <v>0.95289359663592565</v>
       </c>
       <c r="AB24">
-        <v>161.51806013628308</v>
+        <v>863.61739500803003</v>
       </c>
       <c r="AD24" t="s">
         <v>402</v>
@@ -10112,16 +10115,16 @@
         <v>634</v>
       </c>
       <c r="AM24" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AN24" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AO24">
-        <v>0.9936518770554722</v>
+        <v>0.97532618723790843</v>
       </c>
       <c r="AP24">
-        <v>116.38225398301061</v>
+        <v>452.35323397167849</v>
       </c>
       <c r="AR24" t="s">
         <v>402</v>
@@ -10151,13 +10154,13 @@
         <v>818</v>
       </c>
       <c r="BB24" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="BC24">
-        <v>0.94896692115877124</v>
+        <v>0.93693021635476914</v>
       </c>
       <c r="BD24">
-        <v>935.60644542252658</v>
+        <v>1156.2793668292329</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10222,16 +10225,16 @@
         <v>433</v>
       </c>
       <c r="Y25" t="s">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="Z25" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AA25">
-        <v>0.97496236164466343</v>
+        <v>0.97577723283636553</v>
       </c>
       <c r="AB25">
-        <v>459.02336984783733</v>
+        <v>444.08406466663115</v>
       </c>
       <c r="AD25" t="s">
         <v>402</v>
@@ -10258,16 +10261,16 @@
         <v>636</v>
       </c>
       <c r="AM25" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AN25" t="s">
-        <v>702</v>
+        <v>587</v>
       </c>
       <c r="AO25">
-        <v>0.97532618723790843</v>
+        <v>0.97755933784246885</v>
       </c>
       <c r="AP25">
-        <v>452.35323397167849</v>
+        <v>411.4121395547387</v>
       </c>
       <c r="AR25" t="s">
         <v>402</v>
@@ -10297,13 +10300,13 @@
         <v>819</v>
       </c>
       <c r="BB25" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="BC25">
-        <v>0.95197431053166182</v>
+        <v>0.94041102627936679</v>
       </c>
       <c r="BD25">
-        <v>880.47097358620078</v>
+        <v>1092.4645182116094</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10368,16 +10371,16 @@
         <v>435</v>
       </c>
       <c r="Y26" t="s">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="Z26" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AA26">
-        <v>0.97311512275225454</v>
+        <v>0.98985535554561865</v>
       </c>
       <c r="AB26">
-        <v>492.88941620866609</v>
+        <v>185.9851483303255</v>
       </c>
       <c r="AD26" t="s">
         <v>402</v>
@@ -10407,13 +10410,13 @@
         <v>703</v>
       </c>
       <c r="AN26" t="s">
-        <v>704</v>
+        <v>570</v>
       </c>
       <c r="AO26">
-        <v>0.98226637914287063</v>
+        <v>0.97739363651485267</v>
       </c>
       <c r="AP26">
-        <v>325.11638238070481</v>
+        <v>414.44999722770137</v>
       </c>
       <c r="AR26" t="s">
         <v>402</v>
@@ -10443,13 +10446,13 @@
         <v>820</v>
       </c>
       <c r="BB26" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="BC26">
-        <v>0.96951273706693553</v>
+        <v>0.95063651087703893</v>
       </c>
       <c r="BD26">
-        <v>558.93315377284773</v>
+        <v>904.99730058761952</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10514,16 +10517,16 @@
         <v>437</v>
       </c>
       <c r="Y27" t="s">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="Z27" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="AA27">
-        <v>0.99496216240453639</v>
+        <v>0.96781787899545535</v>
       </c>
       <c r="AB27">
-        <v>92.360355916833001</v>
+        <v>590.00555174998567</v>
       </c>
       <c r="AD27" t="s">
         <v>402</v>
@@ -10550,16 +10553,16 @@
         <v>640</v>
       </c>
       <c r="AM27" t="s">
+        <v>704</v>
+      </c>
+      <c r="AN27" t="s">
         <v>705</v>
       </c>
-      <c r="AN27" t="s">
-        <v>706</v>
-      </c>
       <c r="AO27">
-        <v>0.99552970818146125</v>
+        <v>0.98921594161489768</v>
       </c>
       <c r="AP27">
-        <v>81.955350006543654</v>
+        <v>197.70773706020898</v>
       </c>
       <c r="AR27" t="s">
         <v>402</v>
@@ -10589,13 +10592,13 @@
         <v>821</v>
       </c>
       <c r="BB27" t="s">
-        <v>575</v>
+        <v>822</v>
       </c>
       <c r="BC27">
-        <v>0.9602868544779749</v>
+        <v>0.99286819499076961</v>
       </c>
       <c r="BD27">
-        <v>728.07433457046079</v>
+        <v>130.7497585025562</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10660,16 +10663,16 @@
         <v>439</v>
       </c>
       <c r="Y28" t="s">
-        <v>358</v>
+        <v>399</v>
       </c>
       <c r="Z28" t="s">
         <v>570</v>
       </c>
       <c r="AA28">
-        <v>0.95289359663592565</v>
+        <v>0.97597719784352066</v>
       </c>
       <c r="AB28">
-        <v>863.61739500803003</v>
+        <v>440.41803953545457</v>
       </c>
       <c r="AD28" t="s">
         <v>402</v>
@@ -10696,16 +10699,16 @@
         <v>642</v>
       </c>
       <c r="AM28" t="s">
+        <v>706</v>
+      </c>
+      <c r="AN28" t="s">
         <v>707</v>
       </c>
-      <c r="AN28" t="s">
-        <v>708</v>
-      </c>
       <c r="AO28">
-        <v>0.99101688837209245</v>
+        <v>0.99552970818146125</v>
       </c>
       <c r="AP28">
-        <v>164.69037984497118</v>
+        <v>81.955350006543654</v>
       </c>
       <c r="AR28" t="s">
         <v>402</v>
@@ -10732,16 +10735,16 @@
         <v>767</v>
       </c>
       <c r="BA28" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="BB28" t="s">
-        <v>823</v>
+        <v>576</v>
       </c>
       <c r="BC28">
-        <v>0.98716759869587867</v>
+        <v>0.93888082510661108</v>
       </c>
       <c r="BD28">
-        <v>235.26069057555824</v>
+        <v>1120.5182063787968</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10806,16 +10809,16 @@
         <v>441</v>
       </c>
       <c r="Y29" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="Z29" t="s">
         <v>571</v>
       </c>
       <c r="AA29">
-        <v>0.99017812457307008</v>
+        <v>0.99660643716165165</v>
       </c>
       <c r="AB29">
-        <v>180.06771616038245</v>
+        <v>62.215318703052311</v>
       </c>
       <c r="AD29" t="s">
         <v>402</v>
@@ -10842,16 +10845,16 @@
         <v>644</v>
       </c>
       <c r="AM29" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AN29" t="s">
-        <v>710</v>
+        <v>565</v>
       </c>
       <c r="AO29">
-        <v>0.99557021775830368</v>
+        <v>0.95419187641353731</v>
       </c>
       <c r="AP29">
-        <v>81.21267443109943</v>
+        <v>839.81559908514964</v>
       </c>
       <c r="AR29" t="s">
         <v>402</v>
@@ -10881,13 +10884,13 @@
         <v>824</v>
       </c>
       <c r="BB29" t="s">
-        <v>825</v>
+        <v>594</v>
       </c>
       <c r="BC29">
-        <v>0.98529032090802915</v>
+        <v>0.98584164436602861</v>
       </c>
       <c r="BD29">
-        <v>269.67745001946554</v>
+        <v>259.56985328947479</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10952,16 +10955,16 @@
         <v>443</v>
       </c>
       <c r="Y30" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="Z30" t="s">
         <v>572</v>
       </c>
       <c r="AA30">
-        <v>0.99627301415801128</v>
+        <v>0.98786674666740726</v>
       </c>
       <c r="AB30">
-        <v>68.328073769792198</v>
+        <v>222.44297776420015</v>
       </c>
       <c r="AD30" t="s">
         <v>402</v>
@@ -10988,16 +10991,16 @@
         <v>646</v>
       </c>
       <c r="AM30" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="AN30" t="s">
-        <v>565</v>
+        <v>694</v>
       </c>
       <c r="AO30">
-        <v>0.95686428742271346</v>
+        <v>0.98177850613436324</v>
       </c>
       <c r="AP30">
-        <v>790.82139725025399</v>
+        <v>334.06072087000706</v>
       </c>
       <c r="AR30" t="s">
         <v>402</v>
@@ -11024,16 +11027,16 @@
         <v>771</v>
       </c>
       <c r="BA30" t="s">
+        <v>825</v>
+      </c>
+      <c r="BB30" t="s">
         <v>826</v>
       </c>
-      <c r="BB30" t="s">
-        <v>827</v>
-      </c>
       <c r="BC30">
-        <v>0.99036076428701636</v>
+        <v>0.99498145347305278</v>
       </c>
       <c r="BD30">
-        <v>176.71932140470005</v>
+        <v>92.006686327364918</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11098,16 +11101,16 @@
         <v>445</v>
       </c>
       <c r="Y31" t="s">
-        <v>388</v>
+        <v>345</v>
       </c>
       <c r="Z31" t="s">
         <v>573</v>
       </c>
       <c r="AA31">
-        <v>0.99689080338218783</v>
+        <v>0.99400218125602058</v>
       </c>
       <c r="AB31">
-        <v>57.001937993222221</v>
+        <v>109.96001030628999</v>
       </c>
       <c r="AD31" t="s">
         <v>402</v>
@@ -11134,16 +11137,16 @@
         <v>648</v>
       </c>
       <c r="AM31" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="AN31" t="s">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="AO31">
-        <v>0.98177850613436324</v>
+        <v>0.98895557240687315</v>
       </c>
       <c r="AP31">
-        <v>334.06072087000706</v>
+        <v>202.48117254065832</v>
       </c>
       <c r="AR31" t="s">
         <v>402</v>
@@ -11170,16 +11173,16 @@
         <v>773</v>
       </c>
       <c r="BA31" t="s">
+        <v>827</v>
+      </c>
+      <c r="BB31" t="s">
         <v>828</v>
       </c>
-      <c r="BB31" t="s">
-        <v>578</v>
-      </c>
       <c r="BC31">
-        <v>0.93477394593085072</v>
+        <v>0.98831120739622746</v>
       </c>
       <c r="BD31">
-        <v>1195.8109912677364</v>
+        <v>214.2945310691625</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11211,10 +11214,10 @@
         <v>348</v>
       </c>
       <c r="L32">
-        <v>57.218139448914322</v>
+        <v>57.216539448914325</v>
       </c>
       <c r="M32">
-        <v>0.1703690980757801</v>
+        <v>0.17036916346675629</v>
       </c>
       <c r="O32" t="s">
         <v>402</v>
@@ -11244,16 +11247,16 @@
         <v>447</v>
       </c>
       <c r="Y32" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="Z32" t="s">
         <v>574</v>
       </c>
       <c r="AA32">
-        <v>0.96911860205632039</v>
+        <v>0.99624827768323054</v>
       </c>
       <c r="AB32">
-        <v>566.15896230079227</v>
+        <v>68.781575807440518</v>
       </c>
       <c r="AD32" t="s">
         <v>402</v>
@@ -11280,16 +11283,16 @@
         <v>650</v>
       </c>
       <c r="AM32" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AN32" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AO32">
-        <v>0.9574422475745189</v>
+        <v>0.95753456607285348</v>
       </c>
       <c r="AP32">
-        <v>780.22546113382077</v>
+        <v>778.53295533101902</v>
       </c>
       <c r="AR32" t="s">
         <v>402</v>
@@ -11319,13 +11322,13 @@
         <v>829</v>
       </c>
       <c r="BB32" t="s">
-        <v>830</v>
+        <v>707</v>
       </c>
       <c r="BC32">
-        <v>0.99498145347305278</v>
+        <v>0.99160370033662015</v>
       </c>
       <c r="BD32">
-        <v>92.006686327364918</v>
+        <v>153.93216049529627</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11390,16 +11393,16 @@
         <v>449</v>
       </c>
       <c r="Y33" t="s">
-        <v>398</v>
+        <v>347</v>
       </c>
       <c r="Z33" t="s">
         <v>575</v>
       </c>
       <c r="AA33">
-        <v>0.97702953960894623</v>
+        <v>0.98654011406382824</v>
       </c>
       <c r="AB33">
-        <v>421.12510716931934</v>
+        <v>246.76457549648219</v>
       </c>
       <c r="AD33" t="s">
         <v>402</v>
@@ -11426,16 +11429,16 @@
         <v>652</v>
       </c>
       <c r="AM33" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AN33" t="s">
-        <v>715</v>
+        <v>576</v>
       </c>
       <c r="AO33">
-        <v>0.99700964975406792</v>
+        <v>0.94698201881115829</v>
       </c>
       <c r="AP33">
-        <v>54.823087842088889</v>
+        <v>971.99632179543119</v>
       </c>
       <c r="AR33" t="s">
         <v>402</v>
@@ -11462,16 +11465,16 @@
         <v>777</v>
       </c>
       <c r="BA33" t="s">
+        <v>830</v>
+      </c>
+      <c r="BB33" t="s">
         <v>831</v>
       </c>
-      <c r="BB33" t="s">
-        <v>583</v>
-      </c>
       <c r="BC33">
-        <v>0.94478739551790969</v>
+        <v>0.98529032090802915</v>
       </c>
       <c r="BD33">
-        <v>1012.2310821716558</v>
+        <v>269.67745001946554</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11536,16 +11539,16 @@
         <v>451</v>
       </c>
       <c r="Y34" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="Z34" t="s">
         <v>576</v>
       </c>
       <c r="AA34">
-        <v>0.99619242046188483</v>
+        <v>0.97006538483877391</v>
       </c>
       <c r="AB34">
-        <v>69.805624865443917</v>
+        <v>548.80127795581154</v>
       </c>
       <c r="AD34" t="s">
         <v>402</v>
@@ -11572,16 +11575,16 @@
         <v>654</v>
       </c>
       <c r="AM34" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="AN34" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="AO34">
-        <v>0.9755246434835193</v>
+        <v>0.99557021775830368</v>
       </c>
       <c r="AP34">
-        <v>448.71486946881294</v>
+        <v>81.21267443109943</v>
       </c>
       <c r="AR34" t="s">
         <v>402</v>
@@ -11611,13 +11614,13 @@
         <v>832</v>
       </c>
       <c r="BB34" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="BC34">
-        <v>0.97175571177973974</v>
+        <v>0.96834660314974419</v>
       </c>
       <c r="BD34">
-        <v>517.81195070477202</v>
+        <v>580.31227558802345</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11682,16 +11685,16 @@
         <v>453</v>
       </c>
       <c r="Y35" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="Z35" t="s">
         <v>577</v>
       </c>
       <c r="AA35">
-        <v>0.99447688875907914</v>
+        <v>0.96710197646129548</v>
       </c>
       <c r="AB35">
-        <v>101.25703941688285</v>
+        <v>603.13043154291677</v>
       </c>
       <c r="AD35" t="s">
         <v>402</v>
@@ -11718,16 +11721,16 @@
         <v>656</v>
       </c>
       <c r="AM35" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AN35" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AO35">
-        <v>0.98385712877132614</v>
+        <v>0.99117435469129123</v>
       </c>
       <c r="AP35">
-        <v>295.95263919235322</v>
+        <v>161.80349732632692</v>
       </c>
       <c r="AR35" t="s">
         <v>402</v>
@@ -11757,13 +11760,13 @@
         <v>833</v>
       </c>
       <c r="BB35" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="BC35">
-        <v>0.98102590217137298</v>
+        <v>0.96620229207214314</v>
       </c>
       <c r="BD35">
-        <v>347.85846019149614</v>
+        <v>619.62464534404216</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11828,16 +11831,16 @@
         <v>455</v>
       </c>
       <c r="Y36" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="Z36" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="AA36">
-        <v>0.96517074323544272</v>
+        <v>0.97245598614016138</v>
       </c>
       <c r="AB36">
-        <v>638.53637401688275</v>
+        <v>504.97358743037506</v>
       </c>
       <c r="AD36" t="s">
         <v>402</v>
@@ -11864,16 +11867,16 @@
         <v>658</v>
       </c>
       <c r="AM36" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AN36" t="s">
-        <v>583</v>
+        <v>719</v>
       </c>
       <c r="AO36">
-        <v>0.94748255895881095</v>
+        <v>0.99101688837209245</v>
       </c>
       <c r="AP36">
-        <v>962.81975242179908</v>
+        <v>164.69037984497118</v>
       </c>
       <c r="AR36" t="s">
         <v>402</v>
@@ -11903,13 +11906,13 @@
         <v>834</v>
       </c>
       <c r="BB36" t="s">
-        <v>706</v>
+        <v>835</v>
       </c>
       <c r="BC36">
-        <v>0.99160370033662015</v>
+        <v>0.98770095291302495</v>
       </c>
       <c r="BD36">
-        <v>153.93216049529627</v>
+        <v>225.48252992787681</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11974,16 +11977,16 @@
         <v>457</v>
       </c>
       <c r="Y37" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="Z37" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="AA37">
-        <v>0.97245598614016138</v>
+        <v>0.97006792991713942</v>
       </c>
       <c r="AB37">
-        <v>504.97358743037506</v>
+        <v>548.75461818577651</v>
       </c>
       <c r="AD37" t="s">
         <v>402</v>
@@ -12010,16 +12013,16 @@
         <v>660</v>
       </c>
       <c r="AM37" t="s">
+        <v>720</v>
+      </c>
+      <c r="AN37" t="s">
         <v>721</v>
       </c>
-      <c r="AN37" t="s">
-        <v>583</v>
-      </c>
       <c r="AO37">
-        <v>0.95796808346245155</v>
+        <v>0.9755246434835193</v>
       </c>
       <c r="AP37">
-        <v>770.58513652172257</v>
+        <v>448.71486946881294</v>
       </c>
       <c r="AR37" t="s">
         <v>402</v>
@@ -12046,16 +12049,16 @@
         <v>785</v>
       </c>
       <c r="BA37" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="BB37" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="BC37">
-        <v>0.97829546850421678</v>
+        <v>0.9602868544779749</v>
       </c>
       <c r="BD37">
-        <v>397.91641075602604</v>
+        <v>728.07433457046079</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12120,16 +12123,16 @@
         <v>459</v>
       </c>
       <c r="Y38" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s">
         <v>579</v>
       </c>
       <c r="AA38">
-        <v>0.99633073297550734</v>
+        <v>0.98903719509068366</v>
       </c>
       <c r="AB38">
-        <v>67.269895449032902</v>
+        <v>200.98475667080021</v>
       </c>
       <c r="AD38" t="s">
         <v>402</v>
@@ -12159,13 +12162,13 @@
         <v>722</v>
       </c>
       <c r="AN38" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="AO38">
-        <v>0.9436975669946106</v>
+        <v>0.9574422475745189</v>
       </c>
       <c r="AP38">
-        <v>1032.2112717654718</v>
+        <v>780.22546113382077</v>
       </c>
       <c r="AR38" t="s">
         <v>402</v>
@@ -12192,16 +12195,16 @@
         <v>787</v>
       </c>
       <c r="BA38" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="BB38" t="s">
-        <v>583</v>
+        <v>838</v>
       </c>
       <c r="BC38">
-        <v>0.93693021635476914</v>
+        <v>0.98716759869587867</v>
       </c>
       <c r="BD38">
-        <v>1156.2793668292329</v>
+        <v>235.26069057555824</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12266,16 +12269,16 @@
         <v>461</v>
       </c>
       <c r="Y39" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="Z39" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="AA39">
-        <v>0.98421229582412162</v>
+        <v>0.9966278856580183</v>
       </c>
       <c r="AB39">
-        <v>289.44124322443668</v>
+        <v>61.822096269664314</v>
       </c>
       <c r="AD39" t="s">
         <v>402</v>
@@ -12305,13 +12308,13 @@
         <v>723</v>
       </c>
       <c r="AN39" t="s">
-        <v>724</v>
+        <v>561</v>
       </c>
       <c r="AO39">
-        <v>0.99117435469129123</v>
+        <v>0.97673972771258222</v>
       </c>
       <c r="AP39">
-        <v>161.80349732632692</v>
+        <v>426.43832526932584</v>
       </c>
       <c r="AR39" t="s">
         <v>402</v>
@@ -12338,16 +12341,16 @@
         <v>789</v>
       </c>
       <c r="BA39" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="BB39" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="BC39">
-        <v>0.93888082510661108</v>
+        <v>0.93477394593085072</v>
       </c>
       <c r="BD39">
-        <v>1120.5182063787968</v>
+        <v>1195.8109912677364</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12412,16 +12415,16 @@
         <v>463</v>
       </c>
       <c r="Y40" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="Z40" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="AA40">
-        <v>0.94688476071898231</v>
+        <v>0.99689080338218783</v>
       </c>
       <c r="AB40">
-        <v>973.77938681865817</v>
+        <v>57.001937993222221</v>
       </c>
       <c r="AD40" t="s">
         <v>402</v>
@@ -12448,16 +12451,16 @@
         <v>666</v>
       </c>
       <c r="AM40" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AN40" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="AO40">
-        <v>0.97673972771258222</v>
+        <v>0.95686428742271346</v>
       </c>
       <c r="AP40">
-        <v>426.43832526932584</v>
+        <v>790.82139725025399</v>
       </c>
       <c r="AR40" t="s">
         <v>402</v>
@@ -12484,16 +12487,16 @@
         <v>791</v>
       </c>
       <c r="BA40" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="BB40" t="s">
-        <v>601</v>
+        <v>565</v>
       </c>
       <c r="BC40">
-        <v>0.94491770107559214</v>
+        <v>0.95614590843046721</v>
       </c>
       <c r="BD40">
-        <v>1009.8421469474777</v>
+        <v>803.99167877476805</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12558,16 +12561,16 @@
         <v>465</v>
       </c>
       <c r="Y41" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="Z41" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AA41">
-        <v>0.97577723283636553</v>
+        <v>0.98451878015346617</v>
       </c>
       <c r="AB41">
-        <v>444.08406466663115</v>
+        <v>283.82236385312052</v>
       </c>
       <c r="AD41" t="s">
         <v>402</v>
@@ -12594,16 +12597,16 @@
         <v>668</v>
       </c>
       <c r="AM41" t="s">
+        <v>725</v>
+      </c>
+      <c r="AN41" t="s">
         <v>726</v>
       </c>
-      <c r="AN41" t="s">
-        <v>565</v>
-      </c>
       <c r="AO41">
-        <v>0.95753456607285348</v>
+        <v>0.98221507709655431</v>
       </c>
       <c r="AP41">
-        <v>778.53295533101902</v>
+        <v>326.05691989650336</v>
       </c>
       <c r="AR41" t="s">
         <v>402</v>
@@ -12630,16 +12633,16 @@
         <v>793</v>
       </c>
       <c r="BA41" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="BB41" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="BC41">
-        <v>0.95063651087703893</v>
+        <v>0.95197431053166182</v>
       </c>
       <c r="BD41">
-        <v>904.99730058761952</v>
+        <v>880.47097358620078</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12704,16 +12707,16 @@
         <v>467</v>
       </c>
       <c r="Y42" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="Z42" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA42">
-        <v>0.99690816609326338</v>
+        <v>0.9956937957649058</v>
       </c>
       <c r="AB42">
-        <v>56.683621623505239</v>
+        <v>78.947077643392717</v>
       </c>
       <c r="AD42" t="s">
         <v>402</v>
@@ -12743,13 +12746,13 @@
         <v>727</v>
       </c>
       <c r="AN42" t="s">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="AO42">
-        <v>0.9519359532349716</v>
+        <v>0.98026073113098933</v>
       </c>
       <c r="AP42">
-        <v>881.17419069218636</v>
+        <v>361.88659593186213</v>
       </c>
       <c r="AR42" t="s">
         <v>402</v>
@@ -12776,16 +12779,16 @@
         <v>795</v>
       </c>
       <c r="BA42" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="BB42" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="BC42">
-        <v>0.99286819499076961</v>
+        <v>0.99556358538362921</v>
       </c>
       <c r="BD42">
-        <v>130.7497585025562</v>
+        <v>81.334267966797512</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12850,16 +12853,16 @@
         <v>469</v>
       </c>
       <c r="Y43" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="Z43" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA43">
-        <v>0.9791414671967239</v>
+        <v>0.99635032886115649</v>
       </c>
       <c r="AB43">
-        <v>382.40643472672787</v>
+        <v>66.910637545464084</v>
       </c>
       <c r="AD43" t="s">
         <v>402</v>
@@ -12892,10 +12895,10 @@
         <v>729</v>
       </c>
       <c r="AO43">
-        <v>0.98243109777744309</v>
+        <v>0.97905895332023074</v>
       </c>
       <c r="AP43">
-        <v>322.09654074687614</v>
+        <v>383.91918912910296</v>
       </c>
       <c r="AR43" t="s">
         <v>402</v>
@@ -12922,16 +12925,16 @@
         <v>797</v>
       </c>
       <c r="BA43" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="BB43" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="BC43">
-        <v>0.93885489623641283</v>
+        <v>0.94896692115877124</v>
       </c>
       <c r="BD43">
-        <v>1120.9935689990987</v>
+        <v>935.60644542252658</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12996,16 +12999,16 @@
         <v>471</v>
       </c>
       <c r="Y44" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="Z44" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AA44">
-        <v>0.96495725501214258</v>
+        <v>0.98520673013262905</v>
       </c>
       <c r="AB44">
-        <v>642.45032477738675</v>
+        <v>271.20994756846727</v>
       </c>
       <c r="AD44" t="s">
         <v>402</v>
@@ -13035,13 +13038,13 @@
         <v>730</v>
       </c>
       <c r="AN44" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="AO44">
-        <v>0.96732413990250377</v>
+        <v>0.94748255895881095</v>
       </c>
       <c r="AP44">
-        <v>599.05743512076492</v>
+        <v>962.81975242179908</v>
       </c>
       <c r="AR44" t="s">
         <v>402</v>
@@ -13068,16 +13071,16 @@
         <v>799</v>
       </c>
       <c r="BA44" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="BB44" t="s">
-        <v>844</v>
+        <v>570</v>
       </c>
       <c r="BC44">
-        <v>0.98831120739622746</v>
+        <v>0.93885489623641283</v>
       </c>
       <c r="BD44">
-        <v>214.2945310691625</v>
+        <v>1120.9935689990987</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13142,16 +13145,16 @@
         <v>473</v>
       </c>
       <c r="Y45" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="Z45" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AA45">
-        <v>0.99332429446553039</v>
+        <v>0.99719604020926056</v>
       </c>
       <c r="AB45">
-        <v>122.38793479860949</v>
+        <v>51.405929496890515</v>
       </c>
       <c r="AD45" t="s">
         <v>402</v>
@@ -13181,13 +13184,13 @@
         <v>731</v>
       </c>
       <c r="AN45" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="AO45">
-        <v>0.97186368651165222</v>
+        <v>0.95796808346245155</v>
       </c>
       <c r="AP45">
-        <v>515.83241395304219</v>
+        <v>770.58513652172257</v>
       </c>
       <c r="AR45" t="s">
         <v>402</v>
@@ -13214,16 +13217,16 @@
         <v>801</v>
       </c>
       <c r="BA45" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="BB45" t="s">
-        <v>846</v>
+        <v>570</v>
       </c>
       <c r="BC45">
-        <v>0.98770095291302495</v>
+        <v>0.96587851707660599</v>
       </c>
       <c r="BD45">
-        <v>225.48252992787681</v>
+        <v>625.56052026222312</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13288,16 +13291,16 @@
         <v>475</v>
       </c>
       <c r="Y46" t="s">
-        <v>397</v>
+        <v>327</v>
       </c>
       <c r="Z46" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AA46">
-        <v>0.95110614119885384</v>
+        <v>0.9791414671967239</v>
       </c>
       <c r="AB46">
-        <v>896.38741135434657</v>
+        <v>382.40643472672787</v>
       </c>
       <c r="AD46" t="s">
         <v>402</v>
@@ -13327,13 +13330,13 @@
         <v>732</v>
       </c>
       <c r="AN46" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="AO46">
-        <v>0.98026073113098933</v>
+        <v>0.9436975669946106</v>
       </c>
       <c r="AP46">
-        <v>361.88659593186213</v>
+        <v>1032.2112717654718</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13398,16 +13401,16 @@
         <v>477</v>
       </c>
       <c r="Y47" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="Z47" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="AA47">
-        <v>0.98628621327161703</v>
+        <v>0.98267907851268621</v>
       </c>
       <c r="AB47">
-        <v>251.41942335368827</v>
+        <v>317.55022726741913</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13472,16 +13475,16 @@
         <v>479</v>
       </c>
       <c r="Y48" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="Z48" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AA48">
-        <v>0.97678876819750537</v>
+        <v>0.94688476071898231</v>
       </c>
       <c r="AB48">
-        <v>425.5392497124015</v>
+        <v>973.77938681865817</v>
       </c>
     </row>
     <row r="49" spans="2:28">
@@ -13546,16 +13549,16 @@
         <v>481</v>
       </c>
       <c r="Y49" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="Z49" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="AA49">
-        <v>0.96912603699420019</v>
+        <v>0.95227568919833094</v>
       </c>
       <c r="AB49">
-        <v>566.02265510632935</v>
+        <v>874.94569803060017</v>
       </c>
     </row>
     <row r="50" spans="2:28">
@@ -13620,16 +13623,16 @@
         <v>483</v>
       </c>
       <c r="Y50" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="Z50" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="AA50">
-        <v>0.98985535554561865</v>
+        <v>0.99017812457307008</v>
       </c>
       <c r="AB50">
-        <v>185.9851483303255</v>
+        <v>180.06771616038245</v>
       </c>
     </row>
     <row r="51" spans="2:28">
@@ -13694,16 +13697,16 @@
         <v>485</v>
       </c>
       <c r="Y51" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="Z51" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AA51">
-        <v>0.98267907851268621</v>
+        <v>0.99088855789814245</v>
       </c>
       <c r="AB51">
-        <v>317.55022726741913</v>
+        <v>167.04310520072229</v>
       </c>
     </row>
     <row r="52" spans="2:28">
@@ -13768,16 +13771,16 @@
         <v>487</v>
       </c>
       <c r="Y52" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="Z52" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AA52">
-        <v>0.96276589991882666</v>
+        <v>0.9944769137527022</v>
       </c>
       <c r="AB52">
-        <v>682.62516815484491</v>
+        <v>101.25658120045976</v>
       </c>
     </row>
     <row r="53" spans="2:28">
@@ -13842,16 +13845,16 @@
         <v>489</v>
       </c>
       <c r="Y53" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="Z53" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="AA53">
-        <v>0.9966278856580183</v>
+        <v>0.96493395982863905</v>
       </c>
       <c r="AB53">
-        <v>61.822096269664314</v>
+        <v>642.87740314161726</v>
       </c>
     </row>
     <row r="54" spans="2:28">
@@ -13916,16 +13919,16 @@
         <v>491</v>
       </c>
       <c r="Y54" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="Z54" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AA54">
-        <v>0.97067956893851193</v>
+        <v>0.99218536928207235</v>
       </c>
       <c r="AB54">
-        <v>537.54123612728188</v>
+        <v>143.26822982867444</v>
       </c>
     </row>
     <row r="55" spans="2:28">
@@ -13990,16 +13993,16 @@
         <v>493</v>
       </c>
       <c r="Y55" t="s">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="Z55" t="s">
-        <v>589</v>
+        <v>561</v>
       </c>
       <c r="AA55">
-        <v>0.96710197646129548</v>
+        <v>0.99332429446553039</v>
       </c>
       <c r="AB55">
-        <v>603.13043154291677</v>
+        <v>122.38793479860949</v>
       </c>
     </row>
     <row r="56" spans="2:28">
@@ -14064,16 +14067,16 @@
         <v>495</v>
       </c>
       <c r="Y56" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Z56" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AA56">
-        <v>0.99640865233383846</v>
+        <v>0.99496216240453639</v>
       </c>
       <c r="AB56">
-        <v>65.841373879627454</v>
+        <v>92.360355916833001</v>
       </c>
     </row>
     <row r="57" spans="2:28">
@@ -14138,16 +14141,16 @@
         <v>497</v>
       </c>
       <c r="Y57" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="Z57" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AA57">
-        <v>0.98091465074522166</v>
+        <v>0.97702953960894623</v>
       </c>
       <c r="AB57">
-        <v>349.89806967093693</v>
+        <v>421.12510716931934</v>
       </c>
     </row>
     <row r="58" spans="2:28">
@@ -14212,16 +14215,16 @@
         <v>499</v>
       </c>
       <c r="Y58" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="Z58" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="AA58">
-        <v>0.98568253831294061</v>
+        <v>0.98631766623578765</v>
       </c>
       <c r="AB58">
-        <v>262.48679759608808</v>
+        <v>250.84278567722609</v>
       </c>
     </row>
     <row r="59" spans="2:28">
@@ -14286,16 +14289,16 @@
         <v>501</v>
       </c>
       <c r="Y59" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="Z59" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="AA59">
-        <v>0.98520673013262905</v>
+        <v>0.96912603699420019</v>
       </c>
       <c r="AB59">
-        <v>271.20994756846727</v>
+        <v>566.02265510632935</v>
       </c>
     </row>
     <row r="60" spans="2:28">
@@ -14327,10 +14330,10 @@
         <v>376</v>
       </c>
       <c r="L60">
-        <v>68.937478588067492</v>
+        <v>68.930878588067486</v>
       </c>
       <c r="M60">
-        <v>0.1732922978878316</v>
+        <v>0.17329083065270209</v>
       </c>
       <c r="O60" t="s">
         <v>402</v>
@@ -14360,16 +14363,16 @@
         <v>503</v>
       </c>
       <c r="Y60" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="Z60" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="AA60">
-        <v>0.98631766623578765</v>
+        <v>0.99620173788084643</v>
       </c>
       <c r="AB60">
-        <v>250.84278567722609</v>
+        <v>69.634805517815565</v>
       </c>
     </row>
     <row r="61" spans="2:28">
@@ -14434,16 +14437,16 @@
         <v>505</v>
       </c>
       <c r="Y61" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Z61" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA61">
-        <v>0.99235586733508585</v>
+        <v>0.99808042106452499</v>
       </c>
       <c r="AB61">
-        <v>140.14243219009202</v>
+        <v>35.192280483708828</v>
       </c>
     </row>
     <row r="62" spans="2:28">
@@ -14508,16 +14511,16 @@
         <v>507</v>
       </c>
       <c r="Y62" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Z62" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA62">
-        <v>0.99218536928207235</v>
+        <v>0.99235892038811246</v>
       </c>
       <c r="AB62">
-        <v>143.26822982867444</v>
+        <v>140.08645955127213</v>
       </c>
     </row>
     <row r="63" spans="2:28">
@@ -14582,16 +14585,16 @@
         <v>509</v>
       </c>
       <c r="Y63" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="Z63" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AA63">
-        <v>0.95227568919833094</v>
+        <v>0.97311459430172587</v>
       </c>
       <c r="AB63">
-        <v>874.94569803060017</v>
+        <v>492.8991044683591</v>
       </c>
     </row>
     <row r="64" spans="2:28">
@@ -14656,16 +14659,16 @@
         <v>511</v>
       </c>
       <c r="Y64" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="Z64" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA64">
-        <v>0.9956937957649058</v>
+        <v>0.95854557991594525</v>
       </c>
       <c r="AB64">
-        <v>78.947077643392717</v>
+        <v>759.99770154100372</v>
       </c>
     </row>
     <row r="65" spans="2:28">
@@ -14730,16 +14733,16 @@
         <v>513</v>
       </c>
       <c r="Y65" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="Z65" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA65">
-        <v>0.99620173788084643</v>
+        <v>0.98524310910972257</v>
       </c>
       <c r="AB65">
-        <v>69.634805517815565</v>
+        <v>270.5429996550854</v>
       </c>
     </row>
     <row r="66" spans="2:28">
@@ -14804,16 +14807,16 @@
         <v>515</v>
       </c>
       <c r="Y66" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="Z66" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="AA66">
-        <v>0.9771016434875236</v>
+        <v>0.94713624989887801</v>
       </c>
       <c r="AB66">
-        <v>419.80320272873433</v>
+        <v>969.16875185390393</v>
       </c>
     </row>
     <row r="67" spans="2:28">
@@ -14845,10 +14848,10 @@
         <v>383</v>
       </c>
       <c r="L67">
-        <v>3.3639749483881687</v>
+        <v>3.3429749483881688</v>
       </c>
       <c r="M67">
-        <v>0.20091273329694481</v>
+        <v>0.20086831826414461</v>
       </c>
       <c r="O67" t="s">
         <v>402</v>
@@ -14878,16 +14881,16 @@
         <v>517</v>
       </c>
       <c r="Y67" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="Z67" t="s">
-        <v>597</v>
+        <v>556</v>
       </c>
       <c r="AA67">
-        <v>0.98903719509068366</v>
+        <v>0.96517074323544272</v>
       </c>
       <c r="AB67">
-        <v>200.98475667080021</v>
+        <v>638.53637401688275</v>
       </c>
     </row>
     <row r="68" spans="2:28">
@@ -14952,16 +14955,16 @@
         <v>519</v>
       </c>
       <c r="Y68" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="Z68" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AA68">
-        <v>0.97006538483877391</v>
+        <v>0.9771016434875236</v>
       </c>
       <c r="AB68">
-        <v>548.80127795581154</v>
+        <v>419.80320272873433</v>
       </c>
     </row>
     <row r="69" spans="2:28">
@@ -14993,10 +14996,10 @@
         <v>385</v>
       </c>
       <c r="L69">
-        <v>5.9733771859390101</v>
+        <v>5.9553771859390103</v>
       </c>
       <c r="M69">
-        <v>0.20134240341525281</v>
+        <v>0.2013265955471773</v>
       </c>
       <c r="O69" t="s">
         <v>402</v>
@@ -15026,16 +15029,16 @@
         <v>521</v>
       </c>
       <c r="Y69" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="Z69" t="s">
         <v>598</v>
       </c>
       <c r="AA69">
-        <v>0.98524310910972257</v>
+        <v>0.9912986266790621</v>
       </c>
       <c r="AB69">
-        <v>270.5429996550854</v>
+        <v>159.52517755052818</v>
       </c>
     </row>
     <row r="70" spans="2:28">
@@ -15100,16 +15103,16 @@
         <v>523</v>
       </c>
       <c r="Y70" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="Z70" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="AA70">
-        <v>0.97807159933286214</v>
+        <v>0.99619242046188483</v>
       </c>
       <c r="AB70">
-        <v>402.02067889752732</v>
+        <v>69.805624865443917</v>
       </c>
     </row>
     <row r="71" spans="2:28">
@@ -15141,10 +15144,10 @@
         <v>387</v>
       </c>
       <c r="L71">
-        <v>17.525902930935121</v>
+        <v>17.499602930935122</v>
       </c>
       <c r="M71">
-        <v>0.21573704131912899</v>
+        <v>0.21572743675250819</v>
       </c>
       <c r="O71" t="s">
         <v>402</v>
@@ -15174,16 +15177,16 @@
         <v>525</v>
       </c>
       <c r="Y71" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="Z71" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="AA71">
-        <v>0.95152672202699851</v>
+        <v>0.96239325925412511</v>
       </c>
       <c r="AB71">
-        <v>888.67676283836079</v>
+        <v>689.45691367437246</v>
       </c>
     </row>
     <row r="72" spans="2:28">
@@ -15248,16 +15251,16 @@
         <v>527</v>
       </c>
       <c r="Y72" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="Z72" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA72">
-        <v>0.9725266797570975</v>
+        <v>0.95110614119885384</v>
       </c>
       <c r="AB72">
-        <v>503.67753778654668</v>
+        <v>896.38741135434657</v>
       </c>
     </row>
     <row r="73" spans="2:28">
@@ -15322,16 +15325,16 @@
         <v>529</v>
       </c>
       <c r="Y73" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="Z73" t="s">
-        <v>600</v>
+        <v>558</v>
       </c>
       <c r="AA73">
-        <v>0.99439318395533605</v>
+        <v>0.98223116847554315</v>
       </c>
       <c r="AB73">
-        <v>102.7916274855054</v>
+        <v>325.76191128170939</v>
       </c>
     </row>
     <row r="74" spans="2:28">
@@ -15363,10 +15366,10 @@
         <v>390</v>
       </c>
       <c r="L74">
-        <v>26.072418278851309</v>
+        <v>25.97141827885131</v>
       </c>
       <c r="M74">
-        <v>0.1804484765462602</v>
+        <v>0.1804520080831771</v>
       </c>
       <c r="O74" t="s">
         <v>402</v>
@@ -15396,16 +15399,16 @@
         <v>531</v>
       </c>
       <c r="Y74" t="s">
-        <v>383</v>
+        <v>334</v>
       </c>
       <c r="Z74" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="AA74">
-        <v>0.96239820242893215</v>
+        <v>0.97496236164466343</v>
       </c>
       <c r="AB74">
-        <v>689.36628880291153</v>
+        <v>459.02336984783733</v>
       </c>
     </row>
     <row r="75" spans="2:28">
@@ -15437,10 +15440,10 @@
         <v>391</v>
       </c>
       <c r="L75">
-        <v>52.290678889451698</v>
+        <v>52.040578889451702</v>
       </c>
       <c r="M75">
-        <v>0.1928167561575288</v>
+        <v>0.19282734309607169</v>
       </c>
       <c r="O75" t="s">
         <v>402</v>
@@ -15470,16 +15473,16 @@
         <v>533</v>
       </c>
       <c r="Y75" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="Z75" t="s">
         <v>601</v>
       </c>
       <c r="AA75">
-        <v>0.97006792991713942</v>
+        <v>0.96911860205632039</v>
       </c>
       <c r="AB75">
-        <v>548.75461818577651</v>
+        <v>566.15896230079227</v>
       </c>
     </row>
     <row r="76" spans="2:28">
@@ -15544,16 +15547,16 @@
         <v>535</v>
       </c>
       <c r="Y76" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="Z76" t="s">
-        <v>566</v>
+        <v>602</v>
       </c>
       <c r="AA76">
-        <v>0.99088855789814245</v>
+        <v>0.99627301415801128</v>
       </c>
       <c r="AB76">
-        <v>167.04310520072229</v>
+        <v>68.328073769792198</v>
       </c>
     </row>
     <row r="77" spans="2:28">
@@ -15585,10 +15588,10 @@
         <v>393</v>
       </c>
       <c r="L77">
-        <v>23.038550345175565</v>
+        <v>22.969584115861512</v>
       </c>
       <c r="M77">
-        <v>0.22530562305425539</v>
+        <v>0.22529276569457291</v>
       </c>
       <c r="O77" t="s">
         <v>402</v>
@@ -15618,16 +15621,16 @@
         <v>537</v>
       </c>
       <c r="Y77" t="s">
-        <v>399</v>
+        <v>330</v>
       </c>
       <c r="Z77" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="AA77">
-        <v>0.97597719784352066</v>
+        <v>0.99633073297550734</v>
       </c>
       <c r="AB77">
-        <v>440.41803953545457</v>
+        <v>67.269895449032902</v>
       </c>
     </row>
     <row r="78" spans="2:28">
@@ -15659,10 +15662,10 @@
         <v>394</v>
       </c>
       <c r="L78">
-        <v>11.666609368827739</v>
+        <v>11.66550936882774</v>
       </c>
       <c r="M78">
-        <v>0.1989415531628968</v>
+        <v>0.1989396022678272</v>
       </c>
       <c r="O78" t="s">
         <v>402</v>
@@ -15692,16 +15695,16 @@
         <v>539</v>
       </c>
       <c r="Y78" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="Z78" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA78">
-        <v>0.99719604020926056</v>
+        <v>0.9725266797570975</v>
       </c>
       <c r="AB78">
-        <v>51.405929496890515</v>
+        <v>503.67753778654668</v>
       </c>
     </row>
     <row r="79" spans="2:28">
@@ -15766,16 +15769,16 @@
         <v>541</v>
       </c>
       <c r="Y79" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="Z79" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AA79">
-        <v>0.98786674666740726</v>
+        <v>0.99690816609326338</v>
       </c>
       <c r="AB79">
-        <v>222.44297776420015</v>
+        <v>56.683621623505239</v>
       </c>
     </row>
     <row r="80" spans="2:28">
@@ -15807,10 +15810,10 @@
         <v>396</v>
       </c>
       <c r="L80">
-        <v>9.5422982529232083</v>
+        <v>9.538198252923209</v>
       </c>
       <c r="M80">
-        <v>0.2268981201209293</v>
+        <v>0.22689595539720289</v>
       </c>
       <c r="O80" t="s">
         <v>402</v>
@@ -15840,16 +15843,16 @@
         <v>543</v>
       </c>
       <c r="Y80" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="Z80" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA80">
-        <v>0.99400218125602058</v>
+        <v>0.97592802238295073</v>
       </c>
       <c r="AB80">
-        <v>109.96001030628999</v>
+        <v>441.3195896459041</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -15914,16 +15917,16 @@
         <v>545</v>
       </c>
       <c r="Y81" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="Z81" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="AA81">
-        <v>0.99635032886115649</v>
+        <v>0.97807026787476981</v>
       </c>
       <c r="AB81">
-        <v>66.910637545464084</v>
+        <v>402.04508896255408</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -15988,16 +15991,16 @@
         <v>547</v>
       </c>
       <c r="Y82" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="Z82" t="s">
         <v>606</v>
       </c>
       <c r="AA82">
-        <v>0.98696950091677516</v>
+        <v>0.96276589991882666</v>
       </c>
       <c r="AB82">
-        <v>238.89248319245524</v>
+        <v>682.62516815484491</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16062,16 +16065,16 @@
         <v>549</v>
       </c>
       <c r="Y83" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="Z83" t="s">
-        <v>601</v>
+        <v>558</v>
       </c>
       <c r="AA83">
-        <v>0.9582992451809369</v>
+        <v>0.98628621327161703</v>
       </c>
       <c r="AB83">
-        <v>764.51383834949013</v>
+        <v>251.41942335368827</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -16154,7 +16157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2345858E-C8B7-4AB6-878C-66F4E00453A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86E1EF7-7B7A-40C6-86AC-B8DC7EF42FFE}">
   <dimension ref="B9:Z46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16266,7 +16269,7 @@
         <v>847</v>
       </c>
       <c r="K11" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="L11">
         <v>0.129291216127222</v>
@@ -16299,7 +16302,7 @@
         <v>919</v>
       </c>
       <c r="X11" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="Y11">
         <v>6.6577500000000001</v>
@@ -16334,7 +16337,7 @@
         <v>849</v>
       </c>
       <c r="K12" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L12">
         <v>1.2472977367603104</v>
@@ -16367,7 +16370,7 @@
         <v>921</v>
       </c>
       <c r="X12" t="s">
-        <v>836</v>
+        <v>818</v>
       </c>
       <c r="Y12">
         <v>54.581249999999997</v>
@@ -16402,7 +16405,7 @@
         <v>851</v>
       </c>
       <c r="K13" t="s">
-        <v>685</v>
+        <v>708</v>
       </c>
       <c r="L13">
         <v>2.318274719104624</v>
@@ -16435,7 +16438,7 @@
         <v>923</v>
       </c>
       <c r="X13" t="s">
-        <v>831</v>
+        <v>808</v>
       </c>
       <c r="Y13">
         <v>18.436499999999999</v>
@@ -16470,7 +16473,7 @@
         <v>853</v>
       </c>
       <c r="K14" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="L14">
         <v>0.91927356390823156</v>
@@ -16503,7 +16506,7 @@
         <v>925</v>
       </c>
       <c r="X14" t="s">
-        <v>818</v>
+        <v>844</v>
       </c>
       <c r="Y14">
         <v>17.616</v>
@@ -16538,7 +16541,7 @@
         <v>855</v>
       </c>
       <c r="K15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L15">
         <v>4.6464784096723921</v>
@@ -16571,7 +16574,7 @@
         <v>927</v>
       </c>
       <c r="X15" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="Y15">
         <v>14.769</v>
@@ -16606,7 +16609,7 @@
         <v>857</v>
       </c>
       <c r="K16" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="L16">
         <v>11.882635191498228</v>
@@ -16639,7 +16642,7 @@
         <v>929</v>
       </c>
       <c r="X16" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="Y16">
         <v>13.2255</v>
@@ -16674,7 +16677,7 @@
         <v>859</v>
       </c>
       <c r="K17" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="L17">
         <v>11.092555055294371</v>
@@ -16707,7 +16710,7 @@
         <v>931</v>
       </c>
       <c r="X17" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="Y17">
         <v>28.651499999999999</v>
@@ -16742,7 +16745,7 @@
         <v>861</v>
       </c>
       <c r="K18" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="L18">
         <v>4.7403831699218822E-2</v>
@@ -16775,7 +16778,7 @@
         <v>933</v>
       </c>
       <c r="X18" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="Y18">
         <v>27.531749999999999</v>
@@ -16810,7 +16813,7 @@
         <v>863</v>
       </c>
       <c r="K19" t="s">
-        <v>731</v>
+        <v>688</v>
       </c>
       <c r="L19">
         <v>16.426692253806657</v>
@@ -16843,7 +16846,7 @@
         <v>935</v>
       </c>
       <c r="X19" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="Y19">
         <v>51.64425</v>
@@ -16878,7 +16881,7 @@
         <v>865</v>
       </c>
       <c r="K20" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="L20">
         <v>8.1288287393980401</v>
@@ -16911,7 +16914,7 @@
         <v>937</v>
       </c>
       <c r="X20" t="s">
-        <v>808</v>
+        <v>846</v>
       </c>
       <c r="Y20">
         <v>134.35650000000001</v>
@@ -16946,7 +16949,7 @@
         <v>867</v>
       </c>
       <c r="K21" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="L21">
         <v>0.13371018978628957</v>
@@ -16979,7 +16982,7 @@
         <v>939</v>
       </c>
       <c r="X21" t="s">
-        <v>833</v>
+        <v>816</v>
       </c>
       <c r="Y21">
         <v>7.9987500000000002</v>
@@ -17014,7 +17017,7 @@
         <v>869</v>
       </c>
       <c r="K22" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="L22">
         <v>1.3857406990868373</v>
@@ -17047,7 +17050,7 @@
         <v>941</v>
       </c>
       <c r="X22" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
       <c r="Y22">
         <v>115.36875000000001</v>
@@ -17082,13 +17085,13 @@
         <v>871</v>
       </c>
       <c r="K23" t="s">
-        <v>703</v>
+        <v>725</v>
       </c>
       <c r="L23">
-        <v>0.7646774950894254</v>
+        <v>0.75467749508942539</v>
       </c>
       <c r="M23">
-        <v>0.1081269744728183</v>
+        <v>0.1084248921529785</v>
       </c>
       <c r="O23" t="s">
         <v>172</v>
@@ -17115,7 +17118,7 @@
         <v>943</v>
       </c>
       <c r="X23" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="Y23">
         <v>18.766500000000001</v>
@@ -17150,7 +17153,7 @@
         <v>873</v>
       </c>
       <c r="K24" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="L24">
         <v>0.96556410486278166</v>
@@ -17183,7 +17186,7 @@
         <v>945</v>
       </c>
       <c r="X24" t="s">
-        <v>838</v>
+        <v>809</v>
       </c>
       <c r="Y24">
         <v>1.5217499999999999</v>
@@ -17218,7 +17221,7 @@
         <v>875</v>
       </c>
       <c r="K25" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="L25">
         <v>0.43746236883491152</v>
@@ -17251,7 +17254,7 @@
         <v>947</v>
       </c>
       <c r="X25" t="s">
-        <v>815</v>
+        <v>840</v>
       </c>
       <c r="Y25">
         <v>1.90425</v>
@@ -17286,7 +17289,7 @@
         <v>877</v>
       </c>
       <c r="K26" t="s">
-        <v>728</v>
+        <v>689</v>
       </c>
       <c r="L26">
         <v>1.8762027163233561</v>
@@ -17319,7 +17322,7 @@
         <v>949</v>
       </c>
       <c r="X26" t="s">
-        <v>819</v>
+        <v>841</v>
       </c>
       <c r="Y26">
         <v>102.82125000000001</v>
@@ -17354,7 +17357,7 @@
         <v>879</v>
       </c>
       <c r="K27" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="L27">
         <v>0.18022981623384116</v>
@@ -17387,7 +17390,7 @@
         <v>951</v>
       </c>
       <c r="X27" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="Y27">
         <v>26.381250000000001</v>
@@ -17422,7 +17425,7 @@
         <v>881</v>
       </c>
       <c r="K28" t="s">
-        <v>683</v>
+        <v>713</v>
       </c>
       <c r="L28">
         <v>1.1308942027141895</v>
@@ -17455,7 +17458,7 @@
         <v>953</v>
       </c>
       <c r="X28" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="Y28">
         <v>9.1432500000000001</v>
@@ -17490,13 +17493,13 @@
         <v>883</v>
       </c>
       <c r="K29" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="L29">
-        <v>0.82049684706100345</v>
+        <v>0.7454968470610035</v>
       </c>
       <c r="M29">
-        <v>9.8696330216133096E-2</v>
+        <v>9.8070982100838894E-2</v>
       </c>
       <c r="O29" t="s">
         <v>172</v>
@@ -17523,7 +17526,7 @@
         <v>955</v>
       </c>
       <c r="X29" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="Y29">
         <v>49.376249999999999</v>
@@ -17558,7 +17561,7 @@
         <v>885</v>
       </c>
       <c r="K30" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="L30">
         <v>0.13491890498058171</v>
@@ -17591,7 +17594,7 @@
         <v>957</v>
       </c>
       <c r="X30" t="s">
-        <v>803</v>
+        <v>833</v>
       </c>
       <c r="Y30">
         <v>64.686750000000004</v>
@@ -17626,7 +17629,7 @@
         <v>887</v>
       </c>
       <c r="K31" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="L31">
         <v>3.3502966177508899E-2</v>
@@ -17659,7 +17662,7 @@
         <v>959</v>
       </c>
       <c r="X31" t="s">
-        <v>835</v>
+        <v>807</v>
       </c>
       <c r="Y31">
         <v>19.151250000000001</v>
@@ -17694,7 +17697,7 @@
         <v>889</v>
       </c>
       <c r="K32" t="s">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="L32">
         <v>4.4570745535421293E-2</v>
@@ -17727,7 +17730,7 @@
         <v>961</v>
       </c>
       <c r="X32" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="Y32">
         <v>91.322249999999997</v>
@@ -17762,7 +17765,7 @@
         <v>891</v>
       </c>
       <c r="K33" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="L33">
         <v>1.8432371407733249E-2</v>
@@ -17795,7 +17798,7 @@
         <v>963</v>
       </c>
       <c r="X33" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="Y33">
         <v>86.045249999999996</v>
@@ -17830,7 +17833,7 @@
         <v>893</v>
       </c>
       <c r="K34" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="L34">
         <v>0.33180838345937391</v>
@@ -17863,7 +17866,7 @@
         <v>965</v>
       </c>
       <c r="X34" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="Y34">
         <v>34.774500000000003</v>
@@ -17898,7 +17901,7 @@
         <v>895</v>
       </c>
       <c r="K35" t="s">
-        <v>714</v>
+        <v>695</v>
       </c>
       <c r="L35">
         <v>3.1614758986586073</v>
@@ -17931,7 +17934,7 @@
         <v>967</v>
       </c>
       <c r="X35" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="Y35">
         <v>60.10125</v>
@@ -17966,7 +17969,7 @@
         <v>897</v>
       </c>
       <c r="K36" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="L36">
         <v>1.3726240143913757</v>
@@ -17999,7 +18002,7 @@
         <v>969</v>
       </c>
       <c r="X36" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="Y36">
         <v>2.3287499999999999</v>
@@ -18034,7 +18037,7 @@
         <v>899</v>
       </c>
       <c r="K37" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="L37">
         <v>0.1338251234250375</v>
@@ -18067,7 +18070,7 @@
         <v>971</v>
       </c>
       <c r="X37" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="Y37">
         <v>17.766749999999998</v>
@@ -18102,7 +18105,7 @@
         <v>901</v>
       </c>
       <c r="K38" t="s">
-        <v>730</v>
+        <v>680</v>
       </c>
       <c r="L38">
         <v>2.1118535388590605</v>
@@ -18135,7 +18138,7 @@
         <v>973</v>
       </c>
       <c r="X38" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="Y38">
         <v>2.073</v>
@@ -18170,7 +18173,7 @@
         <v>903</v>
       </c>
       <c r="K39" t="s">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="L39">
         <v>1.5197190100572773</v>
@@ -18203,7 +18206,7 @@
         <v>975</v>
       </c>
       <c r="X39" t="s">
-        <v>813</v>
+        <v>842</v>
       </c>
       <c r="Y39">
         <v>3.1927500000000002</v>
@@ -18238,7 +18241,7 @@
         <v>905</v>
       </c>
       <c r="K40" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="L40">
         <v>3.2370560671094046</v>
@@ -18271,7 +18274,7 @@
         <v>977</v>
       </c>
       <c r="X40" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="Y40">
         <v>8.2132500000000004</v>
@@ -18306,7 +18309,7 @@
         <v>907</v>
       </c>
       <c r="K41" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="L41">
         <v>9.3502299727040246</v>
@@ -18339,7 +18342,7 @@
         <v>979</v>
       </c>
       <c r="X41" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="Y41">
         <v>1.2622500000000001</v>
@@ -18374,7 +18377,7 @@
         <v>909</v>
       </c>
       <c r="K42" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="L42">
         <v>3.7895528026363667</v>
@@ -18407,7 +18410,7 @@
         <v>981</v>
       </c>
       <c r="X42" t="s">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="Y42">
         <v>7.3717499999999996</v>
@@ -18442,13 +18445,13 @@
         <v>911</v>
       </c>
       <c r="K43" t="s">
-        <v>688</v>
+        <v>728</v>
       </c>
       <c r="L43">
-        <v>2.5065968290099598</v>
+        <v>2.4345968290099598</v>
       </c>
       <c r="M43">
-        <v>0.1502586949943355</v>
+        <v>0.15008708016414421</v>
       </c>
       <c r="O43" t="s">
         <v>172</v>
@@ -18475,7 +18478,7 @@
         <v>983</v>
       </c>
       <c r="X43" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="Y43">
         <v>9.1162500000000009</v>
@@ -18510,7 +18513,7 @@
         <v>913</v>
       </c>
       <c r="K44" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="L44">
         <v>3.5872166924997928</v>
@@ -18543,7 +18546,7 @@
         <v>985</v>
       </c>
       <c r="X44" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="Y44">
         <v>2.0219999999999998</v>
@@ -18578,7 +18581,7 @@
         <v>915</v>
       </c>
       <c r="K45" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L45">
         <v>1.2359990336927942</v>
@@ -18611,7 +18614,7 @@
         <v>987</v>
       </c>
       <c r="X45" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="Y45">
         <v>6.5925000000000002</v>
@@ -18646,7 +18649,7 @@
         <v>917</v>
       </c>
       <c r="K46" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="L46">
         <v>3.8785201943148309</v>
@@ -18661,7 +18664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE45A88B-5591-468B-8675-C3C6ADCC2427}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC76012E-D3BB-489C-8C67-45244A5C5BF7}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20478,7 +20481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E263AB-2F05-464B-979C-7E09FD541EDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1BB622-71E8-4A1B-BFAD-0B1330881143}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3866D5A-9158-45F7-A8BC-2BB9792B684C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D9F894-C378-42E4-9632-0C8E1BECDA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1339,18 +1339,180 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IDN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IDN_063</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 63</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IDN_010</t>
   </si>
   <si>
@@ -1375,34 +1537,160 @@
     <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IDN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
+    <t>distr_solelc_spv_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
   </si>
   <si>
     <t>distr_solelc_spv_IDN_065</t>
@@ -1435,106 +1723,58 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IDN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
+    <t>distr_solelc_spv_IDN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
   </si>
   <si>
     <t>distr_solelc_spv_IDN_028</t>
@@ -1549,334 +1789,163 @@
     <t>connecting solar to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IDN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_ID1-275_IDN,e_w721674155-275_IDN,e_w340205049-275_IDN,e_w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN,e_w1312287191-275_IDN,e_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN,e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w939542521-275_IDN,e_ID4-275_IDN,e_ID3-275_IDN,e_ID7-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w610198177-275_IDN,e_w753733608-275_IDN,e_w931931121-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1193553154-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_ID9-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN,e_ID1-275_IDN,e_w721685825-275_IDN,e_w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_w562061281-275_IDN,e_ID27-500_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403431-230_IDN,e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w759130125-230_IDN,e_ID9-230_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN,e_w615581270-275_IDN,e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN</t>
+  </si>
+  <si>
     <t>e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN,e_w398909640-500_IDN,e_w340978681-500_IDN,e_ID35-500_IDN,e_ID38-500_IDN</t>
   </si>
   <si>
-    <t>e_ID2-275_IDN</t>
-  </si>
-  <si>
     <t>e_ID34-500_IDN,e_ID38-500_IDN,e_w615581270-275_IDN</t>
   </si>
   <si>
-    <t>e_w759130125-230_IDN</t>
-  </si>
-  <si>
     <t>e_w544403426-230_IDN,e_w759130125-230_IDN</t>
   </si>
   <si>
-    <t>e_w610198177-275_IDN,e_w753733608-275_IDN,e_w931931121-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w1193553154-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403426-230_IDN,e_ID9-230_IDN,e_w759130125-230_IDN</t>
+    <t>e_w721685825-275_IDN,e_w754073846-275_IDN,e_w340205049-275_IDN,e_w310695690-275_IDN,e_w754096394-275_IDN,e_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID6-275_IDN,e_w939542521-275_IDN,e_w841499143-275_IDN,e_w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_w754178666-275_IDN,e_ID3-275_IDN,e_w310695690-275_IDN,e_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN,e_w1316786278-275_IDN,e_w931931121-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w943539373-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w721674155-275_IDN,e_w469888049-275_IDN,e_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w930719092-275_IDN,e_w841499143-275_IDN,e_w1186182648-500_IDN,e_w943539373-275_IDN,e_w753733608-275_IDN,e_w946191122-275_IDN,e_w610198177-275_IDN,e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_w166633831-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w340205049-275_IDN,e_w754073846-275_IDN,e_w310958602-275_IDN,e_w754096394-275_IDN,e_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-500_IDN,e_w562061281-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN,e_w544403426-230_IDN,e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-275_IDN,e_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w1193553154-275_IDN</t>
   </si>
   <si>
     <t>e_w1316876158-275_IDN,e_w161965853-500_IDN,e_w169444592-500_IDN,e_ID10-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_w966209515-500_IDN,e_ID15-500_IDN,e_w960747936-500_IDN,e_w960747902-500_IDN,e_w314452486-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_w629512849-500_IDN,e_ID29-500_IDN</t>
   </si>
   <si>
-    <t>e_w615581232-275_IDN</t>
-  </si>
-  <si>
     <t>e_w615581242-275_IDN,e_w614955993-230_IDN,e_w1193553154-275_IDN,e_w544403431-230_IDN</t>
   </si>
   <si>
     <t>e_w544403431-230_IDN,e_w759130125-230_IDN</t>
   </si>
   <si>
-    <t>e_w562061281-275_IDN,e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID2-275_IDN,e_w615581270-275_IDN,e_w615581242-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403426-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w721685825-275_IDN,e_w754073846-275_IDN,e_w340205049-275_IDN,e_w310695690-275_IDN,e_w754096394-275_IDN,e_w337039411-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID6-275_IDN,e_w939542521-275_IDN,e_w841499143-275_IDN,e_w1312287191-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_w754178666-275_IDN,e_ID3-275_IDN,e_w310695690-275_IDN,e_w736595653-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN,e_w1316786278-275_IDN,e_w931931121-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w943539373-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w943539373-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581242-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID2-275_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID38-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w721674155-275_IDN,e_w469888049-275_IDN,e_ID6-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w930719092-275_IDN,e_w841499143-275_IDN,e_w1186182648-500_IDN,e_w943539373-275_IDN,e_w753733608-275_IDN,e_w946191122-275_IDN,e_w610198177-275_IDN,e_w943539373-500_IDN</t>
-  </si>
-  <si>
-    <t>e_ID28-500_IDN,e_w166633831-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403426-230_IDN,e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+    <t>e_ID27-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_ID6-275_IDN,e_ID5-275_IDN,e_ID3-275_IDN,e_w939542521-275_IDN,e_w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID33-500_IDN,e_w264550744-500_IDN,e_w769617021-500_IDN,e_w314452486-500_IDN,e_ID29-500_IDN,e_w267626657-500_IDN,e_ID31-500_IDN,e_w166633831-500_IDN,e_w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID34-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_w1193553154-275_IDN,e_w615581232-275_IDN</t>
   </si>
   <si>
     <t>e_w841499143-275_IDN,e_w528189342-275_IDN,e_w931931133-275_IDN,e_w527900241-275_IDN,e_w946191122-275_IDN</t>
@@ -1885,73 +1954,82 @@
     <t>e_w614955993-230_IDN,e_w544403431-230_IDN</t>
   </si>
   <si>
-    <t>e_w340205049-275_IDN,e_w754073846-275_IDN,e_w310958602-275_IDN,e_w754096394-275_IDN,e_w721674155-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w736595653-500_IDN,e_w562061281-275_IDN,e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581232-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581232-275_IDN,e_w544403426-230_IDN,e_w614955993-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w736595653-275_IDN,e_w736595653-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w1193553154-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_ID6-275_IDN,e_ID5-275_IDN,e_ID3-275_IDN,e_w939542521-275_IDN,e_w928928133-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID33-500_IDN,e_w264550744-500_IDN,e_w769617021-500_IDN,e_w314452486-500_IDN,e_ID29-500_IDN,e_w267626657-500_IDN,e_ID31-500_IDN,e_w166633831-500_IDN,e_w689263666-500_IDN</t>
-  </si>
-  <si>
-    <t>e_ID34-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581242-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581242-275_IDN,e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581242-275_IDN,e_w1193553154-275_IDN,e_w615581232-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID1-275_IDN,e_w721674155-275_IDN,e_w340205049-275_IDN,e_w310958602-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w841499143-275_IDN,e_w1312287191-275_IDN,e_w528189342-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581232-275_IDN,e_w544403426-230_IDN</t>
-  </si>
-  <si>
-    <t>e_ID27-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w939542521-275_IDN,e_ID4-275_IDN,e_ID3-275_IDN,e_ID7-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w930719092-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w544403426-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w928220391-275_IDN,e_ID1-275_IDN,e_w721685825-275_IDN,e_w754073846-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID28-500_IDN,e_w562061281-275_IDN,e_ID27-500_IDN,e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403431-230_IDN,e_w614955993-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w759130125-230_IDN,e_ID9-230_IDN</t>
+    <t>distr_wonelc_won_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wonelc_won_IDN_028</t>
@@ -1972,12 +2050,6 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IDN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IDN_002</t>
   </si>
   <si>
@@ -1996,42 +2068,6 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IDN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IDN_030</t>
   </si>
   <si>
@@ -2068,6 +2104,36 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IDN_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IDN_015</t>
   </si>
   <si>
@@ -2092,48 +2158,6 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IDN_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IDN_013</t>
   </si>
   <si>
@@ -2146,28 +2170,67 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IDN_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>elc_won_IDN_001</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_036</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_ID33-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_011</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_025</t>
+  </si>
+  <si>
+    <t>e_w960747902-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_ID29-500_IDN,e_ID28-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_019</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN,e_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_007</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_016</t>
+  </si>
+  <si>
+    <t>e_w931931121-275_IDN,e_w610198177-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_023</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN,e_w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_024</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN,e_w528189342-275_IDN,e_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_032</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_ID27-500_IDN,e_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_031</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_026</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_022</t>
   </si>
   <si>
     <t>elc_won_IDN_028</t>
@@ -2182,9 +2245,6 @@
     <t>elc_won_IDN_005</t>
   </si>
   <si>
-    <t>elc_won_IDN_001</t>
-  </si>
-  <si>
     <t>elc_won_IDN_002</t>
   </si>
   <si>
@@ -2197,39 +2257,6 @@
     <t>elc_won_IDN_009</t>
   </si>
   <si>
-    <t>elc_won_IDN_016</t>
-  </si>
-  <si>
-    <t>e_w931931121-275_IDN,e_w610198177-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_036</t>
-  </si>
-  <si>
-    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_ID33-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_011</t>
-  </si>
-  <si>
-    <t>e_w562061281-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_025</t>
-  </si>
-  <si>
-    <t>e_w960747902-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_ID29-500_IDN,e_ID28-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_019</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN,e_w1193553154-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_007</t>
-  </si>
-  <si>
     <t>elc_won_IDN_030</t>
   </si>
   <si>
@@ -2257,6 +2284,27 @@
     <t>elc_won_IDN_003</t>
   </si>
   <si>
+    <t>elc_won_IDN_033</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_006</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_027</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_021</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_034</t>
+  </si>
+  <si>
+    <t>e_w314452486-500_IDN,e_w629512849-500_IDN,e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
+  </si>
+  <si>
     <t>elc_won_IDN_015</t>
   </si>
   <si>
@@ -2272,39 +2320,6 @@
     <t>elc_won_IDN_018</t>
   </si>
   <si>
-    <t>elc_won_IDN_034</t>
-  </si>
-  <si>
-    <t>e_w314452486-500_IDN,e_w629512849-500_IDN,e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_023</t>
-  </si>
-  <si>
-    <t>e_w841499143-275_IDN,e_w528189342-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_024</t>
-  </si>
-  <si>
-    <t>e_w931931133-275_IDN,e_w528189342-275_IDN,e_w1316876158-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_032</t>
-  </si>
-  <si>
-    <t>e_ID28-500_IDN,e_ID27-500_IDN,e_ID34-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_031</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_026</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_022</t>
-  </si>
-  <si>
     <t>elc_won_IDN_013</t>
   </si>
   <si>
@@ -2314,19 +2329,136 @@
     <t>elc_won_IDN_008</t>
   </si>
   <si>
-    <t>elc_won_IDN_033</t>
-  </si>
-  <si>
-    <t>e_ID38-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_006</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_027</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_021</t>
+    <t>distr_wofelc_wof_IDN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IDN_028</t>
@@ -2341,64 +2473,22 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IDN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
+    <t>distr_wofelc_wof_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IDN_019</t>
@@ -2425,96 +2515,6 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IDN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IDN_029</t>
   </si>
   <si>
@@ -2539,6 +2539,93 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>elc_wof_IDN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_033</t>
+  </si>
+  <si>
+    <t>e_w528189342-275_IDN,e_w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_025</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_026</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_027</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN,e_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_035</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_030</t>
+  </si>
+  <si>
+    <t>e_ID37-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_011</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_009</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_032</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w264550744-500_IDN,e_w161960924-500_IDN,e_ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_031</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_023</t>
+  </si>
+  <si>
+    <t>e_ID27-500_IDN,e_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_034</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_007</t>
+  </si>
+  <si>
     <t>elc_wof_IDN_028</t>
   </si>
   <si>
@@ -2548,37 +2635,13 @@
     <t>elc_wof_IDN_005</t>
   </si>
   <si>
-    <t>elc_wof_IDN_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_014</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_012</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_009</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_030</t>
-  </si>
-  <si>
-    <t>e_ID37-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_011</t>
+    <t>elc_wof_IDN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_016</t>
   </si>
   <si>
     <t>elc_wof_IDN_019</t>
@@ -2591,69 +2654,6 @@
   </si>
   <si>
     <t>elc_wof_IDN_013</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_032</t>
-  </si>
-  <si>
-    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w264550744-500_IDN,e_w161960924-500_IDN,e_ID33-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_031</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_025</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_026</t>
-  </si>
-  <si>
-    <t>e_w928220391-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_027</t>
-  </si>
-  <si>
-    <t>e_w928220391-275_IDN,e_w721685825-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_035</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_034</t>
-  </si>
-  <si>
-    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_023</t>
-  </si>
-  <si>
-    <t>e_ID27-500_IDN,e_ID34-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_033</t>
-  </si>
-  <si>
-    <t>e_w528189342-275_IDN,e_w931931133-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_015</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_016</t>
   </si>
   <si>
     <t>elc_wof_IDN_029</t>
@@ -7943,7 +7943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FAABC3E-5BE9-4145-AA65-2070262E2622}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F93EC2E-C1F3-4476-9D04-EDA8906694C9}">
   <dimension ref="B9:BD84"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8181,16 +8181,16 @@
         <v>403</v>
       </c>
       <c r="Y11" t="s">
-        <v>389</v>
+        <v>343</v>
       </c>
       <c r="Z11" t="s">
         <v>555</v>
       </c>
       <c r="AA11">
-        <v>0.99720517126173747</v>
+        <v>0.9912986266790621</v>
       </c>
       <c r="AB11">
-        <v>51.238526868146437</v>
+        <v>159.52517755052818</v>
       </c>
       <c r="AD11" t="s">
         <v>402</v>
@@ -8220,13 +8220,13 @@
         <v>680</v>
       </c>
       <c r="AN11" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="AO11">
-        <v>0.96732413990250377</v>
+        <v>0.9519359532349716</v>
       </c>
       <c r="AP11">
-        <v>599.05743512076492</v>
+        <v>881.17419069218636</v>
       </c>
       <c r="AR11" t="s">
         <v>402</v>
@@ -8256,13 +8256,13 @@
         <v>803</v>
       </c>
       <c r="BB11" t="s">
-        <v>804</v>
+        <v>561</v>
       </c>
       <c r="BC11">
-        <v>0.98373391026642343</v>
+        <v>0.97600654740978099</v>
       </c>
       <c r="BD11">
-        <v>298.21164511556987</v>
+        <v>439.8799641540142</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8327,16 +8327,16 @@
         <v>407</v>
       </c>
       <c r="Y12" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="Z12" t="s">
         <v>556</v>
       </c>
       <c r="AA12">
-        <v>0.98421229582412162</v>
+        <v>0.99619242046188483</v>
       </c>
       <c r="AB12">
-        <v>289.44124322443668</v>
+        <v>69.805624865443917</v>
       </c>
       <c r="AD12" t="s">
         <v>402</v>
@@ -8369,10 +8369,10 @@
         <v>682</v>
       </c>
       <c r="AO12">
-        <v>0.97419216130718622</v>
+        <v>0.9936518770554722</v>
       </c>
       <c r="AP12">
-        <v>473.14370936825355</v>
+        <v>116.38225398301061</v>
       </c>
       <c r="AR12" t="s">
         <v>402</v>
@@ -8399,16 +8399,16 @@
         <v>735</v>
       </c>
       <c r="BA12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="BB12" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="BC12">
-        <v>0.98908976773019719</v>
+        <v>0.97616044738151031</v>
       </c>
       <c r="BD12">
-        <v>200.02092494638529</v>
+        <v>437.05846467231135</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8473,16 +8473,16 @@
         <v>409</v>
       </c>
       <c r="Y13" t="s">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="Z13" t="s">
         <v>557</v>
       </c>
       <c r="AA13">
-        <v>0.97067956893851193</v>
+        <v>0.96239325925412511</v>
       </c>
       <c r="AB13">
-        <v>537.54123612728188</v>
+        <v>689.45691367437246</v>
       </c>
       <c r="AD13" t="s">
         <v>402</v>
@@ -8512,13 +8512,13 @@
         <v>683</v>
       </c>
       <c r="AN13" t="s">
-        <v>570</v>
+        <v>684</v>
       </c>
       <c r="AO13">
-        <v>0.9784298046188693</v>
+        <v>0.9880111771283725</v>
       </c>
       <c r="AP13">
-        <v>395.45358198739586</v>
+        <v>219.79508597983738</v>
       </c>
       <c r="AR13" t="s">
         <v>402</v>
@@ -8545,16 +8545,16 @@
         <v>737</v>
       </c>
       <c r="BA13" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="BB13" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="BC13">
-        <v>0.97616044738151031</v>
+        <v>0.97829546850421678</v>
       </c>
       <c r="BD13">
-        <v>437.05846467231135</v>
+        <v>397.91641075602604</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8619,16 +8619,16 @@
         <v>411</v>
       </c>
       <c r="Y14" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="Z14" t="s">
         <v>558</v>
       </c>
       <c r="AA14">
-        <v>0.98091465074522166</v>
+        <v>0.95110614119885384</v>
       </c>
       <c r="AB14">
-        <v>349.89806967093693</v>
+        <v>896.38741135434657</v>
       </c>
       <c r="AD14" t="s">
         <v>402</v>
@@ -8655,16 +8655,16 @@
         <v>614</v>
       </c>
       <c r="AM14" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AN14" t="s">
-        <v>606</v>
+        <v>686</v>
       </c>
       <c r="AO14">
-        <v>0.9519359532349716</v>
+        <v>0.99700964975406792</v>
       </c>
       <c r="AP14">
-        <v>881.17419069218636</v>
+        <v>54.823087842088889</v>
       </c>
       <c r="AR14" t="s">
         <v>402</v>
@@ -8691,16 +8691,16 @@
         <v>739</v>
       </c>
       <c r="BA14" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="BB14" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="BC14">
-        <v>0.97829546850421678</v>
+        <v>0.94478739551790969</v>
       </c>
       <c r="BD14">
-        <v>397.91641075602604</v>
+        <v>1012.2310821716558</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8765,16 +8765,16 @@
         <v>413</v>
       </c>
       <c r="Y15" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="Z15" t="s">
         <v>559</v>
       </c>
       <c r="AA15">
-        <v>0.97678876819750537</v>
+        <v>0.98223116847554315</v>
       </c>
       <c r="AB15">
-        <v>425.5392497124015</v>
+        <v>325.76191128170939</v>
       </c>
       <c r="AD15" t="s">
         <v>402</v>
@@ -8801,16 +8801,16 @@
         <v>616</v>
       </c>
       <c r="AM15" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AN15" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AO15">
-        <v>0.96896908104036528</v>
+        <v>0.98325145592799346</v>
       </c>
       <c r="AP15">
-        <v>568.90018092663558</v>
+        <v>307.05664132012055</v>
       </c>
       <c r="AR15" t="s">
         <v>402</v>
@@ -8837,16 +8837,16 @@
         <v>741</v>
       </c>
       <c r="BA15" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="BB15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="BC15">
-        <v>0.94478739551790969</v>
+        <v>0.94491770107559214</v>
       </c>
       <c r="BD15">
-        <v>1012.2310821716558</v>
+        <v>1009.8421469474777</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8911,16 +8911,16 @@
         <v>415</v>
       </c>
       <c r="Y16" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="Z16" t="s">
         <v>560</v>
       </c>
       <c r="AA16">
-        <v>0.98696950091677516</v>
+        <v>0.96710197646129548</v>
       </c>
       <c r="AB16">
-        <v>238.89248319245524</v>
+        <v>603.13043154291677</v>
       </c>
       <c r="AD16" t="s">
         <v>402</v>
@@ -8947,16 +8947,16 @@
         <v>618</v>
       </c>
       <c r="AM16" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AN16" t="s">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="AO16">
-        <v>0.97444089635831932</v>
+        <v>0.95111092756566806</v>
       </c>
       <c r="AP16">
-        <v>468.58356676414513</v>
+        <v>896.29966129608511</v>
       </c>
       <c r="AR16" t="s">
         <v>402</v>
@@ -8983,16 +8983,16 @@
         <v>743</v>
       </c>
       <c r="BA16" t="s">
+        <v>808</v>
+      </c>
+      <c r="BB16" t="s">
         <v>809</v>
       </c>
-      <c r="BB16" t="s">
-        <v>565</v>
-      </c>
       <c r="BC16">
-        <v>0.94491770107559214</v>
+        <v>0.98716759869587867</v>
       </c>
       <c r="BD16">
-        <v>1009.8421469474777</v>
+        <v>235.26069057555824</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>417</v>
       </c>
       <c r="Y17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z17" t="s">
         <v>561</v>
       </c>
       <c r="AA17">
-        <v>0.98568311514415174</v>
+        <v>0.97245598614016138</v>
       </c>
       <c r="AB17">
-        <v>262.47622235721866</v>
+        <v>504.97358743037506</v>
       </c>
       <c r="AD17" t="s">
         <v>402</v>
@@ -9093,16 +9093,16 @@
         <v>620</v>
       </c>
       <c r="AM17" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AN17" t="s">
-        <v>570</v>
+        <v>691</v>
       </c>
       <c r="AO17">
-        <v>0.97186368651165222</v>
+        <v>0.98243109777744309</v>
       </c>
       <c r="AP17">
-        <v>515.83241395304219</v>
+        <v>322.09654074687614</v>
       </c>
       <c r="AR17" t="s">
         <v>402</v>
@@ -9132,13 +9132,13 @@
         <v>810</v>
       </c>
       <c r="BB17" t="s">
-        <v>570</v>
+        <v>602</v>
       </c>
       <c r="BC17">
-        <v>0.96951273706693553</v>
+        <v>0.98584164436602861</v>
       </c>
       <c r="BD17">
-        <v>558.93315377284773</v>
+        <v>259.56985328947479</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9203,16 +9203,16 @@
         <v>419</v>
       </c>
       <c r="Y18" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="Z18" t="s">
         <v>562</v>
       </c>
       <c r="AA18">
-        <v>0.99640865233383846</v>
+        <v>0.97006792991713942</v>
       </c>
       <c r="AB18">
-        <v>65.841373879627454</v>
+        <v>548.75461818577651</v>
       </c>
       <c r="AD18" t="s">
         <v>402</v>
@@ -9239,16 +9239,16 @@
         <v>622</v>
       </c>
       <c r="AM18" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="AN18" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="AO18">
-        <v>0.98243109777744309</v>
+        <v>0.99117435469129123</v>
       </c>
       <c r="AP18">
-        <v>322.09654074687614</v>
+        <v>161.80349732632692</v>
       </c>
       <c r="AR18" t="s">
         <v>402</v>
@@ -9278,13 +9278,13 @@
         <v>811</v>
       </c>
       <c r="BB18" t="s">
-        <v>570</v>
+        <v>812</v>
       </c>
       <c r="BC18">
-        <v>0.97175571177973974</v>
+        <v>0.99498145347305278</v>
       </c>
       <c r="BD18">
-        <v>517.81195070477202</v>
+        <v>92.006686327364918</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9349,16 +9349,16 @@
         <v>421</v>
       </c>
       <c r="Y19" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="Z19" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA19">
-        <v>0.95152672202699851</v>
+        <v>0.99627301415801128</v>
       </c>
       <c r="AB19">
-        <v>888.67676283836079</v>
+        <v>68.328073769792198</v>
       </c>
       <c r="AD19" t="s">
         <v>402</v>
@@ -9385,16 +9385,16 @@
         <v>624</v>
       </c>
       <c r="AM19" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AN19" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AO19">
-        <v>0.9936518770554722</v>
+        <v>0.99101688837209245</v>
       </c>
       <c r="AP19">
-        <v>116.38225398301061</v>
+        <v>164.69037984497118</v>
       </c>
       <c r="AR19" t="s">
         <v>402</v>
@@ -9421,16 +9421,16 @@
         <v>749</v>
       </c>
       <c r="BA19" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="BB19" t="s">
-        <v>570</v>
+        <v>814</v>
       </c>
       <c r="BC19">
-        <v>0.97045263692858041</v>
+        <v>0.98831120739622746</v>
       </c>
       <c r="BD19">
-        <v>541.7016563093581</v>
+        <v>214.2945310691625</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9495,16 +9495,16 @@
         <v>423</v>
       </c>
       <c r="Y20" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="Z20" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA20">
-        <v>0.99439318395533605</v>
+        <v>0.99633073297550734</v>
       </c>
       <c r="AB20">
-        <v>102.7916274855054</v>
+        <v>67.269895449032902</v>
       </c>
       <c r="AD20" t="s">
         <v>402</v>
@@ -9531,16 +9531,16 @@
         <v>626</v>
       </c>
       <c r="AM20" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="AN20" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="AO20">
-        <v>0.9880111771283725</v>
+        <v>0.9755246434835193</v>
       </c>
       <c r="AP20">
-        <v>219.79508597983738</v>
+        <v>448.71486946881294</v>
       </c>
       <c r="AR20" t="s">
         <v>402</v>
@@ -9567,16 +9567,16 @@
         <v>751</v>
       </c>
       <c r="BA20" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="BB20" t="s">
-        <v>578</v>
+        <v>716</v>
       </c>
       <c r="BC20">
-        <v>0.97600654740978099</v>
+        <v>0.99160370033662015</v>
       </c>
       <c r="BD20">
-        <v>439.8799641540142</v>
+        <v>153.93216049529627</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9641,16 +9641,16 @@
         <v>425</v>
       </c>
       <c r="Y21" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="Z21" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA21">
-        <v>0.99770573728283862</v>
+        <v>0.9725266797570975</v>
       </c>
       <c r="AB21">
-        <v>42.061483147959365</v>
+        <v>503.67753778654668</v>
       </c>
       <c r="AD21" t="s">
         <v>402</v>
@@ -9677,16 +9677,16 @@
         <v>628</v>
       </c>
       <c r="AM21" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="AN21" t="s">
-        <v>696</v>
+        <v>561</v>
       </c>
       <c r="AO21">
-        <v>0.99700964975406792</v>
+        <v>0.9574422475745189</v>
       </c>
       <c r="AP21">
-        <v>54.823087842088889</v>
+        <v>780.22546113382077</v>
       </c>
       <c r="AR21" t="s">
         <v>402</v>
@@ -9713,10 +9713,10 @@
         <v>753</v>
       </c>
       <c r="BA21" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="BB21" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="BC21">
         <v>0.99036076428701636</v>
@@ -9787,16 +9787,16 @@
         <v>427</v>
       </c>
       <c r="Y22" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="Z22" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="AA22">
-        <v>0.99118992399256634</v>
+        <v>0.98696950091677516</v>
       </c>
       <c r="AB22">
-        <v>161.51806013628308</v>
+        <v>238.89248319245524</v>
       </c>
       <c r="AD22" t="s">
         <v>402</v>
@@ -9823,16 +9823,16 @@
         <v>630</v>
       </c>
       <c r="AM22" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AN22" t="s">
-        <v>698</v>
+        <v>567</v>
       </c>
       <c r="AO22">
-        <v>0.98325145592799346</v>
+        <v>0.97673972771258222</v>
       </c>
       <c r="AP22">
-        <v>307.05664132012055</v>
+        <v>426.43832526932584</v>
       </c>
       <c r="AR22" t="s">
         <v>402</v>
@@ -9859,10 +9859,10 @@
         <v>755</v>
       </c>
       <c r="BA22" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="BB22" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="BC22">
         <v>0.98102590217137298</v>
@@ -9933,16 +9933,16 @@
         <v>429</v>
       </c>
       <c r="Y23" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="Z23" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AA23">
-        <v>0.9582992451809369</v>
+        <v>0.98568311514415174</v>
       </c>
       <c r="AB23">
-        <v>764.51383834949013</v>
+        <v>262.47622235721866</v>
       </c>
       <c r="AD23" t="s">
         <v>402</v>
@@ -9969,16 +9969,16 @@
         <v>632</v>
       </c>
       <c r="AM23" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AN23" t="s">
-        <v>600</v>
+        <v>557</v>
       </c>
       <c r="AO23">
-        <v>0.95111092756566806</v>
+        <v>0.95686428742271346</v>
       </c>
       <c r="AP23">
-        <v>896.29966129608511</v>
+        <v>790.82139725025399</v>
       </c>
       <c r="AR23" t="s">
         <v>402</v>
@@ -10005,16 +10005,16 @@
         <v>757</v>
       </c>
       <c r="BA23" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="BB23" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="BC23">
-        <v>0.96625736872930745</v>
+        <v>0.96951273706693553</v>
       </c>
       <c r="BD23">
-        <v>618.61490662936239</v>
+        <v>558.93315377284773</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10079,16 +10079,16 @@
         <v>431</v>
       </c>
       <c r="Y24" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="Z24" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AA24">
-        <v>0.95289359663592565</v>
+        <v>0.99640865233383846</v>
       </c>
       <c r="AB24">
-        <v>863.61739500803003</v>
+        <v>65.841373879627454</v>
       </c>
       <c r="AD24" t="s">
         <v>402</v>
@@ -10115,16 +10115,16 @@
         <v>634</v>
       </c>
       <c r="AM24" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AN24" t="s">
-        <v>701</v>
+        <v>561</v>
       </c>
       <c r="AO24">
-        <v>0.97532618723790843</v>
+        <v>0.96732413990250377</v>
       </c>
       <c r="AP24">
-        <v>452.35323397167849</v>
+        <v>599.05743512076492</v>
       </c>
       <c r="AR24" t="s">
         <v>402</v>
@@ -10151,16 +10151,16 @@
         <v>759</v>
       </c>
       <c r="BA24" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="BB24" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="BC24">
-        <v>0.93693021635476914</v>
+        <v>0.97175571177973974</v>
       </c>
       <c r="BD24">
-        <v>1156.2793668292329</v>
+        <v>517.81195070477202</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10225,16 +10225,16 @@
         <v>433</v>
       </c>
       <c r="Y25" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="Z25" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA25">
-        <v>0.97577723283636553</v>
+        <v>0.95152672202699851</v>
       </c>
       <c r="AB25">
-        <v>444.08406466663115</v>
+        <v>888.67676283836079</v>
       </c>
       <c r="AD25" t="s">
         <v>402</v>
@@ -10264,13 +10264,13 @@
         <v>702</v>
       </c>
       <c r="AN25" t="s">
-        <v>587</v>
+        <v>703</v>
       </c>
       <c r="AO25">
-        <v>0.97755933784246885</v>
+        <v>0.97419216130718622</v>
       </c>
       <c r="AP25">
-        <v>411.4121395547387</v>
+        <v>473.14370936825355</v>
       </c>
       <c r="AR25" t="s">
         <v>402</v>
@@ -10297,16 +10297,16 @@
         <v>761</v>
       </c>
       <c r="BA25" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="BB25" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="BC25">
-        <v>0.94041102627936679</v>
+        <v>0.97045263692858041</v>
       </c>
       <c r="BD25">
-        <v>1092.4645182116094</v>
+        <v>541.7016563093581</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10371,16 +10371,16 @@
         <v>435</v>
       </c>
       <c r="Y26" t="s">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="Z26" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA26">
-        <v>0.98985535554561865</v>
+        <v>0.99439318395533605</v>
       </c>
       <c r="AB26">
-        <v>185.9851483303255</v>
+        <v>102.7916274855054</v>
       </c>
       <c r="AD26" t="s">
         <v>402</v>
@@ -10407,16 +10407,16 @@
         <v>638</v>
       </c>
       <c r="AM26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AN26" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="AO26">
-        <v>0.97739363651485267</v>
+        <v>0.9784298046188693</v>
       </c>
       <c r="AP26">
-        <v>414.44999722770137</v>
+        <v>395.45358198739586</v>
       </c>
       <c r="AR26" t="s">
         <v>402</v>
@@ -10443,16 +10443,16 @@
         <v>763</v>
       </c>
       <c r="BA26" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="BB26" t="s">
-        <v>570</v>
+        <v>823</v>
       </c>
       <c r="BC26">
-        <v>0.95063651087703893</v>
+        <v>0.99286819499076961</v>
       </c>
       <c r="BD26">
-        <v>904.99730058761952</v>
+        <v>130.7497585025562</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10517,16 +10517,16 @@
         <v>437</v>
       </c>
       <c r="Y27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z27" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA27">
-        <v>0.96781787899545535</v>
+        <v>0.99690816609326338</v>
       </c>
       <c r="AB27">
-        <v>590.00555174998567</v>
+        <v>56.683621623505239</v>
       </c>
       <c r="AD27" t="s">
         <v>402</v>
@@ -10553,16 +10553,16 @@
         <v>640</v>
       </c>
       <c r="AM27" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AN27" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AO27">
-        <v>0.98921594161489768</v>
+        <v>0.96896908104036528</v>
       </c>
       <c r="AP27">
-        <v>197.70773706020898</v>
+        <v>568.90018092663558</v>
       </c>
       <c r="AR27" t="s">
         <v>402</v>
@@ -10589,16 +10589,16 @@
         <v>765</v>
       </c>
       <c r="BA27" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="BB27" t="s">
-        <v>822</v>
+        <v>557</v>
       </c>
       <c r="BC27">
-        <v>0.99286819499076961</v>
+        <v>0.93888082510661108</v>
       </c>
       <c r="BD27">
-        <v>130.7497585025562</v>
+        <v>1120.5182063787968</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10663,16 +10663,16 @@
         <v>439</v>
       </c>
       <c r="Y28" t="s">
-        <v>399</v>
+        <v>333</v>
       </c>
       <c r="Z28" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA28">
-        <v>0.97597719784352066</v>
+        <v>0.97592802238295073</v>
       </c>
       <c r="AB28">
-        <v>440.41803953545457</v>
+        <v>441.3195896459041</v>
       </c>
       <c r="AD28" t="s">
         <v>402</v>
@@ -10699,16 +10699,16 @@
         <v>642</v>
       </c>
       <c r="AM28" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AN28" t="s">
-        <v>707</v>
+        <v>590</v>
       </c>
       <c r="AO28">
-        <v>0.99552970818146125</v>
+        <v>0.97444089635831932</v>
       </c>
       <c r="AP28">
-        <v>81.955350006543654</v>
+        <v>468.58356676414513</v>
       </c>
       <c r="AR28" t="s">
         <v>402</v>
@@ -10735,16 +10735,16 @@
         <v>767</v>
       </c>
       <c r="BA28" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="BB28" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="BC28">
-        <v>0.93888082510661108</v>
+        <v>0.96620229207214314</v>
       </c>
       <c r="BD28">
-        <v>1120.5182063787968</v>
+        <v>619.62464534404216</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10809,16 +10809,16 @@
         <v>441</v>
       </c>
       <c r="Y29" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="Z29" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="AA29">
-        <v>0.99660643716165165</v>
+        <v>0.97807026787476981</v>
       </c>
       <c r="AB29">
-        <v>62.215318703052311</v>
+        <v>402.04508896255408</v>
       </c>
       <c r="AD29" t="s">
         <v>402</v>
@@ -10848,13 +10848,13 @@
         <v>708</v>
       </c>
       <c r="AN29" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="AO29">
-        <v>0.95419187641353731</v>
+        <v>0.97186368651165222</v>
       </c>
       <c r="AP29">
-        <v>839.81559908514964</v>
+        <v>515.83241395304219</v>
       </c>
       <c r="AR29" t="s">
         <v>402</v>
@@ -10881,16 +10881,16 @@
         <v>769</v>
       </c>
       <c r="BA29" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="BB29" t="s">
-        <v>594</v>
+        <v>827</v>
       </c>
       <c r="BC29">
-        <v>0.98584164436602861</v>
+        <v>0.98770095291302495</v>
       </c>
       <c r="BD29">
-        <v>259.56985328947479</v>
+        <v>225.48252992787681</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10955,16 +10955,16 @@
         <v>443</v>
       </c>
       <c r="Y30" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="Z30" t="s">
         <v>572</v>
       </c>
       <c r="AA30">
-        <v>0.98786674666740726</v>
+        <v>0.96276589991882666</v>
       </c>
       <c r="AB30">
-        <v>222.44297776420015</v>
+        <v>682.62516815484491</v>
       </c>
       <c r="AD30" t="s">
         <v>402</v>
@@ -10994,13 +10994,13 @@
         <v>709</v>
       </c>
       <c r="AN30" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="AO30">
-        <v>0.98177850613436324</v>
+        <v>0.97532618723790843</v>
       </c>
       <c r="AP30">
-        <v>334.06072087000706</v>
+        <v>452.35323397167849</v>
       </c>
       <c r="AR30" t="s">
         <v>402</v>
@@ -11027,16 +11027,16 @@
         <v>771</v>
       </c>
       <c r="BA30" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="BB30" t="s">
-        <v>826</v>
+        <v>575</v>
       </c>
       <c r="BC30">
-        <v>0.99498145347305278</v>
+        <v>0.9602868544779749</v>
       </c>
       <c r="BD30">
-        <v>92.006686327364918</v>
+        <v>728.07433457046079</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11101,16 +11101,16 @@
         <v>445</v>
       </c>
       <c r="Y31" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="Z31" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="AA31">
-        <v>0.99400218125602058</v>
+        <v>0.98628621327161703</v>
       </c>
       <c r="AB31">
-        <v>109.96001030628999</v>
+        <v>251.41942335368827</v>
       </c>
       <c r="AD31" t="s">
         <v>402</v>
@@ -11137,16 +11137,16 @@
         <v>648</v>
       </c>
       <c r="AM31" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AN31" t="s">
-        <v>711</v>
+        <v>591</v>
       </c>
       <c r="AO31">
-        <v>0.98895557240687315</v>
+        <v>0.97755933784246885</v>
       </c>
       <c r="AP31">
-        <v>202.48117254065832</v>
+        <v>411.4121395547387</v>
       </c>
       <c r="AR31" t="s">
         <v>402</v>
@@ -11173,16 +11173,16 @@
         <v>773</v>
       </c>
       <c r="BA31" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="BB31" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="BC31">
-        <v>0.98831120739622746</v>
+        <v>0.98529032090802915</v>
       </c>
       <c r="BD31">
-        <v>214.2945310691625</v>
+        <v>269.67745001946554</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11247,16 +11247,16 @@
         <v>447</v>
       </c>
       <c r="Y32" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="Z32" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AA32">
-        <v>0.99624827768323054</v>
+        <v>0.98392857039426507</v>
       </c>
       <c r="AB32">
-        <v>68.781575807440518</v>
+        <v>294.64287610514066</v>
       </c>
       <c r="AD32" t="s">
         <v>402</v>
@@ -11286,13 +11286,13 @@
         <v>712</v>
       </c>
       <c r="AN32" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AO32">
-        <v>0.95753456607285348</v>
+        <v>0.97739363651485267</v>
       </c>
       <c r="AP32">
-        <v>778.53295533101902</v>
+        <v>414.44999722770137</v>
       </c>
       <c r="AR32" t="s">
         <v>402</v>
@@ -11319,16 +11319,16 @@
         <v>775</v>
       </c>
       <c r="BA32" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="BB32" t="s">
-        <v>707</v>
+        <v>575</v>
       </c>
       <c r="BC32">
-        <v>0.99160370033662015</v>
+        <v>0.96834660314974419</v>
       </c>
       <c r="BD32">
-        <v>153.93216049529627</v>
+        <v>580.31227558802345</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11393,16 +11393,16 @@
         <v>449</v>
       </c>
       <c r="Y33" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="Z33" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="AA33">
-        <v>0.98654011406382824</v>
+        <v>0.98985535554561865</v>
       </c>
       <c r="AB33">
-        <v>246.76457549648219</v>
+        <v>185.9851483303255</v>
       </c>
       <c r="AD33" t="s">
         <v>402</v>
@@ -11432,13 +11432,13 @@
         <v>713</v>
       </c>
       <c r="AN33" t="s">
-        <v>576</v>
+        <v>714</v>
       </c>
       <c r="AO33">
-        <v>0.94698201881115829</v>
+        <v>0.98921594161489768</v>
       </c>
       <c r="AP33">
-        <v>971.99632179543119</v>
+        <v>197.70773706020898</v>
       </c>
       <c r="AR33" t="s">
         <v>402</v>
@@ -11465,16 +11465,16 @@
         <v>777</v>
       </c>
       <c r="BA33" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="BB33" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="BC33">
-        <v>0.98529032090802915</v>
+        <v>0.98373391026642343</v>
       </c>
       <c r="BD33">
-        <v>269.67745001946554</v>
+        <v>298.21164511556987</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11539,16 +11539,16 @@
         <v>451</v>
       </c>
       <c r="Y34" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="Z34" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AA34">
-        <v>0.97006538483877391</v>
+        <v>0.96781787899545535</v>
       </c>
       <c r="AB34">
-        <v>548.80127795581154</v>
+        <v>590.00555174998567</v>
       </c>
       <c r="AD34" t="s">
         <v>402</v>
@@ -11575,16 +11575,16 @@
         <v>654</v>
       </c>
       <c r="AM34" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AN34" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AO34">
-        <v>0.99557021775830368</v>
+        <v>0.99552970818146125</v>
       </c>
       <c r="AP34">
-        <v>81.21267443109943</v>
+        <v>81.955350006543654</v>
       </c>
       <c r="AR34" t="s">
         <v>402</v>
@@ -11611,16 +11611,16 @@
         <v>779</v>
       </c>
       <c r="BA34" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="BB34" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="BC34">
-        <v>0.96834660314974419</v>
+        <v>0.98908976773019719</v>
       </c>
       <c r="BD34">
-        <v>580.31227558802345</v>
+        <v>200.02092494638529</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11685,16 +11685,16 @@
         <v>453</v>
       </c>
       <c r="Y35" t="s">
-        <v>337</v>
+        <v>399</v>
       </c>
       <c r="Z35" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AA35">
-        <v>0.96710197646129548</v>
+        <v>0.97597719784352066</v>
       </c>
       <c r="AB35">
-        <v>603.13043154291677</v>
+        <v>440.41803953545457</v>
       </c>
       <c r="AD35" t="s">
         <v>402</v>
@@ -11721,16 +11721,16 @@
         <v>656</v>
       </c>
       <c r="AM35" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AN35" t="s">
-        <v>717</v>
+        <v>562</v>
       </c>
       <c r="AO35">
-        <v>0.99117435469129123</v>
+        <v>0.95419187641353731</v>
       </c>
       <c r="AP35">
-        <v>161.80349732632692</v>
+        <v>839.81559908514964</v>
       </c>
       <c r="AR35" t="s">
         <v>402</v>
@@ -11757,16 +11757,16 @@
         <v>781</v>
       </c>
       <c r="BA35" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="BB35" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="BC35">
-        <v>0.96620229207214314</v>
+        <v>0.93477394593085072</v>
       </c>
       <c r="BD35">
-        <v>619.62464534404216</v>
+        <v>1195.8109912677364</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11831,16 +11831,16 @@
         <v>455</v>
       </c>
       <c r="Y36" t="s">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="Z36" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AA36">
-        <v>0.97245598614016138</v>
+        <v>0.96517074323544272</v>
       </c>
       <c r="AB36">
-        <v>504.97358743037506</v>
+        <v>638.53637401688275</v>
       </c>
       <c r="AD36" t="s">
         <v>402</v>
@@ -11873,10 +11873,10 @@
         <v>719</v>
       </c>
       <c r="AO36">
-        <v>0.99101688837209245</v>
+        <v>0.97905895332023074</v>
       </c>
       <c r="AP36">
-        <v>164.69037984497118</v>
+        <v>383.91918912910296</v>
       </c>
       <c r="AR36" t="s">
         <v>402</v>
@@ -11903,16 +11903,16 @@
         <v>783</v>
       </c>
       <c r="BA36" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="BB36" t="s">
-        <v>835</v>
+        <v>562</v>
       </c>
       <c r="BC36">
-        <v>0.98770095291302495</v>
+        <v>0.95614590843046721</v>
       </c>
       <c r="BD36">
-        <v>225.48252992787681</v>
+        <v>803.99167877476805</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11977,16 +11977,16 @@
         <v>457</v>
       </c>
       <c r="Y37" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="Z37" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="AA37">
-        <v>0.97006792991713942</v>
+        <v>0.9771016434875236</v>
       </c>
       <c r="AB37">
-        <v>548.75461818577651</v>
+        <v>419.80320272873433</v>
       </c>
       <c r="AD37" t="s">
         <v>402</v>
@@ -12016,13 +12016,13 @@
         <v>720</v>
       </c>
       <c r="AN37" t="s">
-        <v>721</v>
+        <v>567</v>
       </c>
       <c r="AO37">
-        <v>0.9755246434835193</v>
+        <v>0.94748255895881095</v>
       </c>
       <c r="AP37">
-        <v>448.71486946881294</v>
+        <v>962.81975242179908</v>
       </c>
       <c r="AR37" t="s">
         <v>402</v>
@@ -12049,16 +12049,16 @@
         <v>785</v>
       </c>
       <c r="BA37" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="BB37" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="BC37">
-        <v>0.9602868544779749</v>
+        <v>0.95197431053166182</v>
       </c>
       <c r="BD37">
-        <v>728.07433457046079</v>
+        <v>880.47097358620078</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12123,16 +12123,16 @@
         <v>459</v>
       </c>
       <c r="Y38" t="s">
-        <v>342</v>
+        <v>389</v>
       </c>
       <c r="Z38" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AA38">
-        <v>0.98903719509068366</v>
+        <v>0.99720517126173747</v>
       </c>
       <c r="AB38">
-        <v>200.98475667080021</v>
+        <v>51.238526868146437</v>
       </c>
       <c r="AD38" t="s">
         <v>402</v>
@@ -12159,16 +12159,16 @@
         <v>662</v>
       </c>
       <c r="AM38" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AN38" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="AO38">
-        <v>0.9574422475745189</v>
+        <v>0.95796808346245155</v>
       </c>
       <c r="AP38">
-        <v>780.22546113382077</v>
+        <v>770.58513652172257</v>
       </c>
       <c r="AR38" t="s">
         <v>402</v>
@@ -12195,16 +12195,16 @@
         <v>787</v>
       </c>
       <c r="BA38" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="BB38" t="s">
-        <v>838</v>
+        <v>564</v>
       </c>
       <c r="BC38">
-        <v>0.98716759869587867</v>
+        <v>0.96625736872930745</v>
       </c>
       <c r="BD38">
-        <v>235.26069057555824</v>
+        <v>618.61490662936239</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12269,16 +12269,16 @@
         <v>461</v>
       </c>
       <c r="Y39" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="Z39" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AA39">
-        <v>0.9966278856580183</v>
+        <v>0.98421229582412162</v>
       </c>
       <c r="AB39">
-        <v>61.822096269664314</v>
+        <v>289.44124322443668</v>
       </c>
       <c r="AD39" t="s">
         <v>402</v>
@@ -12305,16 +12305,16 @@
         <v>664</v>
       </c>
       <c r="AM39" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AN39" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AO39">
-        <v>0.97673972771258222</v>
+        <v>0.9436975669946106</v>
       </c>
       <c r="AP39">
-        <v>426.43832526932584</v>
+        <v>1032.2112717654718</v>
       </c>
       <c r="AR39" t="s">
         <v>402</v>
@@ -12344,13 +12344,13 @@
         <v>839</v>
       </c>
       <c r="BB39" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="BC39">
-        <v>0.93477394593085072</v>
+        <v>0.93693021635476914</v>
       </c>
       <c r="BD39">
-        <v>1195.8109912677364</v>
+        <v>1156.2793668292329</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12415,16 +12415,16 @@
         <v>463</v>
       </c>
       <c r="Y40" t="s">
-        <v>388</v>
+        <v>332</v>
       </c>
       <c r="Z40" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="AA40">
-        <v>0.99689080338218783</v>
+        <v>0.97067956893851193</v>
       </c>
       <c r="AB40">
-        <v>57.001937993222221</v>
+        <v>537.54123612728188</v>
       </c>
       <c r="AD40" t="s">
         <v>402</v>
@@ -12451,16 +12451,16 @@
         <v>666</v>
       </c>
       <c r="AM40" t="s">
+        <v>723</v>
+      </c>
+      <c r="AN40" t="s">
         <v>724</v>
       </c>
-      <c r="AN40" t="s">
-        <v>576</v>
-      </c>
       <c r="AO40">
-        <v>0.95686428742271346</v>
+        <v>0.99557021775830368</v>
       </c>
       <c r="AP40">
-        <v>790.82139725025399</v>
+        <v>81.21267443109943</v>
       </c>
       <c r="AR40" t="s">
         <v>402</v>
@@ -12490,13 +12490,13 @@
         <v>840</v>
       </c>
       <c r="BB40" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="BC40">
-        <v>0.95614590843046721</v>
+        <v>0.94041102627936679</v>
       </c>
       <c r="BD40">
-        <v>803.99167877476805</v>
+        <v>1092.4645182116094</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12561,16 +12561,16 @@
         <v>465</v>
       </c>
       <c r="Y41" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="Z41" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="AA41">
-        <v>0.98451878015346617</v>
+        <v>0.98091465074522166</v>
       </c>
       <c r="AB41">
-        <v>283.82236385312052</v>
+        <v>349.89806967093693</v>
       </c>
       <c r="AD41" t="s">
         <v>402</v>
@@ -12600,13 +12600,13 @@
         <v>725</v>
       </c>
       <c r="AN41" t="s">
-        <v>726</v>
+        <v>684</v>
       </c>
       <c r="AO41">
-        <v>0.98221507709655431</v>
+        <v>0.98177850613436324</v>
       </c>
       <c r="AP41">
-        <v>326.05691989650336</v>
+        <v>334.06072087000706</v>
       </c>
       <c r="AR41" t="s">
         <v>402</v>
@@ -12636,13 +12636,13 @@
         <v>841</v>
       </c>
       <c r="BB41" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="BC41">
-        <v>0.95197431053166182</v>
+        <v>0.95063651087703893</v>
       </c>
       <c r="BD41">
-        <v>880.47097358620078</v>
+        <v>904.99730058761952</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12707,16 +12707,16 @@
         <v>467</v>
       </c>
       <c r="Y42" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Z42" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="AA42">
-        <v>0.9956937957649058</v>
+        <v>0.97678876819750537</v>
       </c>
       <c r="AB42">
-        <v>78.947077643392717</v>
+        <v>425.5392497124015</v>
       </c>
       <c r="AD42" t="s">
         <v>402</v>
@@ -12743,16 +12743,16 @@
         <v>670</v>
       </c>
       <c r="AM42" t="s">
+        <v>726</v>
+      </c>
+      <c r="AN42" t="s">
         <v>727</v>
       </c>
-      <c r="AN42" t="s">
-        <v>558</v>
-      </c>
       <c r="AO42">
-        <v>0.98026073113098933</v>
+        <v>0.98895557240687315</v>
       </c>
       <c r="AP42">
-        <v>361.88659593186213</v>
+        <v>202.48117254065832</v>
       </c>
       <c r="AR42" t="s">
         <v>402</v>
@@ -12853,16 +12853,16 @@
         <v>469</v>
       </c>
       <c r="Y43" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="Z43" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="AA43">
-        <v>0.99635032886115649</v>
+        <v>0.99660643716165165</v>
       </c>
       <c r="AB43">
-        <v>66.910637545464084</v>
+        <v>62.215318703052311</v>
       </c>
       <c r="AD43" t="s">
         <v>402</v>
@@ -12892,13 +12892,13 @@
         <v>728</v>
       </c>
       <c r="AN43" t="s">
-        <v>729</v>
+        <v>557</v>
       </c>
       <c r="AO43">
-        <v>0.97905895332023074</v>
+        <v>0.95753456607285348</v>
       </c>
       <c r="AP43">
-        <v>383.91918912910296</v>
+        <v>778.53295533101902</v>
       </c>
       <c r="AR43" t="s">
         <v>402</v>
@@ -12928,7 +12928,7 @@
         <v>844</v>
       </c>
       <c r="BB43" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="BC43">
         <v>0.94896692115877124</v>
@@ -12999,16 +12999,16 @@
         <v>471</v>
       </c>
       <c r="Y44" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="Z44" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AA44">
-        <v>0.98520673013262905</v>
+        <v>0.98786674666740726</v>
       </c>
       <c r="AB44">
-        <v>271.20994756846727</v>
+        <v>222.44297776420015</v>
       </c>
       <c r="AD44" t="s">
         <v>402</v>
@@ -13035,16 +13035,16 @@
         <v>674</v>
       </c>
       <c r="AM44" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AN44" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AO44">
-        <v>0.94748255895881095</v>
+        <v>0.94698201881115829</v>
       </c>
       <c r="AP44">
-        <v>962.81975242179908</v>
+        <v>971.99632179543119</v>
       </c>
       <c r="AR44" t="s">
         <v>402</v>
@@ -13074,7 +13074,7 @@
         <v>845</v>
       </c>
       <c r="BB44" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="BC44">
         <v>0.93885489623641283</v>
@@ -13145,16 +13145,16 @@
         <v>473</v>
       </c>
       <c r="Y45" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Z45" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AA45">
-        <v>0.99719604020926056</v>
+        <v>0.99400218125602058</v>
       </c>
       <c r="AB45">
-        <v>51.405929496890515</v>
+        <v>109.96001030628999</v>
       </c>
       <c r="AD45" t="s">
         <v>402</v>
@@ -13181,16 +13181,16 @@
         <v>676</v>
       </c>
       <c r="AM45" t="s">
+        <v>730</v>
+      </c>
+      <c r="AN45" t="s">
         <v>731</v>
       </c>
-      <c r="AN45" t="s">
-        <v>561</v>
-      </c>
       <c r="AO45">
-        <v>0.95796808346245155</v>
+        <v>0.98221507709655431</v>
       </c>
       <c r="AP45">
-        <v>770.58513652172257</v>
+        <v>326.05691989650336</v>
       </c>
       <c r="AR45" t="s">
         <v>402</v>
@@ -13220,7 +13220,7 @@
         <v>846</v>
       </c>
       <c r="BB45" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="BC45">
         <v>0.96587851707660599</v>
@@ -13291,16 +13291,16 @@
         <v>475</v>
       </c>
       <c r="Y46" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="Z46" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AA46">
-        <v>0.9791414671967239</v>
+        <v>0.99624827768323054</v>
       </c>
       <c r="AB46">
-        <v>382.40643472672787</v>
+        <v>68.781575807440518</v>
       </c>
       <c r="AD46" t="s">
         <v>402</v>
@@ -13330,13 +13330,13 @@
         <v>732</v>
       </c>
       <c r="AN46" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="AO46">
-        <v>0.9436975669946106</v>
+        <v>0.98026073113098933</v>
       </c>
       <c r="AP46">
-        <v>1032.2112717654718</v>
+        <v>361.88659593186213</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13401,16 +13401,16 @@
         <v>477</v>
       </c>
       <c r="Y47" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="Z47" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AA47">
-        <v>0.98267907851268621</v>
+        <v>0.98654011406382824</v>
       </c>
       <c r="AB47">
-        <v>317.55022726741913</v>
+        <v>246.76457549648219</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13475,16 +13475,16 @@
         <v>479</v>
       </c>
       <c r="Y48" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="Z48" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="AA48">
-        <v>0.94688476071898231</v>
+        <v>0.97006538483877391</v>
       </c>
       <c r="AB48">
-        <v>973.77938681865817</v>
+        <v>548.80127795581154</v>
       </c>
     </row>
     <row r="49" spans="2:28">
@@ -13549,16 +13549,16 @@
         <v>481</v>
       </c>
       <c r="Y49" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="Z49" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="AA49">
-        <v>0.95227568919833094</v>
+        <v>0.98903719509068366</v>
       </c>
       <c r="AB49">
-        <v>874.94569803060017</v>
+        <v>200.98475667080021</v>
       </c>
     </row>
     <row r="50" spans="2:28">
@@ -13623,16 +13623,16 @@
         <v>483</v>
       </c>
       <c r="Y50" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="Z50" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AA50">
-        <v>0.99017812457307008</v>
+        <v>0.9966278856580183</v>
       </c>
       <c r="AB50">
-        <v>180.06771616038245</v>
+        <v>61.822096269664314</v>
       </c>
     </row>
     <row r="51" spans="2:28">
@@ -13697,16 +13697,16 @@
         <v>485</v>
       </c>
       <c r="Y51" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="Z51" t="s">
-        <v>558</v>
+        <v>587</v>
       </c>
       <c r="AA51">
-        <v>0.99088855789814245</v>
+        <v>0.99689080338218783</v>
       </c>
       <c r="AB51">
-        <v>167.04310520072229</v>
+        <v>57.001937993222221</v>
       </c>
     </row>
     <row r="52" spans="2:28">
@@ -13771,16 +13771,16 @@
         <v>487</v>
       </c>
       <c r="Y52" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="Z52" t="s">
-        <v>590</v>
+        <v>557</v>
       </c>
       <c r="AA52">
-        <v>0.9944769137527022</v>
+        <v>0.98451878015346617</v>
       </c>
       <c r="AB52">
-        <v>101.25658120045976</v>
+        <v>283.82236385312052</v>
       </c>
     </row>
     <row r="53" spans="2:28">
@@ -13845,16 +13845,16 @@
         <v>489</v>
       </c>
       <c r="Y53" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="Z53" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="AA53">
-        <v>0.96493395982863905</v>
+        <v>0.9956937957649058</v>
       </c>
       <c r="AB53">
-        <v>642.87740314161726</v>
+        <v>78.947077643392717</v>
       </c>
     </row>
     <row r="54" spans="2:28">
@@ -13919,16 +13919,16 @@
         <v>491</v>
       </c>
       <c r="Y54" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="Z54" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AA54">
-        <v>0.99218536928207235</v>
+        <v>0.99719604020926056</v>
       </c>
       <c r="AB54">
-        <v>143.26822982867444</v>
+        <v>51.405929496890515</v>
       </c>
     </row>
     <row r="55" spans="2:28">
@@ -13993,16 +13993,16 @@
         <v>493</v>
       </c>
       <c r="Y55" t="s">
-        <v>379</v>
+        <v>327</v>
       </c>
       <c r="Z55" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="AA55">
-        <v>0.99332429446553039</v>
+        <v>0.9791414671967239</v>
       </c>
       <c r="AB55">
-        <v>122.38793479860949</v>
+        <v>382.40643472672787</v>
       </c>
     </row>
     <row r="56" spans="2:28">
@@ -14067,16 +14067,16 @@
         <v>495</v>
       </c>
       <c r="Y56" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="Z56" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AA56">
-        <v>0.99496216240453639</v>
+        <v>0.98267907851268621</v>
       </c>
       <c r="AB56">
-        <v>92.360355916833001</v>
+        <v>317.55022726741913</v>
       </c>
     </row>
     <row r="57" spans="2:28">
@@ -14141,16 +14141,16 @@
         <v>497</v>
       </c>
       <c r="Y57" t="s">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="Z57" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="AA57">
-        <v>0.97702953960894623</v>
+        <v>0.94688476071898231</v>
       </c>
       <c r="AB57">
-        <v>421.12510716931934</v>
+        <v>973.77938681865817</v>
       </c>
     </row>
     <row r="58" spans="2:28">
@@ -14215,16 +14215,16 @@
         <v>499</v>
       </c>
       <c r="Y58" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="Z58" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="AA58">
-        <v>0.98631766623578765</v>
+        <v>0.95227568919833094</v>
       </c>
       <c r="AB58">
-        <v>250.84278567722609</v>
+        <v>874.94569803060017</v>
       </c>
     </row>
     <row r="59" spans="2:28">
@@ -14289,16 +14289,16 @@
         <v>501</v>
       </c>
       <c r="Y59" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="Z59" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="AA59">
-        <v>0.96912603699420019</v>
+        <v>0.99017812457307008</v>
       </c>
       <c r="AB59">
-        <v>566.02265510632935</v>
+        <v>180.06771616038245</v>
       </c>
     </row>
     <row r="60" spans="2:28">
@@ -14363,16 +14363,16 @@
         <v>503</v>
       </c>
       <c r="Y60" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="Z60" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="AA60">
-        <v>0.99620173788084643</v>
+        <v>0.99088855789814245</v>
       </c>
       <c r="AB60">
-        <v>69.634805517815565</v>
+        <v>167.04310520072229</v>
       </c>
     </row>
     <row r="61" spans="2:28">
@@ -14437,16 +14437,16 @@
         <v>505</v>
       </c>
       <c r="Y61" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="Z61" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA61">
-        <v>0.99808042106452499</v>
+        <v>0.9944769137527022</v>
       </c>
       <c r="AB61">
-        <v>35.192280483708828</v>
+        <v>101.25658120045976</v>
       </c>
     </row>
     <row r="62" spans="2:28">
@@ -14511,16 +14511,16 @@
         <v>507</v>
       </c>
       <c r="Y62" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="Z62" t="s">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="AA62">
-        <v>0.99235892038811246</v>
+        <v>0.96493395982863905</v>
       </c>
       <c r="AB62">
-        <v>140.08645955127213</v>
+        <v>642.87740314161726</v>
       </c>
     </row>
     <row r="63" spans="2:28">
@@ -14585,16 +14585,16 @@
         <v>509</v>
       </c>
       <c r="Y63" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="Z63" t="s">
         <v>595</v>
       </c>
       <c r="AA63">
-        <v>0.97311459430172587</v>
+        <v>0.99218536928207235</v>
       </c>
       <c r="AB63">
-        <v>492.8991044683591</v>
+        <v>143.26822982867444</v>
       </c>
     </row>
     <row r="64" spans="2:28">
@@ -14659,16 +14659,16 @@
         <v>511</v>
       </c>
       <c r="Y64" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Z64" t="s">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="AA64">
-        <v>0.95854557991594525</v>
+        <v>0.99332429446553039</v>
       </c>
       <c r="AB64">
-        <v>759.99770154100372</v>
+        <v>122.38793479860949</v>
       </c>
     </row>
     <row r="65" spans="2:28">
@@ -14733,16 +14733,16 @@
         <v>513</v>
       </c>
       <c r="Y65" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="Z65" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="AA65">
-        <v>0.98524310910972257</v>
+        <v>0.99496216240453639</v>
       </c>
       <c r="AB65">
-        <v>270.5429996550854</v>
+        <v>92.360355916833001</v>
       </c>
     </row>
     <row r="66" spans="2:28">
@@ -14807,16 +14807,16 @@
         <v>515</v>
       </c>
       <c r="Y66" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z66" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="AA66">
-        <v>0.94713624989887801</v>
+        <v>0.97702953960894623</v>
       </c>
       <c r="AB66">
-        <v>969.16875185390393</v>
+        <v>421.12510716931934</v>
       </c>
     </row>
     <row r="67" spans="2:28">
@@ -14881,16 +14881,16 @@
         <v>517</v>
       </c>
       <c r="Y67" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="Z67" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="AA67">
-        <v>0.96517074323544272</v>
+        <v>0.98631766623578765</v>
       </c>
       <c r="AB67">
-        <v>638.53637401688275</v>
+        <v>250.84278567722609</v>
       </c>
     </row>
     <row r="68" spans="2:28">
@@ -14955,16 +14955,16 @@
         <v>519</v>
       </c>
       <c r="Y68" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="Z68" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="AA68">
-        <v>0.9771016434875236</v>
+        <v>0.96912603699420019</v>
       </c>
       <c r="AB68">
-        <v>419.80320272873433</v>
+        <v>566.02265510632935</v>
       </c>
     </row>
     <row r="69" spans="2:28">
@@ -15029,16 +15029,16 @@
         <v>521</v>
       </c>
       <c r="Y69" t="s">
-        <v>343</v>
+        <v>391</v>
       </c>
       <c r="Z69" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AA69">
-        <v>0.9912986266790621</v>
+        <v>0.99770573728283862</v>
       </c>
       <c r="AB69">
-        <v>159.52517755052818</v>
+        <v>42.061483147959365</v>
       </c>
     </row>
     <row r="70" spans="2:28">
@@ -15103,16 +15103,16 @@
         <v>523</v>
       </c>
       <c r="Y70" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="Z70" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="AA70">
-        <v>0.99619242046188483</v>
+        <v>0.99118992399256634</v>
       </c>
       <c r="AB70">
-        <v>69.805624865443917</v>
+        <v>161.51806013628308</v>
       </c>
     </row>
     <row r="71" spans="2:28">
@@ -15177,16 +15177,16 @@
         <v>525</v>
       </c>
       <c r="Y71" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="Z71" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="AA71">
-        <v>0.96239325925412511</v>
+        <v>0.9582992451809369</v>
       </c>
       <c r="AB71">
-        <v>689.45691367437246</v>
+        <v>764.51383834949013</v>
       </c>
     </row>
     <row r="72" spans="2:28">
@@ -15251,16 +15251,16 @@
         <v>527</v>
       </c>
       <c r="Y72" t="s">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="Z72" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="AA72">
-        <v>0.95110614119885384</v>
+        <v>0.95289359663592565</v>
       </c>
       <c r="AB72">
-        <v>896.38741135434657</v>
+        <v>863.61739500803003</v>
       </c>
     </row>
     <row r="73" spans="2:28">
@@ -15325,16 +15325,16 @@
         <v>529</v>
       </c>
       <c r="Y73" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="Z73" t="s">
-        <v>558</v>
+        <v>598</v>
       </c>
       <c r="AA73">
-        <v>0.98223116847554315</v>
+        <v>0.97577723283636553</v>
       </c>
       <c r="AB73">
-        <v>325.76191128170939</v>
+        <v>444.08406466663115</v>
       </c>
     </row>
     <row r="74" spans="2:28">
@@ -15402,7 +15402,7 @@
         <v>334</v>
       </c>
       <c r="Z74" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="AA74">
         <v>0.97496236164466343</v>
@@ -15476,7 +15476,7 @@
         <v>331</v>
       </c>
       <c r="Z75" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AA75">
         <v>0.96911860205632039</v>
@@ -15547,16 +15547,16 @@
         <v>535</v>
       </c>
       <c r="Y76" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="Z76" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AA76">
-        <v>0.99627301415801128</v>
+        <v>0.99620173788084643</v>
       </c>
       <c r="AB76">
-        <v>68.328073769792198</v>
+        <v>69.634805517815565</v>
       </c>
     </row>
     <row r="77" spans="2:28">
@@ -15621,16 +15621,16 @@
         <v>537</v>
       </c>
       <c r="Y77" t="s">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="Z77" t="s">
-        <v>568</v>
+        <v>601</v>
       </c>
       <c r="AA77">
-        <v>0.99633073297550734</v>
+        <v>0.99808042106452499</v>
       </c>
       <c r="AB77">
-        <v>67.269895449032902</v>
+        <v>35.192280483708828</v>
       </c>
     </row>
     <row r="78" spans="2:28">
@@ -15695,16 +15695,16 @@
         <v>539</v>
       </c>
       <c r="Y78" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="Z78" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AA78">
-        <v>0.9725266797570975</v>
+        <v>0.99235892038811246</v>
       </c>
       <c r="AB78">
-        <v>503.67753778654668</v>
+        <v>140.08645955127213</v>
       </c>
     </row>
     <row r="79" spans="2:28">
@@ -15769,16 +15769,16 @@
         <v>541</v>
       </c>
       <c r="Y79" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="Z79" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AA79">
-        <v>0.99690816609326338</v>
+        <v>0.97311459430172587</v>
       </c>
       <c r="AB79">
-        <v>56.683621623505239</v>
+        <v>492.8991044683591</v>
       </c>
     </row>
     <row r="80" spans="2:28">
@@ -15843,16 +15843,16 @@
         <v>543</v>
       </c>
       <c r="Y80" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="Z80" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AA80">
-        <v>0.97592802238295073</v>
+        <v>0.95854557991594525</v>
       </c>
       <c r="AB80">
-        <v>441.3195896459041</v>
+        <v>759.99770154100372</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -15917,16 +15917,16 @@
         <v>545</v>
       </c>
       <c r="Y81" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Z81" t="s">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="AA81">
-        <v>0.97807026787476981</v>
+        <v>0.98524310910972257</v>
       </c>
       <c r="AB81">
-        <v>402.04508896255408</v>
+        <v>270.5429996550854</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -15991,16 +15991,16 @@
         <v>547</v>
       </c>
       <c r="Y82" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="Z82" t="s">
-        <v>606</v>
+        <v>591</v>
       </c>
       <c r="AA82">
-        <v>0.96276589991882666</v>
+        <v>0.94713624989887801</v>
       </c>
       <c r="AB82">
-        <v>682.62516815484491</v>
+        <v>969.16875185390393</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16065,16 +16065,16 @@
         <v>549</v>
       </c>
       <c r="Y83" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="Z83" t="s">
-        <v>558</v>
+        <v>606</v>
       </c>
       <c r="AA83">
-        <v>0.98628621327161703</v>
+        <v>0.99635032886115649</v>
       </c>
       <c r="AB83">
-        <v>251.41942335368827</v>
+        <v>66.910637545464084</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -16139,16 +16139,16 @@
         <v>551</v>
       </c>
       <c r="Y84" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Z84" t="s">
         <v>607</v>
       </c>
       <c r="AA84">
-        <v>0.98392857039426507</v>
+        <v>0.98520673013262905</v>
       </c>
       <c r="AB84">
-        <v>294.64287610514066</v>
+        <v>271.20994756846727</v>
       </c>
     </row>
   </sheetData>
@@ -16157,7 +16157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86E1EF7-7B7A-40C6-86AC-B8DC7EF42FFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A880180D-94CA-4156-A5AB-3BAFD74C3946}">
   <dimension ref="B9:Z46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16269,7 +16269,7 @@
         <v>847</v>
       </c>
       <c r="K11" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="L11">
         <v>0.129291216127222</v>
@@ -16302,7 +16302,7 @@
         <v>919</v>
       </c>
       <c r="X11" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="Y11">
         <v>6.6577500000000001</v>
@@ -16337,7 +16337,7 @@
         <v>849</v>
       </c>
       <c r="K12" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="L12">
         <v>1.2472977367603104</v>
@@ -16370,7 +16370,7 @@
         <v>921</v>
       </c>
       <c r="X12" t="s">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="Y12">
         <v>54.581249999999997</v>
@@ -16405,7 +16405,7 @@
         <v>851</v>
       </c>
       <c r="K13" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="L13">
         <v>2.318274719104624</v>
@@ -16438,7 +16438,7 @@
         <v>923</v>
       </c>
       <c r="X13" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="Y13">
         <v>18.436499999999999</v>
@@ -16473,7 +16473,7 @@
         <v>853</v>
       </c>
       <c r="K14" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="L14">
         <v>0.91927356390823156</v>
@@ -16541,7 +16541,7 @@
         <v>855</v>
       </c>
       <c r="K15" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="L15">
         <v>4.6464784096723921</v>
@@ -16574,7 +16574,7 @@
         <v>927</v>
       </c>
       <c r="X15" t="s">
-        <v>805</v>
+        <v>834</v>
       </c>
       <c r="Y15">
         <v>14.769</v>
@@ -16609,7 +16609,7 @@
         <v>857</v>
       </c>
       <c r="K16" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="L16">
         <v>11.882635191498228</v>
@@ -16642,7 +16642,7 @@
         <v>929</v>
       </c>
       <c r="X16" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="Y16">
         <v>13.2255</v>
@@ -16677,7 +16677,7 @@
         <v>859</v>
       </c>
       <c r="K17" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="L17">
         <v>11.092555055294371</v>
@@ -16710,7 +16710,7 @@
         <v>931</v>
       </c>
       <c r="X17" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="Y17">
         <v>28.651499999999999</v>
@@ -16745,7 +16745,7 @@
         <v>861</v>
       </c>
       <c r="K18" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="L18">
         <v>4.7403831699218822E-2</v>
@@ -16778,7 +16778,7 @@
         <v>933</v>
       </c>
       <c r="X18" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="Y18">
         <v>27.531749999999999</v>
@@ -16813,7 +16813,7 @@
         <v>863</v>
       </c>
       <c r="K19" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="L19">
         <v>16.426692253806657</v>
@@ -16846,7 +16846,7 @@
         <v>935</v>
       </c>
       <c r="X19" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="Y19">
         <v>51.64425</v>
@@ -16881,7 +16881,7 @@
         <v>865</v>
       </c>
       <c r="K20" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="L20">
         <v>8.1288287393980401</v>
@@ -16949,7 +16949,7 @@
         <v>867</v>
       </c>
       <c r="K21" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="L21">
         <v>0.13371018978628957</v>
@@ -16982,7 +16982,7 @@
         <v>939</v>
       </c>
       <c r="X21" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="Y21">
         <v>7.9987500000000002</v>
@@ -17017,7 +17017,7 @@
         <v>869</v>
       </c>
       <c r="K22" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="L22">
         <v>1.3857406990868373</v>
@@ -17050,7 +17050,7 @@
         <v>941</v>
       </c>
       <c r="X22" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="Y22">
         <v>115.36875000000001</v>
@@ -17085,7 +17085,7 @@
         <v>871</v>
       </c>
       <c r="K23" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="L23">
         <v>0.75467749508942539</v>
@@ -17118,7 +17118,7 @@
         <v>943</v>
       </c>
       <c r="X23" t="s">
-        <v>820</v>
+        <v>841</v>
       </c>
       <c r="Y23">
         <v>18.766500000000001</v>
@@ -17153,7 +17153,7 @@
         <v>873</v>
       </c>
       <c r="K24" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="L24">
         <v>0.96556410486278166</v>
@@ -17186,7 +17186,7 @@
         <v>945</v>
       </c>
       <c r="X24" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Y24">
         <v>1.5217499999999999</v>
@@ -17221,7 +17221,7 @@
         <v>875</v>
       </c>
       <c r="K25" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
       <c r="L25">
         <v>0.43746236883491152</v>
@@ -17254,7 +17254,7 @@
         <v>947</v>
       </c>
       <c r="X25" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="Y25">
         <v>1.90425</v>
@@ -17289,7 +17289,7 @@
         <v>877</v>
       </c>
       <c r="K26" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L26">
         <v>1.8762027163233561</v>
@@ -17322,7 +17322,7 @@
         <v>949</v>
       </c>
       <c r="X26" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="Y26">
         <v>102.82125000000001</v>
@@ -17357,7 +17357,7 @@
         <v>879</v>
       </c>
       <c r="K27" t="s">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="L27">
         <v>0.18022981623384116</v>
@@ -17425,7 +17425,7 @@
         <v>881</v>
       </c>
       <c r="K28" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="L28">
         <v>1.1308942027141895</v>
@@ -17458,7 +17458,7 @@
         <v>953</v>
       </c>
       <c r="X28" t="s">
-        <v>819</v>
+        <v>840</v>
       </c>
       <c r="Y28">
         <v>9.1432500000000001</v>
@@ -17493,7 +17493,7 @@
         <v>883</v>
       </c>
       <c r="K29" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="L29">
         <v>0.7454968470610035</v>
@@ -17526,7 +17526,7 @@
         <v>955</v>
       </c>
       <c r="X29" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="Y29">
         <v>49.376249999999999</v>
@@ -17561,7 +17561,7 @@
         <v>885</v>
       </c>
       <c r="K30" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="L30">
         <v>0.13491890498058171</v>
@@ -17594,7 +17594,7 @@
         <v>957</v>
       </c>
       <c r="X30" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="Y30">
         <v>64.686750000000004</v>
@@ -17629,7 +17629,7 @@
         <v>887</v>
       </c>
       <c r="K31" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="L31">
         <v>3.3502966177508899E-2</v>
@@ -17662,7 +17662,7 @@
         <v>959</v>
       </c>
       <c r="X31" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="Y31">
         <v>19.151250000000001</v>
@@ -17697,7 +17697,7 @@
         <v>889</v>
       </c>
       <c r="K32" t="s">
-        <v>724</v>
+        <v>700</v>
       </c>
       <c r="L32">
         <v>4.4570745535421293E-2</v>
@@ -17730,7 +17730,7 @@
         <v>961</v>
       </c>
       <c r="X32" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="Y32">
         <v>91.322249999999997</v>
@@ -17765,7 +17765,7 @@
         <v>891</v>
       </c>
       <c r="K33" t="s">
-        <v>716</v>
+        <v>692</v>
       </c>
       <c r="L33">
         <v>1.8432371407733249E-2</v>
@@ -17798,7 +17798,7 @@
         <v>963</v>
       </c>
       <c r="X33" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="Y33">
         <v>86.045249999999996</v>
@@ -17833,7 +17833,7 @@
         <v>893</v>
       </c>
       <c r="K34" t="s">
-        <v>718</v>
+        <v>694</v>
       </c>
       <c r="L34">
         <v>0.33180838345937391</v>
@@ -17866,7 +17866,7 @@
         <v>965</v>
       </c>
       <c r="X34" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="Y34">
         <v>34.774500000000003</v>
@@ -17901,7 +17901,7 @@
         <v>895</v>
       </c>
       <c r="K35" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="L35">
         <v>3.1614758986586073</v>
@@ -17934,7 +17934,7 @@
         <v>967</v>
       </c>
       <c r="X35" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="Y35">
         <v>60.10125</v>
@@ -17969,7 +17969,7 @@
         <v>897</v>
       </c>
       <c r="K36" t="s">
-        <v>723</v>
+        <v>699</v>
       </c>
       <c r="L36">
         <v>1.3726240143913757</v>
@@ -18002,7 +18002,7 @@
         <v>969</v>
       </c>
       <c r="X36" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="Y36">
         <v>2.3287499999999999</v>
@@ -18037,7 +18037,7 @@
         <v>899</v>
       </c>
       <c r="K37" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="L37">
         <v>0.1338251234250375</v>
@@ -18070,7 +18070,7 @@
         <v>971</v>
       </c>
       <c r="X37" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="Y37">
         <v>17.766749999999998</v>
@@ -18105,7 +18105,7 @@
         <v>901</v>
       </c>
       <c r="K38" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="L38">
         <v>2.1118535388590605</v>
@@ -18138,7 +18138,7 @@
         <v>973</v>
       </c>
       <c r="X38" t="s">
-        <v>803</v>
+        <v>832</v>
       </c>
       <c r="Y38">
         <v>2.073</v>
@@ -18173,7 +18173,7 @@
         <v>903</v>
       </c>
       <c r="K39" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="L39">
         <v>1.5197190100572773</v>
@@ -18241,7 +18241,7 @@
         <v>905</v>
       </c>
       <c r="K40" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="L40">
         <v>3.2370560671094046</v>
@@ -18274,7 +18274,7 @@
         <v>977</v>
       </c>
       <c r="X40" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="Y40">
         <v>8.2132500000000004</v>
@@ -18309,7 +18309,7 @@
         <v>907</v>
       </c>
       <c r="K41" t="s">
-        <v>722</v>
+        <v>698</v>
       </c>
       <c r="L41">
         <v>9.3502299727040246</v>
@@ -18342,7 +18342,7 @@
         <v>979</v>
       </c>
       <c r="X41" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="Y41">
         <v>1.2622500000000001</v>
@@ -18377,7 +18377,7 @@
         <v>909</v>
       </c>
       <c r="K42" t="s">
-        <v>720</v>
+        <v>696</v>
       </c>
       <c r="L42">
         <v>3.7895528026363667</v>
@@ -18410,7 +18410,7 @@
         <v>981</v>
       </c>
       <c r="X42" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="Y42">
         <v>7.3717499999999996</v>
@@ -18445,7 +18445,7 @@
         <v>911</v>
       </c>
       <c r="K43" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="L43">
         <v>2.4345968290099598</v>
@@ -18478,7 +18478,7 @@
         <v>983</v>
       </c>
       <c r="X43" t="s">
-        <v>837</v>
+        <v>808</v>
       </c>
       <c r="Y43">
         <v>9.1162500000000009</v>
@@ -18513,7 +18513,7 @@
         <v>913</v>
       </c>
       <c r="K44" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="L44">
         <v>3.5872166924997928</v>
@@ -18546,7 +18546,7 @@
         <v>985</v>
       </c>
       <c r="X44" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="Y44">
         <v>2.0219999999999998</v>
@@ -18581,7 +18581,7 @@
         <v>915</v>
       </c>
       <c r="K45" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="L45">
         <v>1.2359990336927942</v>
@@ -18614,7 +18614,7 @@
         <v>987</v>
       </c>
       <c r="X45" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="Y45">
         <v>6.5925000000000002</v>
@@ -18649,7 +18649,7 @@
         <v>917</v>
       </c>
       <c r="K46" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="L46">
         <v>3.8785201943148309</v>
@@ -18664,7 +18664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC76012E-D3BB-489C-8C67-45244A5C5BF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156B972F-3A05-41CE-9CDE-2AA55CB0F32C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20481,7 +20481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1BB622-71E8-4A1B-BFAD-0B1330881143}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206BC03C-031C-4E6A-9FDC-B993A75215FA}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D9F894-C378-42E4-9632-0C8E1BECDA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FDDD0FC-2010-4515-8AFE-A30ABBD399AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1339,18 +1339,156 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IDN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IDN_017</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IDN_027</t>
   </si>
   <si>
@@ -1375,6 +1513,186 @@
     <t>connecting solar to buses in cluster 48</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IDN_011</t>
   </si>
   <si>
@@ -1393,52 +1711,46 @@
     <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IDN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
+    <t>distr_solelc_spv_IDN_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IDN_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
   </si>
   <si>
     <t>distr_solelc_spv_IDN_013</t>
@@ -1477,367 +1789,157 @@
     <t>connecting solar to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IDN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IDN_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_ID6-275_IDN,e_ID5-275_IDN,e_ID3-275_IDN,e_w939542521-275_IDN,e_w928928133-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID33-500_IDN,e_w264550744-500_IDN,e_w769617021-500_IDN,e_w314452486-500_IDN,e_ID29-500_IDN,e_w267626657-500_IDN,e_ID31-500_IDN,e_w166633831-500_IDN,e_w689263666-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID34-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_w1193553154-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN,e_w398909640-500_IDN,e_w340978681-500_IDN,e_ID35-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID34-500_IDN,e_ID38-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w721685825-275_IDN,e_w754073846-275_IDN,e_w340205049-275_IDN,e_w310695690-275_IDN,e_w754096394-275_IDN,e_w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>e_ID6-275_IDN,e_w939542521-275_IDN,e_w841499143-275_IDN,e_w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_w754178666-275_IDN,e_ID3-275_IDN,e_w310695690-275_IDN,e_w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN,e_w1316786278-275_IDN,e_w931931121-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w943539373-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w939542521-275_IDN,e_ID4-275_IDN,e_ID3-275_IDN,e_ID7-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w930719092-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w544403426-230_IDN</t>
+  </si>
+  <si>
     <t>e_ID1-275_IDN,e_w721674155-275_IDN,e_w340205049-275_IDN,e_w310958602-275_IDN</t>
   </si>
   <si>
     <t>e_w841499143-275_IDN,e_w1312287191-275_IDN,e_w528189342-275_IDN</t>
   </si>
   <si>
-    <t>e_w615581242-275_IDN</t>
-  </si>
-  <si>
     <t>e_w615581232-275_IDN,e_w544403426-230_IDN</t>
   </si>
   <si>
-    <t>e_w759130125-230_IDN</t>
+    <t>e_w736595653-275_IDN,e_w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w610198177-275_IDN,e_w753733608-275_IDN,e_w931931121-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w1193553154-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_ID9-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w721674155-275_IDN,e_w469888049-275_IDN,e_ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w930719092-275_IDN,e_w841499143-275_IDN,e_w1186182648-500_IDN,e_w943539373-275_IDN,e_w753733608-275_IDN,e_w946191122-275_IDN,e_w610198177-275_IDN,e_w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_w166633831-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403426-230_IDN,e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_ID27-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w340205049-275_IDN,e_w754073846-275_IDN,e_w310958602-275_IDN,e_w754096394-275_IDN,e_w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w736595653-500_IDN,e_w562061281-275_IDN,e_ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581232-275_IDN,e_w544403426-230_IDN,e_w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_ID2-275_IDN,e_w615581270-275_IDN,e_w615581242-275_IDN</t>
   </si>
   <si>
     <t>e_ID2-275_IDN,e_w615581270-275_IDN</t>
   </si>
   <si>
-    <t>e_ID38-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
     <t>e_w615581232-275_IDN</t>
   </si>
   <si>
-    <t>e_w939542521-275_IDN,e_ID4-275_IDN,e_ID3-275_IDN,e_ID7-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w930719092-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w562061281-275_IDN,e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w544403426-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w610198177-275_IDN,e_w753733608-275_IDN,e_w931931121-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w1193553154-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403426-230_IDN,e_ID9-230_IDN,e_w759130125-230_IDN</t>
+    <t>e_w1316876158-275_IDN,e_w161965853-500_IDN,e_w169444592-500_IDN,e_ID10-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_w966209515-500_IDN,e_ID15-500_IDN,e_w960747936-500_IDN,e_w960747902-500_IDN,e_w314452486-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_w629512849-500_IDN,e_ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>e_w615581242-275_IDN,e_w614955993-230_IDN,e_w1193553154-275_IDN,e_w544403431-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w544403431-230_IDN,e_w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>e_w841499143-275_IDN,e_w528189342-275_IDN,e_w931931133-275_IDN,e_w527900241-275_IDN,e_w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>e_w614955993-230_IDN,e_w544403431-230_IDN</t>
   </si>
   <si>
     <t>e_w928220391-275_IDN,e_ID1-275_IDN,e_w721685825-275_IDN,e_w754073846-275_IDN</t>
@@ -1852,106 +1954,34 @@
     <t>e_w759130125-230_IDN,e_ID9-230_IDN</t>
   </si>
   <si>
-    <t>e_ID2-275_IDN,e_w615581270-275_IDN,e_w615581242-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403426-230_IDN</t>
-  </si>
-  <si>
-    <t>e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN,e_w398909640-500_IDN,e_w340978681-500_IDN,e_ID35-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>e_ID34-500_IDN,e_ID38-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403426-230_IDN,e_w759130125-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w721685825-275_IDN,e_w754073846-275_IDN,e_w340205049-275_IDN,e_w310695690-275_IDN,e_w754096394-275_IDN,e_w337039411-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID6-275_IDN,e_w939542521-275_IDN,e_w841499143-275_IDN,e_w1312287191-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_w754178666-275_IDN,e_ID3-275_IDN,e_w310695690-275_IDN,e_w736595653-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w931931133-275_IDN,e_w1316876158-275_IDN,e_w1316786278-275_IDN,e_w931931121-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w943539373-275_IDN,e_w1186182648-500_IDN,e_w736595653-500_IDN,e_w943539373-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w721674155-275_IDN,e_w469888049-275_IDN,e_ID6-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w930719092-275_IDN,e_w841499143-275_IDN,e_w1186182648-500_IDN,e_w943539373-275_IDN,e_w753733608-275_IDN,e_w946191122-275_IDN,e_w610198177-275_IDN,e_w943539373-500_IDN</t>
-  </si>
-  <si>
-    <t>e_ID28-500_IDN,e_w166633831-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403426-230_IDN,e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w340205049-275_IDN,e_w754073846-275_IDN,e_w310958602-275_IDN,e_w754096394-275_IDN,e_w721674155-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w736595653-500_IDN,e_w562061281-275_IDN,e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581232-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581232-275_IDN,e_w544403426-230_IDN,e_w614955993-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w614955993-230_IDN,e_w544403431-230_IDN,e_w759130125-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w736595653-275_IDN,e_w736595653-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w1193553154-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w1316876158-275_IDN,e_w161965853-500_IDN,e_w169444592-500_IDN,e_ID10-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_w966209515-500_IDN,e_ID15-500_IDN,e_w960747936-500_IDN,e_w960747902-500_IDN,e_w314452486-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_w629512849-500_IDN,e_ID29-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581242-275_IDN,e_w614955993-230_IDN,e_w1193553154-275_IDN,e_w544403431-230_IDN</t>
-  </si>
-  <si>
-    <t>e_w544403431-230_IDN,e_w759130125-230_IDN</t>
-  </si>
-  <si>
-    <t>e_ID27-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w469888049-275_IDN,e_w721674155-275_IDN,e_ID6-275_IDN,e_ID5-275_IDN,e_ID3-275_IDN,e_w939542521-275_IDN,e_w928928133-275_IDN</t>
-  </si>
-  <si>
-    <t>e_ID33-500_IDN,e_w264550744-500_IDN,e_w769617021-500_IDN,e_w314452486-500_IDN,e_ID29-500_IDN,e_w267626657-500_IDN,e_ID31-500_IDN,e_w166633831-500_IDN,e_w689263666-500_IDN</t>
-  </si>
-  <si>
-    <t>e_ID34-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581242-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581242-275_IDN,e_ID2-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w615581242-275_IDN,e_w1193553154-275_IDN,e_w615581232-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w841499143-275_IDN,e_w528189342-275_IDN,e_w931931133-275_IDN,e_w527900241-275_IDN,e_w946191122-275_IDN</t>
-  </si>
-  <si>
-    <t>e_w614955993-230_IDN,e_w544403431-230_IDN</t>
+    <t>distr_wonelc_won_IDN_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_IDN_001</t>
@@ -1960,34 +1990,58 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IDN_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>distr_wonelc_won_IDN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_IDN_016</t>
@@ -1996,6 +2050,36 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IDN_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IDN_023</t>
   </si>
   <si>
@@ -2050,114 +2134,30 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IDN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IDN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IDN_002</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IDN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IDN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IDN_013</t>
   </si>
   <si>
@@ -2170,34 +2170,70 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>elc_won_IDN_036</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_ID33-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_011</t>
+  </si>
+  <si>
+    <t>e_w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_025</t>
+  </si>
+  <si>
+    <t>e_w960747902-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_ID29-500_IDN,e_ID28-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_019</t>
+  </si>
+  <si>
+    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN,e_w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_007</t>
+  </si>
+  <si>
     <t>elc_won_IDN_001</t>
   </si>
   <si>
-    <t>elc_won_IDN_036</t>
-  </si>
-  <si>
-    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w161960924-500_IDN,e_w604684007-500_IDN,e_w264550744-500_IDN,e_ID33-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_011</t>
-  </si>
-  <si>
-    <t>e_w562061281-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_025</t>
-  </si>
-  <si>
-    <t>e_w960747902-500_IDN,e_ID23-500_IDN,e_w1013653012-500_IDN,e_ID29-500_IDN,e_ID28-500_IDN,e_ID27-500_IDN,e_w398909640-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_019</t>
-  </si>
-  <si>
-    <t>e_w615581270-275_IDN,e_w615581242-275_IDN,e_w615581232-275_IDN,e_w1193553154-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_007</t>
+    <t>elc_won_IDN_012</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_009</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_015</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_029</t>
+  </si>
+  <si>
+    <t>e_ID28-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_017</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_018</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_014</t>
+  </si>
+  <si>
+    <t>e_w943539373-275_IDN,e_w943539373-500_IDN,e_w753733608-275_IDN,e_w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_035</t>
+  </si>
+  <si>
+    <t>e_w1316876158-275_IDN,e_w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_003</t>
   </si>
   <si>
     <t>elc_won_IDN_016</t>
@@ -2206,6 +2242,27 @@
     <t>e_w931931121-275_IDN,e_w610198177-275_IDN,e_ID13-500_IDN,e_w1013653012-500_IDN,e_w562061281-275_IDN</t>
   </si>
   <si>
+    <t>elc_won_IDN_033</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_006</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_027</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_021</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_034</t>
+  </si>
+  <si>
+    <t>e_w314452486-500_IDN,e_w629512849-500_IDN,e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
+  </si>
+  <si>
     <t>elc_won_IDN_023</t>
   </si>
   <si>
@@ -2245,81 +2302,24 @@
     <t>elc_won_IDN_005</t>
   </si>
   <si>
+    <t>elc_won_IDN_030</t>
+  </si>
+  <si>
+    <t>e_w340978681-500_IDN,e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_004</t>
+  </si>
+  <si>
+    <t>elc_won_IDN_010</t>
+  </si>
+  <si>
     <t>elc_won_IDN_002</t>
   </si>
   <si>
     <t>e_w544403426-230_IDN,e_w614955993-230_IDN</t>
   </si>
   <si>
-    <t>elc_won_IDN_012</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_009</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_030</t>
-  </si>
-  <si>
-    <t>e_w340978681-500_IDN,e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_004</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_010</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_014</t>
-  </si>
-  <si>
-    <t>e_w943539373-275_IDN,e_w943539373-500_IDN,e_w753733608-275_IDN,e_w610198177-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_035</t>
-  </si>
-  <si>
-    <t>e_w1316876158-275_IDN,e_w161965853-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_003</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_033</t>
-  </si>
-  <si>
-    <t>e_ID38-500_IDN,e_ID34-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_006</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_027</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_021</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_034</t>
-  </si>
-  <si>
-    <t>e_w314452486-500_IDN,e_w629512849-500_IDN,e_ID37-500_IDN,e_w1308433899-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_015</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_029</t>
-  </si>
-  <si>
-    <t>e_ID28-500_IDN,e_ID34-500_IDN,e_ID38-500_IDN,e_w615581270-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_017</t>
-  </si>
-  <si>
-    <t>elc_won_IDN_018</t>
-  </si>
-  <si>
     <t>elc_won_IDN_013</t>
   </si>
   <si>
@@ -2329,34 +2329,130 @@
     <t>elc_won_IDN_008</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IDN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_035</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IDN_024</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IDN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
+    <t>distr_wofelc_wof_IDN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IDN_033</t>
@@ -2365,40 +2461,22 @@
     <t>connecting wind offshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IDN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_035</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
+    <t>distr_wofelc_wof_IDN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IDN_006</t>
@@ -2419,34 +2497,34 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IDN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>distr_wofelc_wof_IDN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IDN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IDN_034</t>
@@ -2461,97 +2539,82 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IDN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IDN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>elc_wof_IDN_026</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_027</t>
+  </si>
+  <si>
+    <t>e_w928220391-275_IDN,e_w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_035</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_019</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_018</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_013</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_032</t>
+  </si>
+  <si>
+    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w264550744-500_IDN,e_w161960924-500_IDN,e_ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_031</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_025</t>
   </si>
   <si>
     <t>elc_wof_IDN_024</t>
   </si>
   <si>
-    <t>elc_wof_IDN_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_014</t>
+    <t>elc_wof_IDN_029</t>
+  </si>
+  <si>
+    <t>e_w314452486-500_IDN,e_w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_017</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_030</t>
+  </si>
+  <si>
+    <t>e_ID37-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_011</t>
   </si>
   <si>
     <t>elc_wof_IDN_033</t>
@@ -2560,31 +2623,16 @@
     <t>e_w528189342-275_IDN,e_w931931133-275_IDN</t>
   </si>
   <si>
-    <t>elc_wof_IDN_025</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_026</t>
-  </si>
-  <si>
-    <t>e_w928220391-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_027</t>
-  </si>
-  <si>
-    <t>e_w928220391-275_IDN,e_w721685825-275_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_035</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_030</t>
-  </si>
-  <si>
-    <t>e_ID37-500_IDN,e_ID36-500_IDN,e_w265318414-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_011</t>
+    <t>elc_wof_IDN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_023</t>
+  </si>
+  <si>
+    <t>e_ID27-500_IDN,e_ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_008</t>
   </si>
   <si>
     <t>elc_wof_IDN_006</t>
@@ -2596,25 +2644,22 @@
     <t>elc_wof_IDN_009</t>
   </si>
   <si>
-    <t>elc_wof_IDN_032</t>
-  </si>
-  <si>
-    <t>e_w161965853-500_IDN,e_w169444592-500_IDN,e_w264550744-500_IDN,e_w161960924-500_IDN,e_ID33-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_031</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_023</t>
-  </si>
-  <si>
-    <t>e_ID27-500_IDN,e_ID34-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_008</t>
+    <t>elc_wof_IDN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_016</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_028</t>
+  </si>
+  <si>
+    <t>e_ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>elc_wof_IDN_005</t>
   </si>
   <si>
     <t>elc_wof_IDN_034</t>
@@ -2624,51 +2669,6 @@
   </si>
   <si>
     <t>elc_wof_IDN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_028</t>
-  </si>
-  <si>
-    <t>e_ID38-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_015</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_016</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_019</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_018</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_013</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_029</t>
-  </si>
-  <si>
-    <t>e_w314452486-500_IDN,e_w629512849-500_IDN</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_017</t>
-  </si>
-  <si>
-    <t>elc_wof_IDN_010</t>
   </si>
   <si>
     <t>e_won_IDN_001</t>
@@ -7943,7 +7943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F93EC2E-C1F3-4476-9D04-EDA8906694C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FAD1E2-B639-4E84-88F4-98192B2601F7}">
   <dimension ref="B9:BD84"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8181,16 +8181,16 @@
         <v>403</v>
       </c>
       <c r="Y11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Z11" t="s">
         <v>555</v>
       </c>
       <c r="AA11">
-        <v>0.9912986266790621</v>
+        <v>0.99620173788084643</v>
       </c>
       <c r="AB11">
-        <v>159.52517755052818</v>
+        <v>69.634805517815565</v>
       </c>
       <c r="AD11" t="s">
         <v>402</v>
@@ -8220,13 +8220,13 @@
         <v>680</v>
       </c>
       <c r="AN11" t="s">
-        <v>572</v>
+        <v>681</v>
       </c>
       <c r="AO11">
-        <v>0.9519359532349716</v>
+        <v>0.9936518770554722</v>
       </c>
       <c r="AP11">
-        <v>881.17419069218636</v>
+        <v>116.38225398301061</v>
       </c>
       <c r="AR11" t="s">
         <v>402</v>
@@ -8256,13 +8256,13 @@
         <v>803</v>
       </c>
       <c r="BB11" t="s">
-        <v>561</v>
+        <v>804</v>
       </c>
       <c r="BC11">
-        <v>0.97600654740978099</v>
+        <v>0.99498145347305278</v>
       </c>
       <c r="BD11">
-        <v>439.8799641540142</v>
+        <v>92.006686327364918</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8327,16 +8327,16 @@
         <v>407</v>
       </c>
       <c r="Y12" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="Z12" t="s">
         <v>556</v>
       </c>
       <c r="AA12">
-        <v>0.99619242046188483</v>
+        <v>0.99808042106452499</v>
       </c>
       <c r="AB12">
-        <v>69.805624865443917</v>
+        <v>35.192280483708828</v>
       </c>
       <c r="AD12" t="s">
         <v>402</v>
@@ -8363,16 +8363,16 @@
         <v>610</v>
       </c>
       <c r="AM12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AN12" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AO12">
-        <v>0.9936518770554722</v>
+        <v>0.9880111771283725</v>
       </c>
       <c r="AP12">
-        <v>116.38225398301061</v>
+        <v>219.79508597983738</v>
       </c>
       <c r="AR12" t="s">
         <v>402</v>
@@ -8399,16 +8399,16 @@
         <v>735</v>
       </c>
       <c r="BA12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="BB12" t="s">
-        <v>561</v>
+        <v>806</v>
       </c>
       <c r="BC12">
-        <v>0.97616044738151031</v>
+        <v>0.98831120739622746</v>
       </c>
       <c r="BD12">
-        <v>437.05846467231135</v>
+        <v>214.2945310691625</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8473,16 +8473,16 @@
         <v>409</v>
       </c>
       <c r="Y13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Z13" t="s">
         <v>557</v>
       </c>
       <c r="AA13">
-        <v>0.96239325925412511</v>
+        <v>0.99235892038811246</v>
       </c>
       <c r="AB13">
-        <v>689.45691367437246</v>
+        <v>140.08645955127213</v>
       </c>
       <c r="AD13" t="s">
         <v>402</v>
@@ -8509,16 +8509,16 @@
         <v>612</v>
       </c>
       <c r="AM13" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AN13" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AO13">
-        <v>0.9880111771283725</v>
+        <v>0.99700964975406792</v>
       </c>
       <c r="AP13">
-        <v>219.79508597983738</v>
+        <v>54.823087842088889</v>
       </c>
       <c r="AR13" t="s">
         <v>402</v>
@@ -8545,16 +8545,16 @@
         <v>737</v>
       </c>
       <c r="BA13" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="BB13" t="s">
-        <v>567</v>
+        <v>700</v>
       </c>
       <c r="BC13">
-        <v>0.97829546850421678</v>
+        <v>0.99160370033662015</v>
       </c>
       <c r="BD13">
-        <v>397.91641075602604</v>
+        <v>153.93216049529627</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8619,16 +8619,16 @@
         <v>411</v>
       </c>
       <c r="Y14" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="Z14" t="s">
         <v>558</v>
       </c>
       <c r="AA14">
-        <v>0.95110614119885384</v>
+        <v>0.97311459430172587</v>
       </c>
       <c r="AB14">
-        <v>896.38741135434657</v>
+        <v>492.8991044683591</v>
       </c>
       <c r="AD14" t="s">
         <v>402</v>
@@ -8655,16 +8655,16 @@
         <v>614</v>
       </c>
       <c r="AM14" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AN14" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AO14">
-        <v>0.99700964975406792</v>
+        <v>0.98325145592799346</v>
       </c>
       <c r="AP14">
-        <v>54.823087842088889</v>
+        <v>307.05664132012055</v>
       </c>
       <c r="AR14" t="s">
         <v>402</v>
@@ -8691,16 +8691,16 @@
         <v>739</v>
       </c>
       <c r="BA14" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="BB14" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="BC14">
-        <v>0.94478739551790969</v>
+        <v>0.96625736872930745</v>
       </c>
       <c r="BD14">
-        <v>1012.2310821716558</v>
+        <v>618.61490662936239</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8765,16 +8765,16 @@
         <v>413</v>
       </c>
       <c r="Y15" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Z15" t="s">
         <v>559</v>
       </c>
       <c r="AA15">
-        <v>0.98223116847554315</v>
+        <v>0.95854557991594525</v>
       </c>
       <c r="AB15">
-        <v>325.76191128170939</v>
+        <v>759.99770154100372</v>
       </c>
       <c r="AD15" t="s">
         <v>402</v>
@@ -8801,16 +8801,16 @@
         <v>616</v>
       </c>
       <c r="AM15" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AN15" t="s">
-        <v>688</v>
+        <v>579</v>
       </c>
       <c r="AO15">
-        <v>0.98325145592799346</v>
+        <v>0.95111092756566806</v>
       </c>
       <c r="AP15">
-        <v>307.05664132012055</v>
+        <v>896.29966129608511</v>
       </c>
       <c r="AR15" t="s">
         <v>402</v>
@@ -8837,16 +8837,16 @@
         <v>741</v>
       </c>
       <c r="BA15" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="BB15" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="BC15">
-        <v>0.94491770107559214</v>
+        <v>0.93693021635476914</v>
       </c>
       <c r="BD15">
-        <v>1009.8421469474777</v>
+        <v>1156.2793668292329</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8911,16 +8911,16 @@
         <v>415</v>
       </c>
       <c r="Y16" t="s">
-        <v>337</v>
+        <v>384</v>
       </c>
       <c r="Z16" t="s">
         <v>560</v>
       </c>
       <c r="AA16">
-        <v>0.96710197646129548</v>
+        <v>0.98524310910972257</v>
       </c>
       <c r="AB16">
-        <v>603.13043154291677</v>
+        <v>270.5429996550854</v>
       </c>
       <c r="AD16" t="s">
         <v>402</v>
@@ -8950,13 +8950,13 @@
         <v>689</v>
       </c>
       <c r="AN16" t="s">
-        <v>558</v>
+        <v>606</v>
       </c>
       <c r="AO16">
-        <v>0.95111092756566806</v>
+        <v>0.9519359532349716</v>
       </c>
       <c r="AP16">
-        <v>896.29966129608511</v>
+        <v>881.17419069218636</v>
       </c>
       <c r="AR16" t="s">
         <v>402</v>
@@ -8983,16 +8983,16 @@
         <v>743</v>
       </c>
       <c r="BA16" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="BB16" t="s">
-        <v>809</v>
+        <v>579</v>
       </c>
       <c r="BC16">
-        <v>0.98716759869587867</v>
+        <v>0.94041102627936679</v>
       </c>
       <c r="BD16">
-        <v>235.26069057555824</v>
+        <v>1092.4645182116094</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>417</v>
       </c>
       <c r="Y17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z17" t="s">
         <v>561</v>
       </c>
       <c r="AA17">
-        <v>0.97245598614016138</v>
+        <v>0.94713624989887801</v>
       </c>
       <c r="AB17">
-        <v>504.97358743037506</v>
+        <v>969.16875185390393</v>
       </c>
       <c r="AD17" t="s">
         <v>402</v>
@@ -9096,13 +9096,13 @@
         <v>690</v>
       </c>
       <c r="AN17" t="s">
-        <v>691</v>
+        <v>593</v>
       </c>
       <c r="AO17">
-        <v>0.98243109777744309</v>
+        <v>0.97444089635831932</v>
       </c>
       <c r="AP17">
-        <v>322.09654074687614</v>
+        <v>468.58356676414513</v>
       </c>
       <c r="AR17" t="s">
         <v>402</v>
@@ -9129,16 +9129,16 @@
         <v>745</v>
       </c>
       <c r="BA17" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="BB17" t="s">
-        <v>602</v>
+        <v>573</v>
       </c>
       <c r="BC17">
-        <v>0.98584164436602861</v>
+        <v>0.95063651087703893</v>
       </c>
       <c r="BD17">
-        <v>259.56985328947479</v>
+        <v>904.99730058761952</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9203,16 +9203,16 @@
         <v>419</v>
       </c>
       <c r="Y18" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="Z18" t="s">
         <v>562</v>
       </c>
       <c r="AA18">
-        <v>0.97006792991713942</v>
+        <v>0.99720517126173747</v>
       </c>
       <c r="AB18">
-        <v>548.75461818577651</v>
+        <v>51.238526868146437</v>
       </c>
       <c r="AD18" t="s">
         <v>402</v>
@@ -9239,16 +9239,16 @@
         <v>622</v>
       </c>
       <c r="AM18" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AN18" t="s">
-        <v>693</v>
+        <v>573</v>
       </c>
       <c r="AO18">
-        <v>0.99117435469129123</v>
+        <v>0.97186368651165222</v>
       </c>
       <c r="AP18">
-        <v>161.80349732632692</v>
+        <v>515.83241395304219</v>
       </c>
       <c r="AR18" t="s">
         <v>402</v>
@@ -9275,16 +9275,16 @@
         <v>747</v>
       </c>
       <c r="BA18" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="BB18" t="s">
-        <v>812</v>
+        <v>581</v>
       </c>
       <c r="BC18">
-        <v>0.99498145347305278</v>
+        <v>0.97616044738151031</v>
       </c>
       <c r="BD18">
-        <v>92.006686327364918</v>
+        <v>437.05846467231135</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9349,16 +9349,16 @@
         <v>421</v>
       </c>
       <c r="Y19" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Z19" t="s">
         <v>563</v>
       </c>
       <c r="AA19">
-        <v>0.99627301415801128</v>
+        <v>0.98421229582412162</v>
       </c>
       <c r="AB19">
-        <v>68.328073769792198</v>
+        <v>289.44124322443668</v>
       </c>
       <c r="AD19" t="s">
         <v>402</v>
@@ -9385,16 +9385,16 @@
         <v>624</v>
       </c>
       <c r="AM19" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="AN19" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="AO19">
-        <v>0.99101688837209245</v>
+        <v>0.98177850613436324</v>
       </c>
       <c r="AP19">
-        <v>164.69037984497118</v>
+        <v>334.06072087000706</v>
       </c>
       <c r="AR19" t="s">
         <v>402</v>
@@ -9424,13 +9424,13 @@
         <v>813</v>
       </c>
       <c r="BB19" t="s">
-        <v>814</v>
+        <v>583</v>
       </c>
       <c r="BC19">
-        <v>0.98831120739622746</v>
+        <v>0.97829546850421678</v>
       </c>
       <c r="BD19">
-        <v>214.2945310691625</v>
+        <v>397.91641075602604</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9495,16 +9495,16 @@
         <v>423</v>
       </c>
       <c r="Y20" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Z20" t="s">
         <v>564</v>
       </c>
       <c r="AA20">
-        <v>0.99633073297550734</v>
+        <v>0.97067956893851193</v>
       </c>
       <c r="AB20">
-        <v>67.269895449032902</v>
+        <v>537.54123612728188</v>
       </c>
       <c r="AD20" t="s">
         <v>402</v>
@@ -9531,16 +9531,16 @@
         <v>626</v>
       </c>
       <c r="AM20" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="AN20" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="AO20">
-        <v>0.9755246434835193</v>
+        <v>0.98895557240687315</v>
       </c>
       <c r="AP20">
-        <v>448.71486946881294</v>
+        <v>202.48117254065832</v>
       </c>
       <c r="AR20" t="s">
         <v>402</v>
@@ -9567,16 +9567,16 @@
         <v>751</v>
       </c>
       <c r="BA20" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="BB20" t="s">
-        <v>716</v>
+        <v>583</v>
       </c>
       <c r="BC20">
-        <v>0.99160370033662015</v>
+        <v>0.94478739551790969</v>
       </c>
       <c r="BD20">
-        <v>153.93216049529627</v>
+        <v>1012.2310821716558</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9641,16 +9641,16 @@
         <v>425</v>
       </c>
       <c r="Y21" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="Z21" t="s">
         <v>565</v>
       </c>
       <c r="AA21">
-        <v>0.9725266797570975</v>
+        <v>0.98091465074522166</v>
       </c>
       <c r="AB21">
-        <v>503.67753778654668</v>
+        <v>349.89806967093693</v>
       </c>
       <c r="AD21" t="s">
         <v>402</v>
@@ -9677,16 +9677,16 @@
         <v>628</v>
       </c>
       <c r="AM21" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="AN21" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="AO21">
-        <v>0.9574422475745189</v>
+        <v>0.95753456607285348</v>
       </c>
       <c r="AP21">
-        <v>780.22546113382077</v>
+        <v>778.53295533101902</v>
       </c>
       <c r="AR21" t="s">
         <v>402</v>
@@ -9713,16 +9713,16 @@
         <v>753</v>
       </c>
       <c r="BA21" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="BB21" t="s">
-        <v>817</v>
+        <v>598</v>
       </c>
       <c r="BC21">
-        <v>0.99036076428701636</v>
+        <v>0.94491770107559214</v>
       </c>
       <c r="BD21">
-        <v>176.71932140470005</v>
+        <v>1009.8421469474777</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9787,16 +9787,16 @@
         <v>427</v>
       </c>
       <c r="Y22" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="Z22" t="s">
         <v>566</v>
       </c>
       <c r="AA22">
-        <v>0.98696950091677516</v>
+        <v>0.97678876819750537</v>
       </c>
       <c r="AB22">
-        <v>238.89248319245524</v>
+        <v>425.5392497124015</v>
       </c>
       <c r="AD22" t="s">
         <v>402</v>
@@ -9823,16 +9823,16 @@
         <v>630</v>
       </c>
       <c r="AM22" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="AN22" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AO22">
-        <v>0.97673972771258222</v>
+        <v>0.94698201881115829</v>
       </c>
       <c r="AP22">
-        <v>426.43832526932584</v>
+        <v>971.99632179543119</v>
       </c>
       <c r="AR22" t="s">
         <v>402</v>
@@ -9859,16 +9859,16 @@
         <v>755</v>
       </c>
       <c r="BA22" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="BB22" t="s">
-        <v>575</v>
+        <v>817</v>
       </c>
       <c r="BC22">
-        <v>0.98102590217137298</v>
+        <v>0.99286819499076961</v>
       </c>
       <c r="BD22">
-        <v>347.85846019149614</v>
+        <v>130.7497585025562</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9933,16 +9933,16 @@
         <v>429</v>
       </c>
       <c r="Y23" t="s">
-        <v>394</v>
+        <v>341</v>
       </c>
       <c r="Z23" t="s">
         <v>567</v>
       </c>
       <c r="AA23">
-        <v>0.98568311514415174</v>
+        <v>0.99660643716165165</v>
       </c>
       <c r="AB23">
-        <v>262.47622235721866</v>
+        <v>62.215318703052311</v>
       </c>
       <c r="AD23" t="s">
         <v>402</v>
@@ -9969,16 +9969,16 @@
         <v>632</v>
       </c>
       <c r="AM23" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AN23" t="s">
-        <v>557</v>
+        <v>698</v>
       </c>
       <c r="AO23">
-        <v>0.95686428742271346</v>
+        <v>0.98921594161489768</v>
       </c>
       <c r="AP23">
-        <v>790.82139725025399</v>
+        <v>197.70773706020898</v>
       </c>
       <c r="AR23" t="s">
         <v>402</v>
@@ -10005,16 +10005,16 @@
         <v>757</v>
       </c>
       <c r="BA23" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="BB23" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="BC23">
-        <v>0.96951273706693553</v>
+        <v>0.93888082510661108</v>
       </c>
       <c r="BD23">
-        <v>558.93315377284773</v>
+        <v>1120.5182063787968</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10079,16 +10079,16 @@
         <v>431</v>
       </c>
       <c r="Y24" t="s">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="Z24" t="s">
         <v>568</v>
       </c>
       <c r="AA24">
-        <v>0.99640865233383846</v>
+        <v>0.98786674666740726</v>
       </c>
       <c r="AB24">
-        <v>65.841373879627454</v>
+        <v>222.44297776420015</v>
       </c>
       <c r="AD24" t="s">
         <v>402</v>
@@ -10115,16 +10115,16 @@
         <v>634</v>
       </c>
       <c r="AM24" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="AN24" t="s">
-        <v>561</v>
+        <v>700</v>
       </c>
       <c r="AO24">
-        <v>0.96732413990250377</v>
+        <v>0.99552970818146125</v>
       </c>
       <c r="AP24">
-        <v>599.05743512076492</v>
+        <v>81.955350006543654</v>
       </c>
       <c r="AR24" t="s">
         <v>402</v>
@@ -10151,16 +10151,16 @@
         <v>759</v>
       </c>
       <c r="BA24" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="BB24" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="BC24">
-        <v>0.97175571177973974</v>
+        <v>0.98584164436602861</v>
       </c>
       <c r="BD24">
-        <v>517.81195070477202</v>
+        <v>259.56985328947479</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10225,16 +10225,16 @@
         <v>433</v>
       </c>
       <c r="Y25" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="Z25" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA25">
-        <v>0.95152672202699851</v>
+        <v>0.99400218125602058</v>
       </c>
       <c r="AB25">
-        <v>888.67676283836079</v>
+        <v>109.96001030628999</v>
       </c>
       <c r="AD25" t="s">
         <v>402</v>
@@ -10261,16 +10261,16 @@
         <v>636</v>
       </c>
       <c r="AM25" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AN25" t="s">
-        <v>703</v>
+        <v>598</v>
       </c>
       <c r="AO25">
-        <v>0.97419216130718622</v>
+        <v>0.95419187641353731</v>
       </c>
       <c r="AP25">
-        <v>473.14370936825355</v>
+        <v>839.81559908514964</v>
       </c>
       <c r="AR25" t="s">
         <v>402</v>
@@ -10297,16 +10297,16 @@
         <v>761</v>
       </c>
       <c r="BA25" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="BB25" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="BC25">
-        <v>0.97045263692858041</v>
+        <v>0.97600654740978099</v>
       </c>
       <c r="BD25">
-        <v>541.7016563093581</v>
+        <v>439.8799641540142</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10371,16 +10371,16 @@
         <v>435</v>
       </c>
       <c r="Y26" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="Z26" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA26">
-        <v>0.99439318395533605</v>
+        <v>0.99624827768323054</v>
       </c>
       <c r="AB26">
-        <v>102.7916274855054</v>
+        <v>68.781575807440518</v>
       </c>
       <c r="AD26" t="s">
         <v>402</v>
@@ -10407,16 +10407,16 @@
         <v>638</v>
       </c>
       <c r="AM26" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AN26" t="s">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="AO26">
-        <v>0.9784298046188693</v>
+        <v>0.98243109777744309</v>
       </c>
       <c r="AP26">
-        <v>395.45358198739586</v>
+        <v>322.09654074687614</v>
       </c>
       <c r="AR26" t="s">
         <v>402</v>
@@ -10443,16 +10443,16 @@
         <v>763</v>
       </c>
       <c r="BA26" t="s">
+        <v>821</v>
+      </c>
+      <c r="BB26" t="s">
         <v>822</v>
       </c>
-      <c r="BB26" t="s">
-        <v>823</v>
-      </c>
       <c r="BC26">
-        <v>0.99286819499076961</v>
+        <v>0.99556358538362921</v>
       </c>
       <c r="BD26">
-        <v>130.7497585025562</v>
+        <v>81.334267966797512</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10517,16 +10517,16 @@
         <v>437</v>
       </c>
       <c r="Y27" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Z27" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA27">
-        <v>0.99690816609326338</v>
+        <v>0.98654011406382824</v>
       </c>
       <c r="AB27">
-        <v>56.683621623505239</v>
+        <v>246.76457549648219</v>
       </c>
       <c r="AD27" t="s">
         <v>402</v>
@@ -10553,16 +10553,16 @@
         <v>640</v>
       </c>
       <c r="AM27" t="s">
+        <v>704</v>
+      </c>
+      <c r="AN27" t="s">
         <v>705</v>
       </c>
-      <c r="AN27" t="s">
-        <v>706</v>
-      </c>
       <c r="AO27">
-        <v>0.96896908104036528</v>
+        <v>0.97905895332023074</v>
       </c>
       <c r="AP27">
-        <v>568.90018092663558</v>
+        <v>383.91918912910296</v>
       </c>
       <c r="AR27" t="s">
         <v>402</v>
@@ -10589,16 +10589,16 @@
         <v>765</v>
       </c>
       <c r="BA27" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="BB27" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="BC27">
-        <v>0.93888082510661108</v>
+        <v>0.94896692115877124</v>
       </c>
       <c r="BD27">
-        <v>1120.5182063787968</v>
+        <v>935.60644542252658</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10663,16 +10663,16 @@
         <v>439</v>
       </c>
       <c r="Y28" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="Z28" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AA28">
-        <v>0.97592802238295073</v>
+        <v>0.97006538483877391</v>
       </c>
       <c r="AB28">
-        <v>441.3195896459041</v>
+        <v>548.80127795581154</v>
       </c>
       <c r="AD28" t="s">
         <v>402</v>
@@ -10699,16 +10699,16 @@
         <v>642</v>
       </c>
       <c r="AM28" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AN28" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="AO28">
-        <v>0.97444089635831932</v>
+        <v>0.94748255895881095</v>
       </c>
       <c r="AP28">
-        <v>468.58356676414513</v>
+        <v>962.81975242179908</v>
       </c>
       <c r="AR28" t="s">
         <v>402</v>
@@ -10735,16 +10735,16 @@
         <v>767</v>
       </c>
       <c r="BA28" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="BB28" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="BC28">
-        <v>0.96620229207214314</v>
+        <v>0.93885489623641283</v>
       </c>
       <c r="BD28">
-        <v>619.62464534404216</v>
+        <v>1120.9935689990987</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10809,16 +10809,16 @@
         <v>441</v>
       </c>
       <c r="Y29" t="s">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="Z29" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="AA29">
-        <v>0.97807026787476981</v>
+        <v>0.96517074323544272</v>
       </c>
       <c r="AB29">
-        <v>402.04508896255408</v>
+        <v>638.53637401688275</v>
       </c>
       <c r="AD29" t="s">
         <v>402</v>
@@ -10845,16 +10845,16 @@
         <v>644</v>
       </c>
       <c r="AM29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AN29" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="AO29">
-        <v>0.97186368651165222</v>
+        <v>0.95796808346245155</v>
       </c>
       <c r="AP29">
-        <v>515.83241395304219</v>
+        <v>770.58513652172257</v>
       </c>
       <c r="AR29" t="s">
         <v>402</v>
@@ -10881,16 +10881,16 @@
         <v>769</v>
       </c>
       <c r="BA29" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="BB29" t="s">
-        <v>827</v>
+        <v>573</v>
       </c>
       <c r="BC29">
-        <v>0.98770095291302495</v>
+        <v>0.96587851707660599</v>
       </c>
       <c r="BD29">
-        <v>225.48252992787681</v>
+        <v>625.56052026222312</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10955,16 +10955,16 @@
         <v>443</v>
       </c>
       <c r="Y30" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="Z30" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA30">
-        <v>0.96276589991882666</v>
+        <v>0.9771016434875236</v>
       </c>
       <c r="AB30">
-        <v>682.62516815484491</v>
+        <v>419.80320272873433</v>
       </c>
       <c r="AD30" t="s">
         <v>402</v>
@@ -10991,16 +10991,16 @@
         <v>646</v>
       </c>
       <c r="AM30" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AN30" t="s">
-        <v>710</v>
+        <v>572</v>
       </c>
       <c r="AO30">
-        <v>0.97532618723790843</v>
+        <v>0.9436975669946106</v>
       </c>
       <c r="AP30">
-        <v>452.35323397167849</v>
+        <v>1032.2112717654718</v>
       </c>
       <c r="AR30" t="s">
         <v>402</v>
@@ -11027,16 +11027,16 @@
         <v>771</v>
       </c>
       <c r="BA30" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="BB30" t="s">
-        <v>575</v>
+        <v>827</v>
       </c>
       <c r="BC30">
-        <v>0.9602868544779749</v>
+        <v>0.99036076428701636</v>
       </c>
       <c r="BD30">
-        <v>728.07433457046079</v>
+        <v>176.71932140470005</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11101,16 +11101,16 @@
         <v>445</v>
       </c>
       <c r="Y31" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="Z31" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="AA31">
-        <v>0.98628621327161703</v>
+        <v>0.99627301415801128</v>
       </c>
       <c r="AB31">
-        <v>251.41942335368827</v>
+        <v>68.328073769792198</v>
       </c>
       <c r="AD31" t="s">
         <v>402</v>
@@ -11137,16 +11137,16 @@
         <v>648</v>
       </c>
       <c r="AM31" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="AN31" t="s">
-        <v>591</v>
+        <v>710</v>
       </c>
       <c r="AO31">
-        <v>0.97755933784246885</v>
+        <v>0.99557021775830368</v>
       </c>
       <c r="AP31">
-        <v>411.4121395547387</v>
+        <v>81.21267443109943</v>
       </c>
       <c r="AR31" t="s">
         <v>402</v>
@@ -11173,16 +11173,16 @@
         <v>773</v>
       </c>
       <c r="BA31" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="BB31" t="s">
-        <v>830</v>
+        <v>573</v>
       </c>
       <c r="BC31">
-        <v>0.98529032090802915</v>
+        <v>0.98102590217137298</v>
       </c>
       <c r="BD31">
-        <v>269.67745001946554</v>
+        <v>347.85846019149614</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11247,16 +11247,16 @@
         <v>447</v>
       </c>
       <c r="Y32" t="s">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="Z32" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA32">
-        <v>0.98392857039426507</v>
+        <v>0.99633073297550734</v>
       </c>
       <c r="AB32">
-        <v>294.64287610514066</v>
+        <v>67.269895449032902</v>
       </c>
       <c r="AD32" t="s">
         <v>402</v>
@@ -11283,16 +11283,16 @@
         <v>650</v>
       </c>
       <c r="AM32" t="s">
+        <v>711</v>
+      </c>
+      <c r="AN32" t="s">
         <v>712</v>
       </c>
-      <c r="AN32" t="s">
-        <v>575</v>
-      </c>
       <c r="AO32">
-        <v>0.97739363651485267</v>
+        <v>0.99117435469129123</v>
       </c>
       <c r="AP32">
-        <v>414.44999722770137</v>
+        <v>161.80349732632692</v>
       </c>
       <c r="AR32" t="s">
         <v>402</v>
@@ -11319,16 +11319,16 @@
         <v>775</v>
       </c>
       <c r="BA32" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="BB32" t="s">
-        <v>575</v>
+        <v>830</v>
       </c>
       <c r="BC32">
-        <v>0.96834660314974419</v>
+        <v>0.98716759869587867</v>
       </c>
       <c r="BD32">
-        <v>580.31227558802345</v>
+        <v>235.26069057555824</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11393,16 +11393,16 @@
         <v>449</v>
       </c>
       <c r="Y33" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="Z33" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="AA33">
-        <v>0.98985535554561865</v>
+        <v>0.9725266797570975</v>
       </c>
       <c r="AB33">
-        <v>185.9851483303255</v>
+        <v>503.67753778654668</v>
       </c>
       <c r="AD33" t="s">
         <v>402</v>
@@ -11435,10 +11435,10 @@
         <v>714</v>
       </c>
       <c r="AO33">
-        <v>0.98921594161489768</v>
+        <v>0.99101688837209245</v>
       </c>
       <c r="AP33">
-        <v>197.70773706020898</v>
+        <v>164.69037984497118</v>
       </c>
       <c r="AR33" t="s">
         <v>402</v>
@@ -11465,16 +11465,16 @@
         <v>777</v>
       </c>
       <c r="BA33" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="BB33" t="s">
-        <v>833</v>
+        <v>575</v>
       </c>
       <c r="BC33">
-        <v>0.98373391026642343</v>
+        <v>0.96620229207214314</v>
       </c>
       <c r="BD33">
-        <v>298.21164511556987</v>
+        <v>619.62464534404216</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11539,16 +11539,16 @@
         <v>451</v>
       </c>
       <c r="Y34" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Z34" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AA34">
-        <v>0.96781787899545535</v>
+        <v>0.9912986266790621</v>
       </c>
       <c r="AB34">
-        <v>590.00555174998567</v>
+        <v>159.52517755052818</v>
       </c>
       <c r="AD34" t="s">
         <v>402</v>
@@ -11581,10 +11581,10 @@
         <v>716</v>
       </c>
       <c r="AO34">
-        <v>0.99552970818146125</v>
+        <v>0.9755246434835193</v>
       </c>
       <c r="AP34">
-        <v>81.955350006543654</v>
+        <v>448.71486946881294</v>
       </c>
       <c r="AR34" t="s">
         <v>402</v>
@@ -11611,16 +11611,16 @@
         <v>779</v>
       </c>
       <c r="BA34" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="BB34" t="s">
-        <v>575</v>
+        <v>833</v>
       </c>
       <c r="BC34">
-        <v>0.98908976773019719</v>
+        <v>0.98770095291302495</v>
       </c>
       <c r="BD34">
-        <v>200.02092494638529</v>
+        <v>225.48252992787681</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11685,16 +11685,16 @@
         <v>453</v>
       </c>
       <c r="Y35" t="s">
-        <v>399</v>
+        <v>353</v>
       </c>
       <c r="Z35" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AA35">
-        <v>0.97597719784352066</v>
+        <v>0.99619242046188483</v>
       </c>
       <c r="AB35">
-        <v>440.41803953545457</v>
+        <v>69.805624865443917</v>
       </c>
       <c r="AD35" t="s">
         <v>402</v>
@@ -11724,13 +11724,13 @@
         <v>717</v>
       </c>
       <c r="AN35" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="AO35">
-        <v>0.95419187641353731</v>
+        <v>0.9574422475745189</v>
       </c>
       <c r="AP35">
-        <v>839.81559908514964</v>
+        <v>780.22546113382077</v>
       </c>
       <c r="AR35" t="s">
         <v>402</v>
@@ -11757,16 +11757,16 @@
         <v>781</v>
       </c>
       <c r="BA35" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="BB35" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="BC35">
-        <v>0.93477394593085072</v>
+        <v>0.9602868544779749</v>
       </c>
       <c r="BD35">
-        <v>1195.8109912677364</v>
+        <v>728.07433457046079</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11831,16 +11831,16 @@
         <v>455</v>
       </c>
       <c r="Y36" t="s">
-        <v>335</v>
+        <v>383</v>
       </c>
       <c r="Z36" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AA36">
-        <v>0.96517074323544272</v>
+        <v>0.96239325925412511</v>
       </c>
       <c r="AB36">
-        <v>638.53637401688275</v>
+        <v>689.45691367437246</v>
       </c>
       <c r="AD36" t="s">
         <v>402</v>
@@ -11870,13 +11870,13 @@
         <v>718</v>
       </c>
       <c r="AN36" t="s">
-        <v>719</v>
+        <v>583</v>
       </c>
       <c r="AO36">
-        <v>0.97905895332023074</v>
+        <v>0.97673972771258222</v>
       </c>
       <c r="AP36">
-        <v>383.91918912910296</v>
+        <v>426.43832526932584</v>
       </c>
       <c r="AR36" t="s">
         <v>402</v>
@@ -11903,16 +11903,16 @@
         <v>783</v>
       </c>
       <c r="BA36" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="BB36" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="BC36">
-        <v>0.95614590843046721</v>
+        <v>0.96951273706693553</v>
       </c>
       <c r="BD36">
-        <v>803.99167877476805</v>
+        <v>558.93315377284773</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11977,16 +11977,16 @@
         <v>457</v>
       </c>
       <c r="Y37" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="Z37" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AA37">
-        <v>0.9771016434875236</v>
+        <v>0.95110614119885384</v>
       </c>
       <c r="AB37">
-        <v>419.80320272873433</v>
+        <v>896.38741135434657</v>
       </c>
       <c r="AD37" t="s">
         <v>402</v>
@@ -12013,16 +12013,16 @@
         <v>660</v>
       </c>
       <c r="AM37" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AN37" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AO37">
-        <v>0.94748255895881095</v>
+        <v>0.95686428742271346</v>
       </c>
       <c r="AP37">
-        <v>962.81975242179908</v>
+        <v>790.82139725025399</v>
       </c>
       <c r="AR37" t="s">
         <v>402</v>
@@ -12049,16 +12049,16 @@
         <v>785</v>
       </c>
       <c r="BA37" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="BB37" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="BC37">
-        <v>0.95197431053166182</v>
+        <v>0.97175571177973974</v>
       </c>
       <c r="BD37">
-        <v>880.47097358620078</v>
+        <v>517.81195070477202</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12123,16 +12123,16 @@
         <v>459</v>
       </c>
       <c r="Y38" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="Z38" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="AA38">
-        <v>0.99720517126173747</v>
+        <v>0.98223116847554315</v>
       </c>
       <c r="AB38">
-        <v>51.238526868146437</v>
+        <v>325.76191128170939</v>
       </c>
       <c r="AD38" t="s">
         <v>402</v>
@@ -12159,16 +12159,16 @@
         <v>662</v>
       </c>
       <c r="AM38" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AN38" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="AO38">
-        <v>0.95796808346245155</v>
+        <v>0.96732413990250377</v>
       </c>
       <c r="AP38">
-        <v>770.58513652172257</v>
+        <v>599.05743512076492</v>
       </c>
       <c r="AR38" t="s">
         <v>402</v>
@@ -12195,16 +12195,16 @@
         <v>787</v>
       </c>
       <c r="BA38" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="BB38" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="BC38">
-        <v>0.96625736872930745</v>
+        <v>0.97045263692858041</v>
       </c>
       <c r="BD38">
-        <v>618.61490662936239</v>
+        <v>541.7016563093581</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12269,16 +12269,16 @@
         <v>461</v>
       </c>
       <c r="Y39" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="Z39" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AA39">
-        <v>0.98421229582412162</v>
+        <v>0.9944769137527022</v>
       </c>
       <c r="AB39">
-        <v>289.44124322443668</v>
+        <v>101.25658120045976</v>
       </c>
       <c r="AD39" t="s">
         <v>402</v>
@@ -12305,16 +12305,16 @@
         <v>664</v>
       </c>
       <c r="AM39" t="s">
+        <v>721</v>
+      </c>
+      <c r="AN39" t="s">
         <v>722</v>
       </c>
-      <c r="AN39" t="s">
-        <v>557</v>
-      </c>
       <c r="AO39">
-        <v>0.9436975669946106</v>
+        <v>0.97419216130718622</v>
       </c>
       <c r="AP39">
-        <v>1032.2112717654718</v>
+        <v>473.14370936825355</v>
       </c>
       <c r="AR39" t="s">
         <v>402</v>
@@ -12341,16 +12341,16 @@
         <v>789</v>
       </c>
       <c r="BA39" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="BB39" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="BC39">
-        <v>0.93693021635476914</v>
+        <v>0.93477394593085072</v>
       </c>
       <c r="BD39">
-        <v>1156.2793668292329</v>
+        <v>1195.8109912677364</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12415,16 +12415,16 @@
         <v>463</v>
       </c>
       <c r="Y40" t="s">
-        <v>332</v>
+        <v>393</v>
       </c>
       <c r="Z40" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AA40">
-        <v>0.97067956893851193</v>
+        <v>0.96493395982863905</v>
       </c>
       <c r="AB40">
-        <v>537.54123612728188</v>
+        <v>642.87740314161726</v>
       </c>
       <c r="AD40" t="s">
         <v>402</v>
@@ -12454,13 +12454,13 @@
         <v>723</v>
       </c>
       <c r="AN40" t="s">
-        <v>724</v>
+        <v>573</v>
       </c>
       <c r="AO40">
-        <v>0.99557021775830368</v>
+        <v>0.9784298046188693</v>
       </c>
       <c r="AP40">
-        <v>81.21267443109943</v>
+        <v>395.45358198739586</v>
       </c>
       <c r="AR40" t="s">
         <v>402</v>
@@ -12487,16 +12487,16 @@
         <v>791</v>
       </c>
       <c r="BA40" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="BB40" t="s">
-        <v>558</v>
+        <v>598</v>
       </c>
       <c r="BC40">
-        <v>0.94041102627936679</v>
+        <v>0.95614590843046721</v>
       </c>
       <c r="BD40">
-        <v>1092.4645182116094</v>
+        <v>803.99167877476805</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12561,16 +12561,16 @@
         <v>465</v>
       </c>
       <c r="Y41" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="Z41" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="AA41">
-        <v>0.98091465074522166</v>
+        <v>0.99218536928207235</v>
       </c>
       <c r="AB41">
-        <v>349.89806967093693</v>
+        <v>143.26822982867444</v>
       </c>
       <c r="AD41" t="s">
         <v>402</v>
@@ -12597,16 +12597,16 @@
         <v>668</v>
       </c>
       <c r="AM41" t="s">
+        <v>724</v>
+      </c>
+      <c r="AN41" t="s">
         <v>725</v>
       </c>
-      <c r="AN41" t="s">
-        <v>684</v>
-      </c>
       <c r="AO41">
-        <v>0.98177850613436324</v>
+        <v>0.97532618723790843</v>
       </c>
       <c r="AP41">
-        <v>334.06072087000706</v>
+        <v>452.35323397167849</v>
       </c>
       <c r="AR41" t="s">
         <v>402</v>
@@ -12633,16 +12633,16 @@
         <v>793</v>
       </c>
       <c r="BA41" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="BB41" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="BC41">
-        <v>0.95063651087703893</v>
+        <v>0.95197431053166182</v>
       </c>
       <c r="BD41">
-        <v>904.99730058761952</v>
+        <v>880.47097358620078</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12707,16 +12707,16 @@
         <v>467</v>
       </c>
       <c r="Y42" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="Z42" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AA42">
-        <v>0.97678876819750537</v>
+        <v>0.99332429446553039</v>
       </c>
       <c r="AB42">
-        <v>425.5392497124015</v>
+        <v>122.38793479860949</v>
       </c>
       <c r="AD42" t="s">
         <v>402</v>
@@ -12746,13 +12746,13 @@
         <v>726</v>
       </c>
       <c r="AN42" t="s">
-        <v>727</v>
+        <v>561</v>
       </c>
       <c r="AO42">
-        <v>0.98895557240687315</v>
+        <v>0.97755933784246885</v>
       </c>
       <c r="AP42">
-        <v>202.48117254065832</v>
+        <v>411.4121395547387</v>
       </c>
       <c r="AR42" t="s">
         <v>402</v>
@@ -12779,16 +12779,16 @@
         <v>795</v>
       </c>
       <c r="BA42" t="s">
+        <v>841</v>
+      </c>
+      <c r="BB42" t="s">
         <v>842</v>
       </c>
-      <c r="BB42" t="s">
-        <v>843</v>
-      </c>
       <c r="BC42">
-        <v>0.99556358538362921</v>
+        <v>0.98373391026642343</v>
       </c>
       <c r="BD42">
-        <v>81.334267966797512</v>
+        <v>298.21164511556987</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12853,16 +12853,16 @@
         <v>469</v>
       </c>
       <c r="Y43" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="Z43" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="AA43">
-        <v>0.99660643716165165</v>
+        <v>0.99496216240453639</v>
       </c>
       <c r="AB43">
-        <v>62.215318703052311</v>
+        <v>92.360355916833001</v>
       </c>
       <c r="AD43" t="s">
         <v>402</v>
@@ -12889,16 +12889,16 @@
         <v>672</v>
       </c>
       <c r="AM43" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AN43" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="AO43">
-        <v>0.95753456607285348</v>
+        <v>0.97739363651485267</v>
       </c>
       <c r="AP43">
-        <v>778.53295533101902</v>
+        <v>414.44999722770137</v>
       </c>
       <c r="AR43" t="s">
         <v>402</v>
@@ -12925,16 +12925,16 @@
         <v>797</v>
       </c>
       <c r="BA43" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="BB43" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="BC43">
-        <v>0.94896692115877124</v>
+        <v>0.98908976773019719</v>
       </c>
       <c r="BD43">
-        <v>935.60644542252658</v>
+        <v>200.02092494638529</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12999,16 +12999,16 @@
         <v>471</v>
       </c>
       <c r="Y44" t="s">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="Z44" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="AA44">
-        <v>0.98786674666740726</v>
+        <v>0.97702953960894623</v>
       </c>
       <c r="AB44">
-        <v>222.44297776420015</v>
+        <v>421.12510716931934</v>
       </c>
       <c r="AD44" t="s">
         <v>402</v>
@@ -13035,16 +13035,16 @@
         <v>674</v>
       </c>
       <c r="AM44" t="s">
+        <v>728</v>
+      </c>
+      <c r="AN44" t="s">
         <v>729</v>
       </c>
-      <c r="AN44" t="s">
-        <v>557</v>
-      </c>
       <c r="AO44">
-        <v>0.94698201881115829</v>
+        <v>0.96896908104036528</v>
       </c>
       <c r="AP44">
-        <v>971.99632179543119</v>
+        <v>568.90018092663558</v>
       </c>
       <c r="AR44" t="s">
         <v>402</v>
@@ -13071,16 +13071,16 @@
         <v>799</v>
       </c>
       <c r="BA44" t="s">
+        <v>844</v>
+      </c>
+      <c r="BB44" t="s">
         <v>845</v>
       </c>
-      <c r="BB44" t="s">
-        <v>575</v>
-      </c>
       <c r="BC44">
-        <v>0.93885489623641283</v>
+        <v>0.98529032090802915</v>
       </c>
       <c r="BD44">
-        <v>1120.9935689990987</v>
+        <v>269.67745001946554</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -13145,16 +13145,16 @@
         <v>473</v>
       </c>
       <c r="Y45" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="Z45" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="AA45">
-        <v>0.99400218125602058</v>
+        <v>0.98631766623578765</v>
       </c>
       <c r="AB45">
-        <v>109.96001030628999</v>
+        <v>250.84278567722609</v>
       </c>
       <c r="AD45" t="s">
         <v>402</v>
@@ -13220,13 +13220,13 @@
         <v>846</v>
       </c>
       <c r="BB45" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="BC45">
-        <v>0.96587851707660599</v>
+        <v>0.96834660314974419</v>
       </c>
       <c r="BD45">
-        <v>625.56052026222312</v>
+        <v>580.31227558802345</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13291,16 +13291,16 @@
         <v>475</v>
       </c>
       <c r="Y46" t="s">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="Z46" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="AA46">
-        <v>0.99624827768323054</v>
+        <v>0.96912603699420019</v>
       </c>
       <c r="AB46">
-        <v>68.781575807440518</v>
+        <v>566.02265510632935</v>
       </c>
       <c r="AD46" t="s">
         <v>402</v>
@@ -13330,7 +13330,7 @@
         <v>732</v>
       </c>
       <c r="AN46" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="AO46">
         <v>0.98026073113098933</v>
@@ -13401,16 +13401,16 @@
         <v>477</v>
       </c>
       <c r="Y47" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Z47" t="s">
         <v>584</v>
       </c>
       <c r="AA47">
-        <v>0.98654011406382824</v>
+        <v>0.98696950091677516</v>
       </c>
       <c r="AB47">
-        <v>246.76457549648219</v>
+        <v>238.89248319245524</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13475,16 +13475,16 @@
         <v>479</v>
       </c>
       <c r="Y48" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="Z48" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="AA48">
-        <v>0.97006538483877391</v>
+        <v>0.98568311514415174</v>
       </c>
       <c r="AB48">
-        <v>548.80127795581154</v>
+        <v>262.47622235721866</v>
       </c>
     </row>
     <row r="49" spans="2:28">
@@ -13549,16 +13549,16 @@
         <v>481</v>
       </c>
       <c r="Y49" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="Z49" t="s">
         <v>585</v>
       </c>
       <c r="AA49">
-        <v>0.98903719509068366</v>
+        <v>0.99640865233383846</v>
       </c>
       <c r="AB49">
-        <v>200.98475667080021</v>
+        <v>65.841373879627454</v>
       </c>
     </row>
     <row r="50" spans="2:28">
@@ -13623,16 +13623,16 @@
         <v>483</v>
       </c>
       <c r="Y50" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="Z50" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AA50">
-        <v>0.9966278856580183</v>
+        <v>0.95152672202699851</v>
       </c>
       <c r="AB50">
-        <v>61.822096269664314</v>
+        <v>888.67676283836079</v>
       </c>
     </row>
     <row r="51" spans="2:28">
@@ -13697,16 +13697,16 @@
         <v>485</v>
       </c>
       <c r="Y51" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="Z51" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AA51">
-        <v>0.99689080338218783</v>
+        <v>0.99439318395533605</v>
       </c>
       <c r="AB51">
-        <v>57.001937993222221</v>
+        <v>102.7916274855054</v>
       </c>
     </row>
     <row r="52" spans="2:28">
@@ -13771,16 +13771,16 @@
         <v>487</v>
       </c>
       <c r="Y52" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="Z52" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="AA52">
-        <v>0.98451878015346617</v>
+        <v>0.98903719509068366</v>
       </c>
       <c r="AB52">
-        <v>283.82236385312052</v>
+        <v>200.98475667080021</v>
       </c>
     </row>
     <row r="53" spans="2:28">
@@ -13845,16 +13845,16 @@
         <v>489</v>
       </c>
       <c r="Y53" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="Z53" t="s">
         <v>588</v>
       </c>
       <c r="AA53">
-        <v>0.9956937957649058</v>
+        <v>0.9966278856580183</v>
       </c>
       <c r="AB53">
-        <v>78.947077643392717</v>
+        <v>61.822096269664314</v>
       </c>
     </row>
     <row r="54" spans="2:28">
@@ -13919,16 +13919,16 @@
         <v>491</v>
       </c>
       <c r="Y54" t="s">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="Z54" t="s">
         <v>589</v>
       </c>
       <c r="AA54">
-        <v>0.99719604020926056</v>
+        <v>0.99689080338218783</v>
       </c>
       <c r="AB54">
-        <v>51.405929496890515</v>
+        <v>57.001937993222221</v>
       </c>
     </row>
     <row r="55" spans="2:28">
@@ -13993,16 +13993,16 @@
         <v>493</v>
       </c>
       <c r="Y55" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="Z55" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="AA55">
-        <v>0.9791414671967239</v>
+        <v>0.98451878015346617</v>
       </c>
       <c r="AB55">
-        <v>382.40643472672787</v>
+        <v>283.82236385312052</v>
       </c>
     </row>
     <row r="56" spans="2:28">
@@ -14067,16 +14067,16 @@
         <v>495</v>
       </c>
       <c r="Y56" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="Z56" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AA56">
-        <v>0.98267907851268621</v>
+        <v>0.9956937957649058</v>
       </c>
       <c r="AB56">
-        <v>317.55022726741913</v>
+        <v>78.947077643392717</v>
       </c>
     </row>
     <row r="57" spans="2:28">
@@ -14141,16 +14141,16 @@
         <v>497</v>
       </c>
       <c r="Y57" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="Z57" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="AA57">
-        <v>0.94688476071898231</v>
+        <v>0.97496236164466343</v>
       </c>
       <c r="AB57">
-        <v>973.77938681865817</v>
+        <v>459.02336984783733</v>
       </c>
     </row>
     <row r="58" spans="2:28">
@@ -14215,16 +14215,16 @@
         <v>499</v>
       </c>
       <c r="Y58" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="Z58" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AA58">
-        <v>0.95227568919833094</v>
+        <v>0.96911860205632039</v>
       </c>
       <c r="AB58">
-        <v>874.94569803060017</v>
+        <v>566.15896230079227</v>
       </c>
     </row>
     <row r="59" spans="2:28">
@@ -14289,16 +14289,16 @@
         <v>501</v>
       </c>
       <c r="Y59" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="Z59" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AA59">
-        <v>0.99017812457307008</v>
+        <v>0.99719604020926056</v>
       </c>
       <c r="AB59">
-        <v>180.06771616038245</v>
+        <v>51.405929496890515</v>
       </c>
     </row>
     <row r="60" spans="2:28">
@@ -14363,16 +14363,16 @@
         <v>503</v>
       </c>
       <c r="Y60" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="Z60" t="s">
-        <v>559</v>
+        <v>593</v>
       </c>
       <c r="AA60">
-        <v>0.99088855789814245</v>
+        <v>0.9791414671967239</v>
       </c>
       <c r="AB60">
-        <v>167.04310520072229</v>
+        <v>382.40643472672787</v>
       </c>
     </row>
     <row r="61" spans="2:28">
@@ -14437,16 +14437,16 @@
         <v>505</v>
       </c>
       <c r="Y61" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="Z61" t="s">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="AA61">
-        <v>0.9944769137527022</v>
+        <v>0.98267907851268621</v>
       </c>
       <c r="AB61">
-        <v>101.25658120045976</v>
+        <v>317.55022726741913</v>
       </c>
     </row>
     <row r="62" spans="2:28">
@@ -14511,16 +14511,16 @@
         <v>507</v>
       </c>
       <c r="Y62" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="Z62" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="AA62">
-        <v>0.96493395982863905</v>
+        <v>0.94688476071898231</v>
       </c>
       <c r="AB62">
-        <v>642.87740314161726</v>
+        <v>973.77938681865817</v>
       </c>
     </row>
     <row r="63" spans="2:28">
@@ -14585,16 +14585,16 @@
         <v>509</v>
       </c>
       <c r="Y63" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="Z63" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AA63">
-        <v>0.99218536928207235</v>
+        <v>0.95227568919833094</v>
       </c>
       <c r="AB63">
-        <v>143.26822982867444</v>
+        <v>874.94569803060017</v>
       </c>
     </row>
     <row r="64" spans="2:28">
@@ -14659,16 +14659,16 @@
         <v>511</v>
       </c>
       <c r="Y64" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="Z64" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="AA64">
-        <v>0.99332429446553039</v>
+        <v>0.99017812457307008</v>
       </c>
       <c r="AB64">
-        <v>122.38793479860949</v>
+        <v>180.06771616038245</v>
       </c>
     </row>
     <row r="65" spans="2:28">
@@ -14733,16 +14733,16 @@
         <v>513</v>
       </c>
       <c r="Y65" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="Z65" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="AA65">
-        <v>0.99496216240453639</v>
+        <v>0.99088855789814245</v>
       </c>
       <c r="AB65">
-        <v>92.360355916833001</v>
+        <v>167.04310520072229</v>
       </c>
     </row>
     <row r="66" spans="2:28">
@@ -14807,16 +14807,16 @@
         <v>515</v>
       </c>
       <c r="Y66" t="s">
-        <v>398</v>
+        <v>328</v>
       </c>
       <c r="Z66" t="s">
         <v>575</v>
       </c>
       <c r="AA66">
-        <v>0.97702953960894623</v>
+        <v>0.98985535554561865</v>
       </c>
       <c r="AB66">
-        <v>421.12510716931934</v>
+        <v>185.9851483303255</v>
       </c>
     </row>
     <row r="67" spans="2:28">
@@ -14881,16 +14881,16 @@
         <v>517</v>
       </c>
       <c r="Y67" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="Z67" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="AA67">
-        <v>0.98631766623578765</v>
+        <v>0.96781787899545535</v>
       </c>
       <c r="AB67">
-        <v>250.84278567722609</v>
+        <v>590.00555174998567</v>
       </c>
     </row>
     <row r="68" spans="2:28">
@@ -14955,16 +14955,16 @@
         <v>519</v>
       </c>
       <c r="Y68" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Z68" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AA68">
-        <v>0.96912603699420019</v>
+        <v>0.97597719784352066</v>
       </c>
       <c r="AB68">
-        <v>566.02265510632935</v>
+        <v>440.41803953545457</v>
       </c>
     </row>
     <row r="69" spans="2:28">
@@ -15029,16 +15029,16 @@
         <v>521</v>
       </c>
       <c r="Y69" t="s">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="Z69" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA69">
-        <v>0.99770573728283862</v>
+        <v>0.96710197646129548</v>
       </c>
       <c r="AB69">
-        <v>42.061483147959365</v>
+        <v>603.13043154291677</v>
       </c>
     </row>
     <row r="70" spans="2:28">
@@ -15103,16 +15103,16 @@
         <v>523</v>
       </c>
       <c r="Y70" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="Z70" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AA70">
-        <v>0.99118992399256634</v>
+        <v>0.97245598614016138</v>
       </c>
       <c r="AB70">
-        <v>161.51806013628308</v>
+        <v>504.97358743037506</v>
       </c>
     </row>
     <row r="71" spans="2:28">
@@ -15177,16 +15177,16 @@
         <v>525</v>
       </c>
       <c r="Y71" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z71" t="s">
-        <v>562</v>
+        <v>598</v>
       </c>
       <c r="AA71">
-        <v>0.9582992451809369</v>
+        <v>0.97006792991713942</v>
       </c>
       <c r="AB71">
-        <v>764.51383834949013</v>
+        <v>548.75461818577651</v>
       </c>
     </row>
     <row r="72" spans="2:28">
@@ -15251,16 +15251,16 @@
         <v>527</v>
       </c>
       <c r="Y72" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="Z72" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AA72">
-        <v>0.95289359663592565</v>
+        <v>0.99770573728283862</v>
       </c>
       <c r="AB72">
-        <v>863.61739500803003</v>
+        <v>42.061483147959365</v>
       </c>
     </row>
     <row r="73" spans="2:28">
@@ -15325,16 +15325,16 @@
         <v>529</v>
       </c>
       <c r="Y73" t="s">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="Z73" t="s">
-        <v>598</v>
+        <v>563</v>
       </c>
       <c r="AA73">
-        <v>0.97577723283636553</v>
+        <v>0.99118992399256634</v>
       </c>
       <c r="AB73">
-        <v>444.08406466663115</v>
+        <v>161.51806013628308</v>
       </c>
     </row>
     <row r="74" spans="2:28">
@@ -15399,16 +15399,16 @@
         <v>531</v>
       </c>
       <c r="Y74" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="Z74" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="AA74">
-        <v>0.97496236164466343</v>
+        <v>0.9582992451809369</v>
       </c>
       <c r="AB74">
-        <v>459.02336984783733</v>
+        <v>764.51383834949013</v>
       </c>
     </row>
     <row r="75" spans="2:28">
@@ -15473,16 +15473,16 @@
         <v>533</v>
       </c>
       <c r="Y75" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="Z75" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA75">
-        <v>0.96911860205632039</v>
+        <v>0.95289359663592565</v>
       </c>
       <c r="AB75">
-        <v>566.15896230079227</v>
+        <v>863.61739500803003</v>
       </c>
     </row>
     <row r="76" spans="2:28">
@@ -15547,16 +15547,16 @@
         <v>535</v>
       </c>
       <c r="Y76" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="Z76" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA76">
-        <v>0.99620173788084643</v>
+        <v>0.97577723283636553</v>
       </c>
       <c r="AB76">
-        <v>69.634805517815565</v>
+        <v>444.08406466663115</v>
       </c>
     </row>
     <row r="77" spans="2:28">
@@ -15621,16 +15621,16 @@
         <v>537</v>
       </c>
       <c r="Y77" t="s">
-        <v>390</v>
+        <v>354</v>
       </c>
       <c r="Z77" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA77">
-        <v>0.99808042106452499</v>
+        <v>0.99635032886115649</v>
       </c>
       <c r="AB77">
-        <v>35.192280483708828</v>
+        <v>66.910637545464084</v>
       </c>
     </row>
     <row r="78" spans="2:28">
@@ -15695,16 +15695,16 @@
         <v>539</v>
       </c>
       <c r="Y78" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="Z78" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA78">
-        <v>0.99235892038811246</v>
+        <v>0.98520673013262905</v>
       </c>
       <c r="AB78">
-        <v>140.08645955127213</v>
+        <v>271.20994756846727</v>
       </c>
     </row>
     <row r="79" spans="2:28">
@@ -15769,16 +15769,16 @@
         <v>541</v>
       </c>
       <c r="Y79" t="s">
-        <v>376</v>
+        <v>339</v>
       </c>
       <c r="Z79" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AA79">
-        <v>0.97311459430172587</v>
+        <v>0.99690816609326338</v>
       </c>
       <c r="AB79">
-        <v>492.8991044683591</v>
+        <v>56.683621623505239</v>
       </c>
     </row>
     <row r="80" spans="2:28">
@@ -15843,16 +15843,16 @@
         <v>543</v>
       </c>
       <c r="Y80" t="s">
-        <v>377</v>
+        <v>333</v>
       </c>
       <c r="Z80" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA80">
-        <v>0.95854557991594525</v>
+        <v>0.97592802238295073</v>
       </c>
       <c r="AB80">
-        <v>759.99770154100372</v>
+        <v>441.3195896459041</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -15917,16 +15917,16 @@
         <v>545</v>
       </c>
       <c r="Y81" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z81" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="AA81">
-        <v>0.98524310910972257</v>
+        <v>0.97807026787476981</v>
       </c>
       <c r="AB81">
-        <v>270.5429996550854</v>
+        <v>402.04508896255408</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -15991,16 +15991,16 @@
         <v>547</v>
       </c>
       <c r="Y82" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="Z82" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="AA82">
-        <v>0.94713624989887801</v>
+        <v>0.96276589991882666</v>
       </c>
       <c r="AB82">
-        <v>969.16875185390393</v>
+        <v>682.62516815484491</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16065,16 +16065,16 @@
         <v>549</v>
       </c>
       <c r="Y83" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="Z83" t="s">
-        <v>606</v>
+        <v>565</v>
       </c>
       <c r="AA83">
-        <v>0.99635032886115649</v>
+        <v>0.98628621327161703</v>
       </c>
       <c r="AB83">
-        <v>66.910637545464084</v>
+        <v>251.41942335368827</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -16139,16 +16139,16 @@
         <v>551</v>
       </c>
       <c r="Y84" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="Z84" t="s">
         <v>607</v>
       </c>
       <c r="AA84">
-        <v>0.98520673013262905</v>
+        <v>0.98392857039426507</v>
       </c>
       <c r="AB84">
-        <v>271.20994756846727</v>
+        <v>294.64287610514066</v>
       </c>
     </row>
   </sheetData>
@@ -16157,7 +16157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A880180D-94CA-4156-A5AB-3BAFD74C3946}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C4D2FB-6089-4D0E-8038-2D78AEED9933}">
   <dimension ref="B9:Z46"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16269,7 +16269,7 @@
         <v>847</v>
       </c>
       <c r="K11" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="L11">
         <v>0.129291216127222</v>
@@ -16302,7 +16302,7 @@
         <v>919</v>
       </c>
       <c r="X11" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="Y11">
         <v>6.6577500000000001</v>
@@ -16337,7 +16337,7 @@
         <v>849</v>
       </c>
       <c r="K12" t="s">
-        <v>705</v>
+        <v>728</v>
       </c>
       <c r="L12">
         <v>1.2472977367603104</v>
@@ -16370,7 +16370,7 @@
         <v>921</v>
       </c>
       <c r="X12" t="s">
-        <v>839</v>
+        <v>809</v>
       </c>
       <c r="Y12">
         <v>54.581249999999997</v>
@@ -16405,7 +16405,7 @@
         <v>851</v>
       </c>
       <c r="K13" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="L13">
         <v>2.318274719104624</v>
@@ -16438,7 +16438,7 @@
         <v>923</v>
       </c>
       <c r="X13" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="Y13">
         <v>18.436499999999999</v>
@@ -16473,7 +16473,7 @@
         <v>853</v>
       </c>
       <c r="K14" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L14">
         <v>0.91927356390823156</v>
@@ -16506,7 +16506,7 @@
         <v>925</v>
       </c>
       <c r="X14" t="s">
-        <v>844</v>
+        <v>823</v>
       </c>
       <c r="Y14">
         <v>17.616</v>
@@ -16541,7 +16541,7 @@
         <v>855</v>
       </c>
       <c r="K15" t="s">
-        <v>704</v>
+        <v>723</v>
       </c>
       <c r="L15">
         <v>4.6464784096723921</v>
@@ -16574,7 +16574,7 @@
         <v>927</v>
       </c>
       <c r="X15" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="Y15">
         <v>14.769</v>
@@ -16609,7 +16609,7 @@
         <v>857</v>
       </c>
       <c r="K16" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="L16">
         <v>11.882635191498228</v>
@@ -16642,7 +16642,7 @@
         <v>929</v>
       </c>
       <c r="X16" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="Y16">
         <v>13.2255</v>
@@ -16677,7 +16677,7 @@
         <v>859</v>
       </c>
       <c r="K17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="L17">
         <v>11.092555055294371</v>
@@ -16710,7 +16710,7 @@
         <v>931</v>
       </c>
       <c r="X17" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="Y17">
         <v>28.651499999999999</v>
@@ -16778,7 +16778,7 @@
         <v>933</v>
       </c>
       <c r="X18" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="Y18">
         <v>27.531749999999999</v>
@@ -16813,7 +16813,7 @@
         <v>863</v>
       </c>
       <c r="K19" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="L19">
         <v>16.426692253806657</v>
@@ -16846,7 +16846,7 @@
         <v>935</v>
       </c>
       <c r="X19" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="Y19">
         <v>51.64425</v>
@@ -16881,7 +16881,7 @@
         <v>865</v>
       </c>
       <c r="K20" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="L20">
         <v>8.1288287393980401</v>
@@ -16914,7 +16914,7 @@
         <v>937</v>
       </c>
       <c r="X20" t="s">
-        <v>846</v>
+        <v>825</v>
       </c>
       <c r="Y20">
         <v>134.35650000000001</v>
@@ -16949,7 +16949,7 @@
         <v>867</v>
       </c>
       <c r="K21" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L21">
         <v>0.13371018978628957</v>
@@ -16982,7 +16982,7 @@
         <v>939</v>
       </c>
       <c r="X21" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="Y21">
         <v>7.9987500000000002</v>
@@ -17017,7 +17017,7 @@
         <v>869</v>
       </c>
       <c r="K22" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="L22">
         <v>1.3857406990868373</v>
@@ -17050,7 +17050,7 @@
         <v>941</v>
       </c>
       <c r="X22" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="Y22">
         <v>115.36875000000001</v>
@@ -17118,7 +17118,7 @@
         <v>943</v>
       </c>
       <c r="X23" t="s">
-        <v>841</v>
+        <v>811</v>
       </c>
       <c r="Y23">
         <v>18.766500000000001</v>
@@ -17153,7 +17153,7 @@
         <v>873</v>
       </c>
       <c r="K24" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="L24">
         <v>0.96556410486278166</v>
@@ -17186,7 +17186,7 @@
         <v>945</v>
       </c>
       <c r="X24" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="Y24">
         <v>1.5217499999999999</v>
@@ -17221,7 +17221,7 @@
         <v>875</v>
       </c>
       <c r="K25" t="s">
-        <v>725</v>
+        <v>692</v>
       </c>
       <c r="L25">
         <v>0.43746236883491152</v>
@@ -17254,7 +17254,7 @@
         <v>947</v>
       </c>
       <c r="X25" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="Y25">
         <v>1.90425</v>
@@ -17289,7 +17289,7 @@
         <v>877</v>
       </c>
       <c r="K26" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="L26">
         <v>1.8762027163233561</v>
@@ -17322,7 +17322,7 @@
         <v>949</v>
       </c>
       <c r="X26" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="Y26">
         <v>102.82125000000001</v>
@@ -17357,7 +17357,7 @@
         <v>879</v>
       </c>
       <c r="K27" t="s">
-        <v>728</v>
+        <v>695</v>
       </c>
       <c r="L27">
         <v>0.18022981623384116</v>
@@ -17390,7 +17390,7 @@
         <v>951</v>
       </c>
       <c r="X27" t="s">
-        <v>845</v>
+        <v>824</v>
       </c>
       <c r="Y27">
         <v>26.381250000000001</v>
@@ -17425,7 +17425,7 @@
         <v>881</v>
       </c>
       <c r="K28" t="s">
-        <v>729</v>
+        <v>696</v>
       </c>
       <c r="L28">
         <v>1.1308942027141895</v>
@@ -17458,7 +17458,7 @@
         <v>953</v>
       </c>
       <c r="X28" t="s">
-        <v>840</v>
+        <v>810</v>
       </c>
       <c r="Y28">
         <v>9.1432500000000001</v>
@@ -17493,7 +17493,7 @@
         <v>883</v>
       </c>
       <c r="K29" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L29">
         <v>0.7454968470610035</v>
@@ -17526,7 +17526,7 @@
         <v>955</v>
       </c>
       <c r="X29" t="s">
-        <v>838</v>
+        <v>808</v>
       </c>
       <c r="Y29">
         <v>49.376249999999999</v>
@@ -17561,7 +17561,7 @@
         <v>885</v>
       </c>
       <c r="K30" t="s">
-        <v>702</v>
+        <v>721</v>
       </c>
       <c r="L30">
         <v>0.13491890498058171</v>
@@ -17594,7 +17594,7 @@
         <v>957</v>
       </c>
       <c r="X30" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="Y30">
         <v>64.686750000000004</v>
@@ -17629,7 +17629,7 @@
         <v>887</v>
       </c>
       <c r="K31" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="L31">
         <v>3.3502966177508899E-2</v>
@@ -17662,7 +17662,7 @@
         <v>959</v>
       </c>
       <c r="X31" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="Y31">
         <v>19.151250000000001</v>
@@ -17697,7 +17697,7 @@
         <v>889</v>
       </c>
       <c r="K32" t="s">
-        <v>700</v>
+        <v>719</v>
       </c>
       <c r="L32">
         <v>4.4570745535421293E-2</v>
@@ -17730,7 +17730,7 @@
         <v>961</v>
       </c>
       <c r="X32" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="Y32">
         <v>91.322249999999997</v>
@@ -17765,7 +17765,7 @@
         <v>891</v>
       </c>
       <c r="K33" t="s">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="L33">
         <v>1.8432371407733249E-2</v>
@@ -17798,7 +17798,7 @@
         <v>963</v>
       </c>
       <c r="X33" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="Y33">
         <v>86.045249999999996</v>
@@ -17833,7 +17833,7 @@
         <v>893</v>
       </c>
       <c r="K34" t="s">
-        <v>694</v>
+        <v>713</v>
       </c>
       <c r="L34">
         <v>0.33180838345937391</v>
@@ -17866,7 +17866,7 @@
         <v>965</v>
       </c>
       <c r="X34" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="Y34">
         <v>34.774500000000003</v>
@@ -17901,7 +17901,7 @@
         <v>895</v>
       </c>
       <c r="K35" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L35">
         <v>3.1614758986586073</v>
@@ -17934,7 +17934,7 @@
         <v>967</v>
       </c>
       <c r="X35" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="Y35">
         <v>60.10125</v>
@@ -17969,7 +17969,7 @@
         <v>897</v>
       </c>
       <c r="K36" t="s">
-        <v>699</v>
+        <v>718</v>
       </c>
       <c r="L36">
         <v>1.3726240143913757</v>
@@ -18002,7 +18002,7 @@
         <v>969</v>
       </c>
       <c r="X36" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="Y36">
         <v>2.3287499999999999</v>
@@ -18037,7 +18037,7 @@
         <v>899</v>
       </c>
       <c r="K37" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="L37">
         <v>0.1338251234250375</v>
@@ -18070,7 +18070,7 @@
         <v>971</v>
       </c>
       <c r="X37" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="Y37">
         <v>17.766749999999998</v>
@@ -18105,7 +18105,7 @@
         <v>901</v>
       </c>
       <c r="K38" t="s">
-        <v>701</v>
+        <v>720</v>
       </c>
       <c r="L38">
         <v>2.1118535388590605</v>
@@ -18138,7 +18138,7 @@
         <v>973</v>
       </c>
       <c r="X38" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="Y38">
         <v>2.073</v>
@@ -18173,7 +18173,7 @@
         <v>903</v>
       </c>
       <c r="K39" t="s">
-        <v>726</v>
+        <v>693</v>
       </c>
       <c r="L39">
         <v>1.5197190100572773</v>
@@ -18206,7 +18206,7 @@
         <v>975</v>
       </c>
       <c r="X39" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="Y39">
         <v>3.1927500000000002</v>
@@ -18241,7 +18241,7 @@
         <v>905</v>
       </c>
       <c r="K40" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="L40">
         <v>3.2370560671094046</v>
@@ -18274,7 +18274,7 @@
         <v>977</v>
       </c>
       <c r="X40" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="Y40">
         <v>8.2132500000000004</v>
@@ -18309,7 +18309,7 @@
         <v>907</v>
       </c>
       <c r="K41" t="s">
-        <v>698</v>
+        <v>717</v>
       </c>
       <c r="L41">
         <v>9.3502299727040246</v>
@@ -18342,7 +18342,7 @@
         <v>979</v>
       </c>
       <c r="X41" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="Y41">
         <v>1.2622500000000001</v>
@@ -18377,7 +18377,7 @@
         <v>909</v>
       </c>
       <c r="K42" t="s">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="L42">
         <v>3.7895528026363667</v>
@@ -18410,7 +18410,7 @@
         <v>981</v>
       </c>
       <c r="X42" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="Y42">
         <v>7.3717499999999996</v>
@@ -18445,7 +18445,7 @@
         <v>911</v>
       </c>
       <c r="K43" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="L43">
         <v>2.4345968290099598</v>
@@ -18478,7 +18478,7 @@
         <v>983</v>
       </c>
       <c r="X43" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="Y43">
         <v>9.1162500000000009</v>
@@ -18513,7 +18513,7 @@
         <v>913</v>
       </c>
       <c r="K44" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="L44">
         <v>3.5872166924997928</v>
@@ -18546,7 +18546,7 @@
         <v>985</v>
       </c>
       <c r="X44" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="Y44">
         <v>2.0219999999999998</v>
@@ -18581,7 +18581,7 @@
         <v>915</v>
       </c>
       <c r="K45" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="L45">
         <v>1.2359990336927942</v>
@@ -18614,7 +18614,7 @@
         <v>987</v>
       </c>
       <c r="X45" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="Y45">
         <v>6.5925000000000002</v>
@@ -18649,7 +18649,7 @@
         <v>917</v>
       </c>
       <c r="K46" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L46">
         <v>3.8785201943148309</v>
@@ -18664,7 +18664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156B972F-3A05-41CE-9CDE-2AA55CB0F32C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B37034CD-1148-4905-8DA4-0ADBBDF0603C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20481,7 +20481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206BC03C-031C-4E6A-9FDC-B993A75215FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD5EDB31-5E71-4505-96B6-BDA8363A5212}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
